--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376233</v>
+        <v>124376865</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467068</v>
+        <v>466954</v>
       </c>
       <c r="R2" t="n">
-        <v>6720851</v>
+        <v>6720913</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124376295</v>
+        <v>124375132</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467095</v>
+        <v>467184</v>
       </c>
       <c r="R3" t="n">
-        <v>6720881</v>
+        <v>6720843</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376194</v>
+        <v>124374995</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466996</v>
+        <v>467162</v>
       </c>
       <c r="R4" t="n">
-        <v>6720894</v>
+        <v>6720859</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375132</v>
+        <v>124374620</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,24 +1013,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1045,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467184</v>
+        <v>467213</v>
       </c>
       <c r="R5" t="n">
-        <v>6720843</v>
+        <v>6720795</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376889</v>
+        <v>124376750</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1143,7 +1142,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1155,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467053</v>
+        <v>467146</v>
       </c>
       <c r="R6" t="n">
-        <v>6720874</v>
+        <v>6721019</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1218,7 +1217,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124375140</v>
+        <v>124376910</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1251,7 +1250,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1261,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467191</v>
+        <v>467140</v>
       </c>
       <c r="R7" t="n">
-        <v>6720859</v>
+        <v>6720805</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1324,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374678</v>
+        <v>124376827</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1357,7 +1360,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1367,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467230</v>
+        <v>467053</v>
       </c>
       <c r="R8" t="n">
-        <v>6720817</v>
+        <v>6720938</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1430,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376794</v>
+        <v>124376194</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,34 +1449,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467106</v>
+        <v>466996</v>
       </c>
       <c r="R9" t="n">
-        <v>6720967</v>
+        <v>6720894</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1540,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375713</v>
+        <v>124375938</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,30 +1564,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1583,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467042</v>
+        <v>466966</v>
       </c>
       <c r="R10" t="n">
-        <v>6721029</v>
+        <v>6720916</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1627,7 +1644,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1646,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374570</v>
+        <v>124374936</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1689,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467219</v>
+        <v>467173</v>
       </c>
       <c r="R11" t="n">
-        <v>6720761</v>
+        <v>6720889</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1752,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375684</v>
+        <v>124375783</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,30 +1780,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467166</v>
+        <v>467016</v>
       </c>
       <c r="R12" t="n">
-        <v>6720986</v>
+        <v>6720909</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1858,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375732</v>
+        <v>124375436</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,36 +1895,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467043</v>
+        <v>467164</v>
       </c>
       <c r="R13" t="n">
-        <v>6720984</v>
+        <v>6720898</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1970,10 +1998,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375270</v>
+        <v>124376046</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,30 +2010,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2013,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467180</v>
+        <v>466941</v>
       </c>
       <c r="R14" t="n">
-        <v>6720912</v>
+        <v>6720908</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2076,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375768</v>
+        <v>124374804</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,24 +2129,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2119,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467034</v>
+        <v>467239</v>
       </c>
       <c r="R15" t="n">
-        <v>6720933</v>
+        <v>6720849</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2182,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375292</v>
+        <v>124374678</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2198,21 +2239,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2225,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467160</v>
+        <v>467230</v>
       </c>
       <c r="R16" t="n">
-        <v>6720888</v>
+        <v>6720817</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2288,10 +2329,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124376923</v>
+        <v>124375461</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,34 +2341,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2335,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467176</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6720792</v>
+        <v>6720908</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2398,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124375461</v>
+        <v>124375713</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2410,39 +2456,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2450,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467156</v>
+        <v>467042</v>
       </c>
       <c r="R18" t="n">
-        <v>6720908</v>
+        <v>6721029</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2513,10 +2550,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374620</v>
+        <v>124375292</v>
       </c>
       <c r="B19" t="n">
-        <v>91032</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,28 +2566,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2560,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467213</v>
+        <v>467160</v>
       </c>
       <c r="R19" t="n">
-        <v>6720795</v>
+        <v>6720888</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2623,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124375752</v>
+        <v>124374584</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2635,36 +2668,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2672,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467047</v>
+        <v>467197</v>
       </c>
       <c r="R20" t="n">
-        <v>6720974</v>
+        <v>6720764</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2735,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124374845</v>
+        <v>124374757</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,39 +2774,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2787,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467251</v>
+        <v>467204</v>
       </c>
       <c r="R21" t="n">
-        <v>6720866</v>
+        <v>6720836</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2850,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376089</v>
+        <v>124375270</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,39 +2880,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2902,10 +2911,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466904</v>
+        <v>467180</v>
       </c>
       <c r="R22" t="n">
-        <v>6720952</v>
+        <v>6720912</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2965,7 +2974,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374736</v>
+        <v>124374508</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3008,10 +3017,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467232</v>
+        <v>467196</v>
       </c>
       <c r="R23" t="n">
-        <v>6720833</v>
+        <v>6720772</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3071,10 +3080,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124374600</v>
+        <v>124376295</v>
       </c>
       <c r="B24" t="n">
-        <v>92293</v>
+        <v>90977</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3087,21 +3096,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3114,10 +3123,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467226</v>
+        <v>467095</v>
       </c>
       <c r="R24" t="n">
-        <v>6720796</v>
+        <v>6720881</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3177,10 +3186,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124376843</v>
+        <v>124374309</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3193,30 +3202,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3224,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467041</v>
+        <v>467236</v>
       </c>
       <c r="R25" t="n">
-        <v>6720899</v>
+        <v>6720773</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3268,7 +3282,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3287,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124375106</v>
+        <v>124376270</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3299,30 +3312,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3330,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467167</v>
+        <v>467075</v>
       </c>
       <c r="R26" t="n">
-        <v>6720870</v>
+        <v>6720892</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3393,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124374309</v>
+        <v>124375400</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3405,39 +3424,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3445,10 +3464,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467236</v>
+        <v>467157</v>
       </c>
       <c r="R27" t="n">
-        <v>6720773</v>
+        <v>6720898</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3489,6 +3508,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3617,7 +3637,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375210</v>
+        <v>124374951</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3660,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467193</v>
+        <v>467182</v>
       </c>
       <c r="R29" t="n">
-        <v>6720911</v>
+        <v>6720879</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3723,10 +3743,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375596</v>
+        <v>124375039</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,39 +3755,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3775,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467127</v>
+        <v>467157</v>
       </c>
       <c r="R30" t="n">
-        <v>6720921</v>
+        <v>6720881</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3838,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124375400</v>
+        <v>124376320</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3850,39 +3861,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3890,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467157</v>
+        <v>467117</v>
       </c>
       <c r="R31" t="n">
-        <v>6720898</v>
+        <v>6720888</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3953,10 +3955,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375482</v>
+        <v>124374900</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3965,39 +3967,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4005,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467191</v>
       </c>
       <c r="R32" t="n">
-        <v>6720905</v>
+        <v>6720901</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4068,7 +4061,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124375057</v>
+        <v>124375010</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4111,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467156</v>
+        <v>467143</v>
       </c>
       <c r="R33" t="n">
-        <v>6720850</v>
+        <v>6720866</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4174,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374436</v>
+        <v>124375684</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4190,21 +4183,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4217,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467202</v>
+        <v>467166</v>
       </c>
       <c r="R34" t="n">
-        <v>6720759</v>
+        <v>6720986</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4280,10 +4273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374900</v>
+        <v>124375596</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4292,30 +4285,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4323,10 +4325,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467191</v>
+        <v>467127</v>
       </c>
       <c r="R35" t="n">
-        <v>6720901</v>
+        <v>6720921</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4386,7 +4388,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374951</v>
+        <v>124374553</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4429,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467182</v>
+        <v>467224</v>
       </c>
       <c r="R36" t="n">
-        <v>6720879</v>
+        <v>6720768</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4492,7 +4494,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124376762</v>
+        <v>124374964</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4525,11 +4527,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4539,10 +4537,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467043</v>
+        <v>467169</v>
       </c>
       <c r="R37" t="n">
-        <v>6721047</v>
+        <v>6720904</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4708,7 +4706,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124375039</v>
+        <v>124375210</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4751,10 +4749,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467157</v>
+        <v>467193</v>
       </c>
       <c r="R39" t="n">
-        <v>6720881</v>
+        <v>6720911</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4814,10 +4812,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124376865</v>
+        <v>124375768</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4830,28 +4828,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4861,10 +4855,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466954</v>
+        <v>467034</v>
       </c>
       <c r="R40" t="n">
-        <v>6720913</v>
+        <v>6720933</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4924,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124376320</v>
+        <v>124375118</v>
       </c>
       <c r="B41" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4940,21 +4934,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4967,10 +4961,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467117</v>
+        <v>467177</v>
       </c>
       <c r="R41" t="n">
-        <v>6720888</v>
+        <v>6720859</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5030,10 +5024,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124375621</v>
+        <v>124374570</v>
       </c>
       <c r="B42" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5046,28 +5040,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5077,10 +5067,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467135</v>
+        <v>467219</v>
       </c>
       <c r="R42" t="n">
-        <v>6720927</v>
+        <v>6720761</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5140,10 +5130,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376031</v>
+        <v>124376342</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5152,37 +5142,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5192,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466944</v>
+        <v>467083</v>
       </c>
       <c r="R43" t="n">
-        <v>6720920</v>
+        <v>6720839</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5255,7 +5237,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124374508</v>
+        <v>124376762</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5288,7 +5270,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5298,10 +5284,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467196</v>
+        <v>467043</v>
       </c>
       <c r="R44" t="n">
-        <v>6720772</v>
+        <v>6721047</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5361,7 +5347,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374995</v>
+        <v>124376843</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5394,7 +5380,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5404,10 +5394,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467162</v>
+        <v>467041</v>
       </c>
       <c r="R45" t="n">
-        <v>6720859</v>
+        <v>6720899</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5467,10 +5457,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124374936</v>
+        <v>124375482</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5479,30 +5469,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5510,10 +5509,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467173</v>
+        <v>467160</v>
       </c>
       <c r="R46" t="n">
-        <v>6720889</v>
+        <v>6720905</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5573,7 +5572,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124376750</v>
+        <v>124376775</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5608,7 +5607,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5620,10 +5619,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467146</v>
+        <v>467056</v>
       </c>
       <c r="R47" t="n">
-        <v>6721019</v>
+        <v>6720996</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5683,10 +5682,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124376385</v>
+        <v>124376126</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5695,39 +5694,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5735,10 +5730,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467094</v>
+        <v>466911</v>
       </c>
       <c r="R48" t="n">
-        <v>6720828</v>
+        <v>6720956</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5779,7 +5774,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5798,10 +5792,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376270</v>
+        <v>124375057</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5810,36 +5804,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5847,10 +5835,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467075</v>
+        <v>467156</v>
       </c>
       <c r="R49" t="n">
-        <v>6720892</v>
+        <v>6720850</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5910,10 +5898,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375650</v>
+        <v>124376385</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5922,30 +5910,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5953,10 +5950,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467134</v>
+        <v>467094</v>
       </c>
       <c r="R50" t="n">
-        <v>6720941</v>
+        <v>6720828</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6016,10 +6013,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124374964</v>
+        <v>124375650</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6032,21 +6029,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6059,10 +6056,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467169</v>
+        <v>467134</v>
       </c>
       <c r="R51" t="n">
-        <v>6720904</v>
+        <v>6720941</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6122,7 +6119,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124376910</v>
+        <v>124376923</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6169,10 +6166,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467140</v>
+        <v>467176</v>
       </c>
       <c r="R52" t="n">
-        <v>6720805</v>
+        <v>6720792</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6232,10 +6229,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124376342</v>
+        <v>124376794</v>
       </c>
       <c r="B53" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6244,31 +6241,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467083</v>
+        <v>467106</v>
       </c>
       <c r="R53" t="n">
-        <v>6720839</v>
+        <v>6720967</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6339,10 +6339,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124375783</v>
+        <v>124374600</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6351,39 +6351,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6391,10 +6382,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467016</v>
+        <v>467226</v>
       </c>
       <c r="R54" t="n">
-        <v>6720909</v>
+        <v>6720796</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6454,10 +6445,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124376046</v>
+        <v>124374709</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6466,39 +6457,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6506,10 +6488,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466941</v>
+        <v>467216</v>
       </c>
       <c r="R55" t="n">
-        <v>6720908</v>
+        <v>6720827</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6569,10 +6551,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376126</v>
+        <v>124375732</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6585,29 +6567,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6617,10 +6600,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466911</v>
+        <v>467043</v>
       </c>
       <c r="R56" t="n">
-        <v>6720956</v>
+        <v>6720984</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6661,6 +6644,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6679,7 +6663,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124374694</v>
+        <v>124374476</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6722,10 +6706,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467218</v>
+        <v>467209</v>
       </c>
       <c r="R57" t="n">
-        <v>6720814</v>
+        <v>6720770</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6785,10 +6769,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124374804</v>
+        <v>124376889</v>
       </c>
       <c r="B58" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6801,26 +6785,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -6832,10 +6816,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467239</v>
+        <v>467053</v>
       </c>
       <c r="R58" t="n">
-        <v>6720849</v>
+        <v>6720874</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6895,7 +6879,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124374553</v>
+        <v>124375140</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6938,10 +6922,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467224</v>
+        <v>467191</v>
       </c>
       <c r="R59" t="n">
-        <v>6720768</v>
+        <v>6720859</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7001,10 +6985,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124374709</v>
+        <v>124376233</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7013,25 +6997,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7044,10 +7028,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467216</v>
+        <v>467068</v>
       </c>
       <c r="R60" t="n">
-        <v>6720827</v>
+        <v>6720851</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7107,10 +7091,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124374584</v>
+        <v>124376089</v>
       </c>
       <c r="B61" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7119,30 +7103,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7150,10 +7143,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467197</v>
+        <v>466904</v>
       </c>
       <c r="R61" t="n">
-        <v>6720764</v>
+        <v>6720952</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7213,10 +7206,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124374757</v>
+        <v>124376031</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7225,30 +7218,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7256,10 +7258,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467204</v>
+        <v>466944</v>
       </c>
       <c r="R62" t="n">
-        <v>6720836</v>
+        <v>6720920</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7319,10 +7321,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124375436</v>
+        <v>124375752</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7331,39 +7333,36 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7371,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467164</v>
+        <v>467047</v>
       </c>
       <c r="R63" t="n">
-        <v>6720898</v>
+        <v>6720974</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7434,7 +7433,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124374476</v>
+        <v>124374736</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7477,10 +7476,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467209</v>
+        <v>467232</v>
       </c>
       <c r="R64" t="n">
-        <v>6720770</v>
+        <v>6720833</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7540,7 +7539,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124375118</v>
+        <v>124375106</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7583,10 +7582,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467177</v>
+        <v>467167</v>
       </c>
       <c r="R65" t="n">
-        <v>6720859</v>
+        <v>6720870</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7646,10 +7645,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124375938</v>
+        <v>124374436</v>
       </c>
       <c r="B66" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7658,35 +7657,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7694,10 +7688,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466966</v>
+        <v>467202</v>
       </c>
       <c r="R66" t="n">
-        <v>6720916</v>
+        <v>6720759</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7738,6 +7732,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7756,7 +7751,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375010</v>
+        <v>124374694</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7799,10 +7794,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467143</v>
+        <v>467218</v>
       </c>
       <c r="R67" t="n">
-        <v>6720866</v>
+        <v>6720814</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7862,10 +7857,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376827</v>
+        <v>124375621</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7878,26 +7873,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -7909,10 +7904,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467053</v>
+        <v>467135</v>
       </c>
       <c r="R68" t="n">
-        <v>6720938</v>
+        <v>6720927</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7972,10 +7967,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124376775</v>
+        <v>124374845</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7984,34 +7979,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467056</v>
+        <v>467251</v>
       </c>
       <c r="R69" t="n">
-        <v>6720996</v>
+        <v>6720866</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376865</v>
+        <v>124374600</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466954</v>
+        <v>467226</v>
       </c>
       <c r="R2" t="n">
-        <v>6720913</v>
+        <v>6720796</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375132</v>
+        <v>124375713</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467184</v>
+        <v>467042</v>
       </c>
       <c r="R3" t="n">
-        <v>6720843</v>
+        <v>6721029</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374995</v>
+        <v>124376342</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,30 +899,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467162</v>
+        <v>467083</v>
       </c>
       <c r="R4" t="n">
-        <v>6720859</v>
+        <v>6720839</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -997,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374620</v>
+        <v>124375292</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,28 +1010,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1044,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467213</v>
+        <v>467160</v>
       </c>
       <c r="R5" t="n">
-        <v>6720795</v>
+        <v>6720888</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1217,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124376910</v>
+        <v>124374936</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1250,11 +1243,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1264,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467140</v>
+        <v>467173</v>
       </c>
       <c r="R7" t="n">
-        <v>6720805</v>
+        <v>6720889</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1327,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124376827</v>
+        <v>124374553</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1360,11 +1349,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1374,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467053</v>
+        <v>467224</v>
       </c>
       <c r="R8" t="n">
-        <v>6720938</v>
+        <v>6720768</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1437,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376194</v>
+        <v>124375106</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,39 +1434,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466996</v>
+        <v>467167</v>
       </c>
       <c r="R9" t="n">
-        <v>6720894</v>
+        <v>6720870</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1552,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375938</v>
+        <v>124375461</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,35 +1540,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466966</v>
+        <v>467156</v>
       </c>
       <c r="R10" t="n">
-        <v>6720916</v>
+        <v>6720908</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1644,6 +1624,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1662,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374936</v>
+        <v>124376385</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,30 +1655,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1705,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467173</v>
+        <v>467094</v>
       </c>
       <c r="R11" t="n">
-        <v>6720889</v>
+        <v>6720828</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1768,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375783</v>
+        <v>124376889</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,39 +1770,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1820,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467016</v>
+        <v>467053</v>
       </c>
       <c r="R12" t="n">
-        <v>6720909</v>
+        <v>6720874</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1883,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375436</v>
+        <v>124376808</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,39 +1880,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1935,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467164</v>
+        <v>467087</v>
       </c>
       <c r="R13" t="n">
-        <v>6720898</v>
+        <v>6720934</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1998,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124376046</v>
+        <v>124376295</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2010,39 +1990,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2050,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>466941</v>
+        <v>467095</v>
       </c>
       <c r="R14" t="n">
-        <v>6720908</v>
+        <v>6720881</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2113,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374804</v>
+        <v>124375057</v>
       </c>
       <c r="B15" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,28 +2100,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2160,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467239</v>
+        <v>467156</v>
       </c>
       <c r="R15" t="n">
-        <v>6720849</v>
+        <v>6720850</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2223,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374678</v>
+        <v>124375752</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,30 +2202,36 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2266,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467230</v>
+        <v>467047</v>
       </c>
       <c r="R16" t="n">
-        <v>6720817</v>
+        <v>6720974</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2329,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375461</v>
+        <v>124376320</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,39 +2314,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2381,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>467117</v>
       </c>
       <c r="R17" t="n">
-        <v>6720908</v>
+        <v>6720888</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2444,7 +2408,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124375713</v>
+        <v>124375768</v>
       </c>
       <c r="B18" t="n">
         <v>78547</v>
@@ -2487,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467042</v>
+        <v>467034</v>
       </c>
       <c r="R18" t="n">
-        <v>6721029</v>
+        <v>6720933</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2550,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375292</v>
+        <v>124375938</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2562,30 +2526,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2593,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467160</v>
+        <v>466966</v>
       </c>
       <c r="R19" t="n">
-        <v>6720888</v>
+        <v>6720916</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2637,7 +2606,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2656,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124374584</v>
+        <v>124375732</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,30 +2636,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2699,10 +2673,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467197</v>
+        <v>467043</v>
       </c>
       <c r="R20" t="n">
-        <v>6720764</v>
+        <v>6720984</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2762,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124374757</v>
+        <v>124375621</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2778,24 +2752,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2805,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467204</v>
+        <v>467135</v>
       </c>
       <c r="R21" t="n">
-        <v>6720836</v>
+        <v>6720927</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2868,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124375270</v>
+        <v>124376126</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2880,30 +2858,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2911,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467180</v>
+        <v>466911</v>
       </c>
       <c r="R22" t="n">
-        <v>6720912</v>
+        <v>6720956</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2955,7 +2938,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2974,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374508</v>
+        <v>124376194</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2986,30 +2968,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3017,10 +3008,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467196</v>
+        <v>466996</v>
       </c>
       <c r="R23" t="n">
-        <v>6720772</v>
+        <v>6720894</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3080,10 +3071,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124376295</v>
+        <v>124375010</v>
       </c>
       <c r="B24" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3092,25 +3083,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3123,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467095</v>
+        <v>467143</v>
       </c>
       <c r="R24" t="n">
-        <v>6720881</v>
+        <v>6720866</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3186,10 +3177,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374309</v>
+        <v>124374900</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3202,35 +3193,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3238,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467236</v>
+        <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6720773</v>
+        <v>6720901</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3282,6 +3264,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3300,10 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124376270</v>
+        <v>124374757</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3312,36 +3295,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3349,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467075</v>
+        <v>467204</v>
       </c>
       <c r="R26" t="n">
-        <v>6720892</v>
+        <v>6720836</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3412,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375400</v>
+        <v>124375140</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3424,39 +3401,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3464,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467157</v>
+        <v>467191</v>
       </c>
       <c r="R27" t="n">
-        <v>6720898</v>
+        <v>6720859</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3527,7 +3495,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124376808</v>
+        <v>124374508</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3560,11 +3528,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3574,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467087</v>
+        <v>467196</v>
       </c>
       <c r="R28" t="n">
-        <v>6720934</v>
+        <v>6720772</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3637,7 +3601,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374951</v>
+        <v>124374995</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3680,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467182</v>
+        <v>467162</v>
       </c>
       <c r="R29" t="n">
-        <v>6720879</v>
+        <v>6720859</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3743,7 +3707,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375039</v>
+        <v>124374964</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3786,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467157</v>
+        <v>467169</v>
       </c>
       <c r="R30" t="n">
-        <v>6720881</v>
+        <v>6720904</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3849,10 +3813,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124376320</v>
+        <v>124374951</v>
       </c>
       <c r="B31" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3865,21 +3829,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3892,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467117</v>
+        <v>467182</v>
       </c>
       <c r="R31" t="n">
-        <v>6720888</v>
+        <v>6720879</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3955,7 +3919,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124374900</v>
+        <v>124375210</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3998,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467191</v>
+        <v>467193</v>
       </c>
       <c r="R32" t="n">
-        <v>6720901</v>
+        <v>6720911</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4061,10 +4025,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124375010</v>
+        <v>124374620</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4077,24 +4041,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4104,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467143</v>
+        <v>467213</v>
       </c>
       <c r="R33" t="n">
-        <v>6720866</v>
+        <v>6720795</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4167,10 +4135,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124375684</v>
+        <v>124374436</v>
       </c>
       <c r="B34" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4183,21 +4151,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4210,10 +4178,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467166</v>
+        <v>467202</v>
       </c>
       <c r="R34" t="n">
-        <v>6720986</v>
+        <v>6720759</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4273,7 +4241,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124375596</v>
+        <v>124374845</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4308,7 +4276,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4325,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467127</v>
+        <v>467251</v>
       </c>
       <c r="R35" t="n">
-        <v>6720921</v>
+        <v>6720866</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4388,7 +4356,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374553</v>
+        <v>124374476</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4431,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467224</v>
+        <v>467209</v>
       </c>
       <c r="R36" t="n">
-        <v>6720768</v>
+        <v>6720770</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4494,10 +4462,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374964</v>
+        <v>124376233</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4506,25 +4474,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4537,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467169</v>
+        <v>467068</v>
       </c>
       <c r="R37" t="n">
-        <v>6720904</v>
+        <v>6720851</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4706,7 +4674,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124375210</v>
+        <v>124375039</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4749,10 +4717,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467193</v>
+        <v>467157</v>
       </c>
       <c r="R39" t="n">
-        <v>6720911</v>
+        <v>6720881</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4812,10 +4780,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375768</v>
+        <v>124375783</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,30 +4792,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4855,10 +4832,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467034</v>
+        <v>467016</v>
       </c>
       <c r="R40" t="n">
-        <v>6720933</v>
+        <v>6720909</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4918,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375118</v>
+        <v>124374584</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4934,21 +4911,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4961,10 +4938,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467177</v>
+        <v>467197</v>
       </c>
       <c r="R41" t="n">
-        <v>6720859</v>
+        <v>6720764</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5024,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124374570</v>
+        <v>124376270</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5036,30 +5013,36 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5067,10 +5050,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467219</v>
+        <v>467075</v>
       </c>
       <c r="R42" t="n">
-        <v>6720761</v>
+        <v>6720892</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5130,10 +5113,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376342</v>
+        <v>124375118</v>
       </c>
       <c r="B43" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5142,31 +5125,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5174,10 +5156,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467083</v>
+        <v>467177</v>
       </c>
       <c r="R43" t="n">
-        <v>6720839</v>
+        <v>6720859</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5237,7 +5219,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124376762</v>
+        <v>124376775</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5284,10 +5266,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467043</v>
+        <v>467056</v>
       </c>
       <c r="R44" t="n">
-        <v>6721047</v>
+        <v>6720996</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5347,7 +5329,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124376843</v>
+        <v>124376762</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5394,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467041</v>
+        <v>467043</v>
       </c>
       <c r="R45" t="n">
-        <v>6720899</v>
+        <v>6721047</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5457,7 +5439,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375482</v>
+        <v>124376046</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5492,7 +5474,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5509,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467160</v>
+        <v>466941</v>
       </c>
       <c r="R46" t="n">
-        <v>6720905</v>
+        <v>6720908</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5572,10 +5554,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124376775</v>
+        <v>124374804</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5588,26 +5570,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5619,10 +5601,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467056</v>
+        <v>467239</v>
       </c>
       <c r="R47" t="n">
-        <v>6720996</v>
+        <v>6720849</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5682,10 +5664,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124376126</v>
+        <v>124374694</v>
       </c>
       <c r="B48" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5694,35 +5676,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5730,10 +5707,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466911</v>
+        <v>467218</v>
       </c>
       <c r="R48" t="n">
-        <v>6720956</v>
+        <v>6720814</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5774,6 +5751,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5792,7 +5770,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124375057</v>
+        <v>124374709</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5835,10 +5813,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467156</v>
+        <v>467216</v>
       </c>
       <c r="R49" t="n">
-        <v>6720850</v>
+        <v>6720827</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5898,10 +5876,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376385</v>
+        <v>124376827</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5910,39 +5888,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5950,10 +5923,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467094</v>
+        <v>467053</v>
       </c>
       <c r="R50" t="n">
-        <v>6720828</v>
+        <v>6720938</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6013,10 +5986,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375650</v>
+        <v>124375400</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6025,30 +5998,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6056,10 +6038,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467134</v>
+        <v>467157</v>
       </c>
       <c r="R51" t="n">
-        <v>6720941</v>
+        <v>6720898</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6119,10 +6101,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124376923</v>
+        <v>124374309</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6135,30 +6117,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6166,10 +6153,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467176</v>
+        <v>467236</v>
       </c>
       <c r="R52" t="n">
-        <v>6720792</v>
+        <v>6720773</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6210,7 +6197,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6229,7 +6215,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124376794</v>
+        <v>124376843</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6276,10 +6262,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467106</v>
+        <v>467041</v>
       </c>
       <c r="R53" t="n">
-        <v>6720967</v>
+        <v>6720899</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6339,10 +6325,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374600</v>
+        <v>124375270</v>
       </c>
       <c r="B54" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6351,25 +6337,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6382,10 +6368,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467226</v>
+        <v>467180</v>
       </c>
       <c r="R54" t="n">
-        <v>6720796</v>
+        <v>6720912</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6445,7 +6431,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374709</v>
+        <v>124374736</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6488,10 +6474,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467216</v>
+        <v>467232</v>
       </c>
       <c r="R55" t="n">
-        <v>6720827</v>
+        <v>6720833</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6551,10 +6537,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124375732</v>
+        <v>124376089</v>
       </c>
       <c r="B56" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6563,36 +6549,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6600,10 +6589,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467043</v>
+        <v>466904</v>
       </c>
       <c r="R56" t="n">
-        <v>6720984</v>
+        <v>6720952</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6663,10 +6652,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124374476</v>
+        <v>124375650</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6679,21 +6668,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6706,10 +6695,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467209</v>
+        <v>467134</v>
       </c>
       <c r="R57" t="n">
-        <v>6720770</v>
+        <v>6720941</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6769,10 +6758,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124376889</v>
+        <v>124375684</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6785,28 +6774,24 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6816,10 +6801,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467053</v>
+        <v>467166</v>
       </c>
       <c r="R58" t="n">
-        <v>6720874</v>
+        <v>6720986</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6879,10 +6864,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375140</v>
+        <v>124375482</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6891,30 +6876,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6922,10 +6916,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467191</v>
+        <v>467160</v>
       </c>
       <c r="R59" t="n">
-        <v>6720859</v>
+        <v>6720905</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6985,10 +6979,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376233</v>
+        <v>124376865</v>
       </c>
       <c r="B60" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6997,28 +6991,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7028,10 +7026,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467068</v>
+        <v>466954</v>
       </c>
       <c r="R60" t="n">
-        <v>6720851</v>
+        <v>6720913</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7091,7 +7089,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376089</v>
+        <v>124376031</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7126,7 +7124,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7143,10 +7141,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466904</v>
+        <v>466944</v>
       </c>
       <c r="R61" t="n">
-        <v>6720952</v>
+        <v>6720920</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7206,7 +7204,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376031</v>
+        <v>124375436</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7241,7 +7239,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7258,10 +7256,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466944</v>
+        <v>467164</v>
       </c>
       <c r="R62" t="n">
-        <v>6720920</v>
+        <v>6720898</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7321,10 +7319,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124375752</v>
+        <v>124374570</v>
       </c>
       <c r="B63" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7333,36 +7331,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7370,10 +7362,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467047</v>
+        <v>467219</v>
       </c>
       <c r="R63" t="n">
-        <v>6720974</v>
+        <v>6720761</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7433,7 +7425,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124374736</v>
+        <v>124376794</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7466,7 +7458,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -7476,10 +7472,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467232</v>
+        <v>467106</v>
       </c>
       <c r="R64" t="n">
-        <v>6720833</v>
+        <v>6720967</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7539,7 +7535,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124375106</v>
+        <v>124376910</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7572,7 +7568,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467167</v>
+        <v>467140</v>
       </c>
       <c r="R65" t="n">
-        <v>6720870</v>
+        <v>6720805</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7645,7 +7645,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124374436</v>
+        <v>124374678</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467202</v>
+        <v>467230</v>
       </c>
       <c r="R66" t="n">
-        <v>6720759</v>
+        <v>6720817</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7751,10 +7751,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124374694</v>
+        <v>124375596</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7763,30 +7763,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7794,10 +7803,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467218</v>
+        <v>467127</v>
       </c>
       <c r="R67" t="n">
-        <v>6720814</v>
+        <v>6720921</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7857,10 +7866,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124375621</v>
+        <v>124375132</v>
       </c>
       <c r="B68" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7873,28 +7882,24 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -7904,10 +7909,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467135</v>
+        <v>467184</v>
       </c>
       <c r="R68" t="n">
-        <v>6720927</v>
+        <v>6720843</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7967,10 +7972,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124374845</v>
+        <v>124376923</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7979,39 +7984,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467251</v>
+        <v>467176</v>
       </c>
       <c r="R69" t="n">
-        <v>6720866</v>
+        <v>6720792</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374600</v>
+        <v>124374804</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467226</v>
+        <v>467239</v>
       </c>
       <c r="R2" t="n">
-        <v>6720796</v>
+        <v>6720849</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375713</v>
+        <v>124374570</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467042</v>
+        <v>467219</v>
       </c>
       <c r="R3" t="n">
-        <v>6721029</v>
+        <v>6720761</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376342</v>
+        <v>124376750</v>
       </c>
       <c r="B4" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,31 +903,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467083</v>
+        <v>467146</v>
       </c>
       <c r="R4" t="n">
-        <v>6720839</v>
+        <v>6721019</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375292</v>
+        <v>124375732</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,30 +1013,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467160</v>
+        <v>467043</v>
       </c>
       <c r="R5" t="n">
-        <v>6720888</v>
+        <v>6720984</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1100,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376750</v>
+        <v>124374309</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,30 +1129,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467146</v>
+        <v>467236</v>
       </c>
       <c r="R6" t="n">
-        <v>6721019</v>
+        <v>6720773</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1191,7 +1209,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374936</v>
+        <v>124374995</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1253,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467173</v>
+        <v>467162</v>
       </c>
       <c r="R7" t="n">
-        <v>6720889</v>
+        <v>6720859</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1316,7 +1333,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374553</v>
+        <v>124374951</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1359,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467224</v>
+        <v>467182</v>
       </c>
       <c r="R8" t="n">
-        <v>6720768</v>
+        <v>6720879</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1422,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124375106</v>
+        <v>124376342</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,30 +1451,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467167</v>
+        <v>467083</v>
       </c>
       <c r="R9" t="n">
-        <v>6720870</v>
+        <v>6720839</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1528,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375461</v>
+        <v>124375596</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1563,7 +1581,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1580,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467156</v>
+        <v>467127</v>
       </c>
       <c r="R10" t="n">
-        <v>6720908</v>
+        <v>6720921</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1643,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124376385</v>
+        <v>124375010</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,39 +1673,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1695,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467094</v>
+        <v>467143</v>
       </c>
       <c r="R11" t="n">
-        <v>6720828</v>
+        <v>6720866</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1758,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376889</v>
+        <v>124376295</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,32 +1779,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1805,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467053</v>
+        <v>467095</v>
       </c>
       <c r="R12" t="n">
-        <v>6720874</v>
+        <v>6720881</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1868,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124376808</v>
+        <v>124375400</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,34 +1885,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467087</v>
+        <v>467157</v>
       </c>
       <c r="R13" t="n">
-        <v>6720934</v>
+        <v>6720898</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1978,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124376295</v>
+        <v>124374845</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,30 +2000,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467095</v>
+        <v>467251</v>
       </c>
       <c r="R14" t="n">
-        <v>6720881</v>
+        <v>6720866</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2084,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375057</v>
+        <v>124376046</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,30 +2115,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467156</v>
+        <v>466941</v>
       </c>
       <c r="R15" t="n">
-        <v>6720850</v>
+        <v>6720908</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2190,10 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375752</v>
+        <v>124375057</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,36 +2230,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2239,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467047</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6720974</v>
+        <v>6720850</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2302,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124376320</v>
+        <v>124376762</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,24 +2340,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2345,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467117</v>
+        <v>467043</v>
       </c>
       <c r="R17" t="n">
-        <v>6720888</v>
+        <v>6721047</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2408,10 +2434,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124375768</v>
+        <v>124375270</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,21 +2450,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2451,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467034</v>
+        <v>467180</v>
       </c>
       <c r="R18" t="n">
-        <v>6720933</v>
+        <v>6720912</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2514,10 +2540,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375938</v>
+        <v>124374709</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2526,35 +2552,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2562,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466966</v>
+        <v>467216</v>
       </c>
       <c r="R19" t="n">
-        <v>6720916</v>
+        <v>6720827</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2606,6 +2627,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124375732</v>
+        <v>124376089</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,36 +2658,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2673,10 +2698,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467043</v>
+        <v>466904</v>
       </c>
       <c r="R20" t="n">
-        <v>6720984</v>
+        <v>6720952</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2736,10 +2761,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375621</v>
+        <v>124376385</v>
       </c>
       <c r="B21" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,34 +2773,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2783,10 +2813,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467135</v>
+        <v>467094</v>
       </c>
       <c r="R21" t="n">
-        <v>6720927</v>
+        <v>6720828</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2846,10 +2876,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376126</v>
+        <v>124374736</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,35 +2888,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2894,10 +2919,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466911</v>
+        <v>467232</v>
       </c>
       <c r="R22" t="n">
-        <v>6720956</v>
+        <v>6720833</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2938,6 +2963,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2956,10 +2982,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124376194</v>
+        <v>124375768</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,39 +2994,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3008,10 +3025,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>466996</v>
+        <v>467034</v>
       </c>
       <c r="R23" t="n">
-        <v>6720894</v>
+        <v>6720933</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3071,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375010</v>
+        <v>124375938</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3083,30 +3100,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3114,10 +3136,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467143</v>
+        <v>466966</v>
       </c>
       <c r="R24" t="n">
-        <v>6720866</v>
+        <v>6720916</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3158,7 +3180,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3177,7 +3198,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374900</v>
+        <v>124375140</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3223,7 +3244,7 @@
         <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6720901</v>
+        <v>6720859</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3283,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374757</v>
+        <v>124374600</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,25 +3316,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3326,10 +3347,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467204</v>
+        <v>467226</v>
       </c>
       <c r="R26" t="n">
-        <v>6720836</v>
+        <v>6720796</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3389,7 +3410,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375140</v>
+        <v>124375210</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3432,10 +3453,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467191</v>
+        <v>467193</v>
       </c>
       <c r="R27" t="n">
-        <v>6720859</v>
+        <v>6720911</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3495,10 +3516,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374508</v>
+        <v>124376320</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,21 +3532,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3559,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467196</v>
+        <v>467117</v>
       </c>
       <c r="R28" t="n">
-        <v>6720772</v>
+        <v>6720888</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3601,7 +3622,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374995</v>
+        <v>124374476</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3644,10 +3665,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467162</v>
+        <v>467209</v>
       </c>
       <c r="R29" t="n">
-        <v>6720859</v>
+        <v>6720770</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3707,7 +3728,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124374964</v>
+        <v>124374900</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3750,10 +3771,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467169</v>
+        <v>467191</v>
       </c>
       <c r="R30" t="n">
-        <v>6720904</v>
+        <v>6720901</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3813,10 +3834,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124374951</v>
+        <v>124376126</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3825,30 +3846,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467182</v>
+        <v>466911</v>
       </c>
       <c r="R31" t="n">
-        <v>6720879</v>
+        <v>6720956</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3900,7 +3926,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3919,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375210</v>
+        <v>124375461</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3931,30 +3956,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3962,10 +3996,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467193</v>
+        <v>467156</v>
       </c>
       <c r="R32" t="n">
-        <v>6720911</v>
+        <v>6720908</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4025,10 +4059,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374620</v>
+        <v>124374694</v>
       </c>
       <c r="B33" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,28 +4075,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4072,10 +4102,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467213</v>
+        <v>467218</v>
       </c>
       <c r="R33" t="n">
-        <v>6720795</v>
+        <v>6720814</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4135,7 +4165,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374436</v>
+        <v>124374553</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4178,10 +4208,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467202</v>
+        <v>467224</v>
       </c>
       <c r="R34" t="n">
-        <v>6720759</v>
+        <v>6720768</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4241,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374845</v>
+        <v>124374964</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4253,39 +4283,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4293,10 +4314,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467251</v>
+        <v>467169</v>
       </c>
       <c r="R35" t="n">
-        <v>6720866</v>
+        <v>6720904</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4356,10 +4377,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374476</v>
+        <v>124376233</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,25 +4389,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4399,10 +4420,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467209</v>
+        <v>467068</v>
       </c>
       <c r="R36" t="n">
-        <v>6720770</v>
+        <v>6720851</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4462,10 +4483,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124376233</v>
+        <v>124375106</v>
       </c>
       <c r="B37" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4474,25 +4495,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4505,10 +4526,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467068</v>
+        <v>467167</v>
       </c>
       <c r="R37" t="n">
-        <v>6720851</v>
+        <v>6720870</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4568,7 +4589,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124374922</v>
+        <v>124375039</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4611,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467194</v>
+        <v>467157</v>
       </c>
       <c r="R38" t="n">
-        <v>6720885</v>
+        <v>6720881</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4674,10 +4695,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124375039</v>
+        <v>124375482</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4686,30 +4707,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4717,10 +4747,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467157</v>
+        <v>467160</v>
       </c>
       <c r="R39" t="n">
-        <v>6720881</v>
+        <v>6720905</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4780,10 +4810,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375783</v>
+        <v>124375752</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4792,39 +4822,36 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4832,10 +4859,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467016</v>
+        <v>467047</v>
       </c>
       <c r="R40" t="n">
-        <v>6720909</v>
+        <v>6720974</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4895,10 +4922,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124374584</v>
+        <v>124375436</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4907,30 +4934,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4938,10 +4974,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467197</v>
+        <v>467164</v>
       </c>
       <c r="R41" t="n">
-        <v>6720764</v>
+        <v>6720898</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5001,10 +5037,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124376270</v>
+        <v>124374584</v>
       </c>
       <c r="B42" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5013,36 +5049,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5050,10 +5080,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467075</v>
+        <v>467197</v>
       </c>
       <c r="R42" t="n">
-        <v>6720892</v>
+        <v>6720764</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5113,7 +5143,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375118</v>
+        <v>124376865</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5146,7 +5176,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5156,10 +5190,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467177</v>
+        <v>466954</v>
       </c>
       <c r="R43" t="n">
-        <v>6720859</v>
+        <v>6720913</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5219,7 +5253,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124376775</v>
+        <v>124376889</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5266,10 +5300,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467056</v>
+        <v>467053</v>
       </c>
       <c r="R44" t="n">
-        <v>6720996</v>
+        <v>6720874</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5329,10 +5363,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124376762</v>
+        <v>124376270</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5341,34 +5375,36 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5376,10 +5412,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467043</v>
+        <v>467075</v>
       </c>
       <c r="R45" t="n">
-        <v>6721047</v>
+        <v>6720892</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5439,10 +5475,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124376046</v>
+        <v>124375132</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,39 +5487,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5491,10 +5518,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466941</v>
+        <v>467184</v>
       </c>
       <c r="R46" t="n">
-        <v>6720908</v>
+        <v>6720843</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5554,10 +5581,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374804</v>
+        <v>124376923</v>
       </c>
       <c r="B47" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5570,26 +5597,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5601,10 +5628,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467239</v>
+        <v>467176</v>
       </c>
       <c r="R47" t="n">
-        <v>6720849</v>
+        <v>6720792</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5664,7 +5691,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124374694</v>
+        <v>124374757</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5707,10 +5734,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467218</v>
+        <v>467204</v>
       </c>
       <c r="R48" t="n">
-        <v>6720814</v>
+        <v>6720836</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5770,7 +5797,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124374709</v>
+        <v>124376775</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5803,7 +5830,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -5813,10 +5844,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467216</v>
+        <v>467056</v>
       </c>
       <c r="R49" t="n">
-        <v>6720827</v>
+        <v>6720996</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5876,10 +5907,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376827</v>
+        <v>124376194</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5888,34 +5919,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5923,10 +5959,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467053</v>
+        <v>466996</v>
       </c>
       <c r="R50" t="n">
-        <v>6720938</v>
+        <v>6720894</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5986,10 +6022,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375400</v>
+        <v>124374508</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5998,39 +6034,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6038,10 +6065,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467157</v>
+        <v>467196</v>
       </c>
       <c r="R51" t="n">
-        <v>6720898</v>
+        <v>6720772</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6101,10 +6128,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124374309</v>
+        <v>124374436</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6117,35 +6144,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6153,10 +6171,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467236</v>
+        <v>467202</v>
       </c>
       <c r="R52" t="n">
-        <v>6720773</v>
+        <v>6720759</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6197,6 +6215,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6325,10 +6344,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124375270</v>
+        <v>124374620</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6341,24 +6360,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6368,10 +6391,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467180</v>
+        <v>467213</v>
       </c>
       <c r="R54" t="n">
-        <v>6720912</v>
+        <v>6720795</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6431,7 +6454,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374736</v>
+        <v>124374936</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6474,10 +6497,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467232</v>
+        <v>467173</v>
       </c>
       <c r="R55" t="n">
-        <v>6720833</v>
+        <v>6720889</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6537,10 +6560,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376089</v>
+        <v>124376808</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6549,39 +6572,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6589,10 +6607,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466904</v>
+        <v>467087</v>
       </c>
       <c r="R56" t="n">
-        <v>6720952</v>
+        <v>6720934</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6652,10 +6670,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124375650</v>
+        <v>124376910</v>
       </c>
       <c r="B57" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6668,24 +6686,28 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6695,10 +6717,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467134</v>
+        <v>467140</v>
       </c>
       <c r="R57" t="n">
-        <v>6720941</v>
+        <v>6720805</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6758,7 +6780,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375684</v>
+        <v>124375650</v>
       </c>
       <c r="B58" t="n">
         <v>78547</v>
@@ -6801,10 +6823,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467166</v>
+        <v>467134</v>
       </c>
       <c r="R58" t="n">
-        <v>6720986</v>
+        <v>6720941</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6864,7 +6886,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375482</v>
+        <v>124375783</v>
       </c>
       <c r="B59" t="n">
         <v>98101</v>
@@ -6899,7 +6921,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6916,10 +6938,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467160</v>
+        <v>467016</v>
       </c>
       <c r="R59" t="n">
-        <v>6720905</v>
+        <v>6720909</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6979,7 +7001,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376865</v>
+        <v>124376827</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7026,10 +7048,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466954</v>
+        <v>467053</v>
       </c>
       <c r="R60" t="n">
-        <v>6720913</v>
+        <v>6720938</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7089,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376031</v>
+        <v>124376794</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7101,39 +7123,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7141,10 +7158,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466944</v>
+        <v>467106</v>
       </c>
       <c r="R61" t="n">
-        <v>6720920</v>
+        <v>6720967</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7204,10 +7221,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124375436</v>
+        <v>124374678</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7216,39 +7233,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7256,10 +7264,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467164</v>
+        <v>467230</v>
       </c>
       <c r="R62" t="n">
-        <v>6720898</v>
+        <v>6720817</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7319,7 +7327,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124374570</v>
+        <v>124374922</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7362,10 +7370,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467219</v>
+        <v>467194</v>
       </c>
       <c r="R63" t="n">
-        <v>6720761</v>
+        <v>6720885</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7425,10 +7433,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376794</v>
+        <v>124376031</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7437,34 +7445,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7472,10 +7485,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467106</v>
+        <v>466944</v>
       </c>
       <c r="R64" t="n">
-        <v>6720967</v>
+        <v>6720920</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7535,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124376910</v>
+        <v>124375292</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7551,28 +7564,24 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7582,10 +7591,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467140</v>
+        <v>467160</v>
       </c>
       <c r="R65" t="n">
-        <v>6720805</v>
+        <v>6720888</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7645,10 +7654,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124374678</v>
+        <v>124375684</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7661,21 +7670,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7688,10 +7697,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467230</v>
+        <v>467166</v>
       </c>
       <c r="R66" t="n">
-        <v>6720817</v>
+        <v>6720986</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7751,10 +7760,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375596</v>
+        <v>124375713</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7763,39 +7772,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467127</v>
+        <v>467042</v>
       </c>
       <c r="R67" t="n">
-        <v>6720921</v>
+        <v>6721029</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124375132</v>
+        <v>124375118</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467184</v>
+        <v>467177</v>
       </c>
       <c r="R68" t="n">
-        <v>6720843</v>
+        <v>6720859</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7972,10 +7972,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124376923</v>
+        <v>124375621</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7988,26 +7988,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467176</v>
+        <v>467135</v>
       </c>
       <c r="R69" t="n">
-        <v>6720792</v>
+        <v>6720927</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374804</v>
+        <v>124376320</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467239</v>
+        <v>467117</v>
       </c>
       <c r="R2" t="n">
-        <v>6720849</v>
+        <v>6720888</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -785,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374570</v>
+        <v>124375140</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467219</v>
+        <v>467191</v>
       </c>
       <c r="R3" t="n">
-        <v>6720761</v>
+        <v>6720859</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376750</v>
+        <v>124375118</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,11 +920,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -938,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467146</v>
+        <v>467177</v>
       </c>
       <c r="R4" t="n">
-        <v>6721019</v>
+        <v>6720859</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375732</v>
+        <v>124374995</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,36 +1005,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467043</v>
+        <v>467162</v>
       </c>
       <c r="R5" t="n">
-        <v>6720984</v>
+        <v>6720859</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1113,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374309</v>
+        <v>124376194</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,39 +1111,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467236</v>
+        <v>466996</v>
       </c>
       <c r="R6" t="n">
-        <v>6720773</v>
+        <v>6720894</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1209,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1227,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374995</v>
+        <v>124375292</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467162</v>
+        <v>467160</v>
       </c>
       <c r="R7" t="n">
-        <v>6720859</v>
+        <v>6720888</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374951</v>
+        <v>124376031</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,30 +1332,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467182</v>
+        <v>466944</v>
       </c>
       <c r="R8" t="n">
-        <v>6720879</v>
+        <v>6720920</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1439,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376342</v>
+        <v>124375010</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,31 +1447,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467083</v>
+        <v>467143</v>
       </c>
       <c r="R9" t="n">
-        <v>6720839</v>
+        <v>6720866</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1546,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375596</v>
+        <v>124376233</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,39 +1553,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1598,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467127</v>
+        <v>467068</v>
       </c>
       <c r="R10" t="n">
-        <v>6720921</v>
+        <v>6720851</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1661,7 +1647,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124375010</v>
+        <v>124376843</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1694,7 +1680,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1704,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467143</v>
+        <v>467041</v>
       </c>
       <c r="R11" t="n">
-        <v>6720866</v>
+        <v>6720899</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1767,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376295</v>
+        <v>124375039</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1769,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,7 +1800,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467095</v>
+        <v>467157</v>
       </c>
       <c r="R12" t="n">
         <v>6720881</v>
@@ -1873,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375400</v>
+        <v>124375732</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,39 +1875,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1925,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467157</v>
+        <v>467043</v>
       </c>
       <c r="R13" t="n">
-        <v>6720898</v>
+        <v>6720984</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1988,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374845</v>
+        <v>124374804</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2000,39 +1987,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2040,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467251</v>
+        <v>467239</v>
       </c>
       <c r="R14" t="n">
-        <v>6720866</v>
+        <v>6720849</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2103,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124376046</v>
+        <v>124375684</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,39 +2097,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466941</v>
+        <v>467166</v>
       </c>
       <c r="R15" t="n">
-        <v>6720908</v>
+        <v>6720986</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2218,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375057</v>
+        <v>124375783</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,30 +2203,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2261,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467016</v>
       </c>
       <c r="R16" t="n">
-        <v>6720850</v>
+        <v>6720909</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2324,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124376762</v>
+        <v>124376089</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,34 +2318,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2371,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467043</v>
+        <v>466904</v>
       </c>
       <c r="R17" t="n">
-        <v>6721047</v>
+        <v>6720952</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2434,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124375270</v>
+        <v>124376046</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2446,30 +2433,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2477,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467180</v>
+        <v>466941</v>
       </c>
       <c r="R18" t="n">
-        <v>6720912</v>
+        <v>6720908</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2540,7 +2536,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374709</v>
+        <v>124375132</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2583,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467216</v>
+        <v>467184</v>
       </c>
       <c r="R19" t="n">
-        <v>6720827</v>
+        <v>6720843</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2646,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124376089</v>
+        <v>124374694</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,39 +2654,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2698,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466904</v>
+        <v>467218</v>
       </c>
       <c r="R20" t="n">
-        <v>6720952</v>
+        <v>6720814</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2761,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124376385</v>
+        <v>124375270</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2773,39 +2760,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2813,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467094</v>
+        <v>467180</v>
       </c>
       <c r="R21" t="n">
-        <v>6720828</v>
+        <v>6720912</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2876,7 +2854,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124374736</v>
+        <v>124376775</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2909,7 +2887,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2919,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467232</v>
+        <v>467056</v>
       </c>
       <c r="R22" t="n">
-        <v>6720833</v>
+        <v>6720996</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2982,7 +2964,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124375768</v>
+        <v>124374584</v>
       </c>
       <c r="B23" t="n">
         <v>78547</v>
@@ -3025,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467034</v>
+        <v>467197</v>
       </c>
       <c r="R23" t="n">
-        <v>6720933</v>
+        <v>6720764</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3088,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375938</v>
+        <v>124374476</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,35 +3082,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3136,10 +3113,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>466966</v>
+        <v>467209</v>
       </c>
       <c r="R24" t="n">
-        <v>6720916</v>
+        <v>6720770</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3180,6 +3157,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3198,7 +3176,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375140</v>
+        <v>124374678</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3241,10 +3219,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467191</v>
+        <v>467230</v>
       </c>
       <c r="R25" t="n">
-        <v>6720859</v>
+        <v>6720817</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3304,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374600</v>
+        <v>124374936</v>
       </c>
       <c r="B26" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,25 +3294,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3347,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467226</v>
+        <v>467173</v>
       </c>
       <c r="R26" t="n">
-        <v>6720796</v>
+        <v>6720889</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3410,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375210</v>
+        <v>124375621</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3426,24 +3404,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3453,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467193</v>
+        <v>467135</v>
       </c>
       <c r="R27" t="n">
-        <v>6720911</v>
+        <v>6720927</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3516,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124376320</v>
+        <v>124375400</v>
       </c>
       <c r="B28" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3528,30 +3510,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3559,10 +3550,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467117</v>
+        <v>467157</v>
       </c>
       <c r="R28" t="n">
-        <v>6720888</v>
+        <v>6720898</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3622,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374476</v>
+        <v>124375482</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3634,30 +3625,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467209</v>
+        <v>467160</v>
       </c>
       <c r="R29" t="n">
-        <v>6720770</v>
+        <v>6720905</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124374900</v>
+        <v>124376794</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3761,7 +3761,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3771,10 +3775,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467191</v>
+        <v>467106</v>
       </c>
       <c r="R30" t="n">
-        <v>6720901</v>
+        <v>6720967</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3834,10 +3838,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124376126</v>
+        <v>124374922</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3846,35 +3850,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3882,10 +3881,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466911</v>
+        <v>467194</v>
       </c>
       <c r="R31" t="n">
-        <v>6720956</v>
+        <v>6720885</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3926,6 +3925,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375461</v>
+        <v>124376295</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,39 +3956,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3996,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467156</v>
+        <v>467095</v>
       </c>
       <c r="R32" t="n">
-        <v>6720908</v>
+        <v>6720881</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4059,7 +4050,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374694</v>
+        <v>124374709</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4102,10 +4093,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467218</v>
+        <v>467216</v>
       </c>
       <c r="R33" t="n">
-        <v>6720814</v>
+        <v>6720827</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4165,7 +4156,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374553</v>
+        <v>124376762</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4198,7 +4189,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4208,10 +4203,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467224</v>
+        <v>467043</v>
       </c>
       <c r="R34" t="n">
-        <v>6720768</v>
+        <v>6721047</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4271,7 +4266,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374964</v>
+        <v>124374951</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467169</v>
+        <v>467182</v>
       </c>
       <c r="R35" t="n">
-        <v>6720904</v>
+        <v>6720879</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4377,10 +4372,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124376233</v>
+        <v>124374570</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4389,25 +4384,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4420,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467068</v>
+        <v>467219</v>
       </c>
       <c r="R36" t="n">
-        <v>6720851</v>
+        <v>6720761</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4483,7 +4478,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124375106</v>
+        <v>124374436</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4526,10 +4521,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467167</v>
+        <v>467202</v>
       </c>
       <c r="R37" t="n">
-        <v>6720870</v>
+        <v>6720759</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4589,10 +4584,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124375039</v>
+        <v>124375938</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4601,30 +4596,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467157</v>
+        <v>466966</v>
       </c>
       <c r="R38" t="n">
-        <v>6720881</v>
+        <v>6720916</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4676,7 +4676,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4695,10 +4694,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124375482</v>
+        <v>124374757</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4707,39 +4706,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4747,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467160</v>
+        <v>467204</v>
       </c>
       <c r="R39" t="n">
-        <v>6720905</v>
+        <v>6720836</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4810,10 +4800,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375752</v>
+        <v>124374964</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4822,36 +4812,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4859,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467047</v>
+        <v>467169</v>
       </c>
       <c r="R40" t="n">
-        <v>6720974</v>
+        <v>6720904</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4922,7 +4906,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375436</v>
+        <v>124375596</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4957,7 +4941,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4974,10 +4958,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467164</v>
+        <v>467127</v>
       </c>
       <c r="R41" t="n">
-        <v>6720898</v>
+        <v>6720921</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5037,10 +5021,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124374584</v>
+        <v>124374900</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5053,21 +5037,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5080,10 +5064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467197</v>
+        <v>467191</v>
       </c>
       <c r="R42" t="n">
-        <v>6720764</v>
+        <v>6720901</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5143,10 +5127,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376865</v>
+        <v>124376270</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5155,34 +5139,36 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5190,10 +5176,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466954</v>
+        <v>467075</v>
       </c>
       <c r="R43" t="n">
-        <v>6720913</v>
+        <v>6720892</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5363,10 +5349,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124376270</v>
+        <v>124374553</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5375,36 +5361,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5412,10 +5392,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467075</v>
+        <v>467224</v>
       </c>
       <c r="R45" t="n">
-        <v>6720892</v>
+        <v>6720768</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5475,7 +5455,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375132</v>
+        <v>124376808</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5508,7 +5488,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5518,10 +5502,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467184</v>
+        <v>467087</v>
       </c>
       <c r="R46" t="n">
-        <v>6720843</v>
+        <v>6720934</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5581,10 +5565,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124376923</v>
+        <v>124374620</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5597,26 +5581,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -5628,10 +5612,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467176</v>
+        <v>467213</v>
       </c>
       <c r="R47" t="n">
-        <v>6720792</v>
+        <v>6720795</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5691,10 +5675,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124374757</v>
+        <v>124376342</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5703,30 +5687,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5734,10 +5719,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467204</v>
+        <v>467083</v>
       </c>
       <c r="R48" t="n">
-        <v>6720836</v>
+        <v>6720839</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5797,10 +5782,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376775</v>
+        <v>124374600</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5809,32 +5794,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -5844,10 +5825,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467056</v>
+        <v>467226</v>
       </c>
       <c r="R49" t="n">
-        <v>6720996</v>
+        <v>6720796</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5907,10 +5888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376194</v>
+        <v>124375210</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5919,39 +5900,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5959,10 +5931,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466996</v>
+        <v>467193</v>
       </c>
       <c r="R50" t="n">
-        <v>6720894</v>
+        <v>6720911</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6022,7 +5994,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124374508</v>
+        <v>124376750</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6055,7 +6027,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -6065,10 +6041,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467196</v>
+        <v>467146</v>
       </c>
       <c r="R51" t="n">
-        <v>6720772</v>
+        <v>6721019</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6128,10 +6104,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124374436</v>
+        <v>124375713</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6144,21 +6120,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6171,10 +6147,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467202</v>
+        <v>467042</v>
       </c>
       <c r="R52" t="n">
-        <v>6720759</v>
+        <v>6721029</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6234,10 +6210,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124376843</v>
+        <v>124374845</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6246,34 +6222,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6281,10 +6262,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467041</v>
+        <v>467251</v>
       </c>
       <c r="R53" t="n">
-        <v>6720899</v>
+        <v>6720866</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6344,10 +6325,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374620</v>
+        <v>124376923</v>
       </c>
       <c r="B54" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6360,26 +6341,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6391,10 +6372,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467213</v>
+        <v>467176</v>
       </c>
       <c r="R54" t="n">
-        <v>6720795</v>
+        <v>6720792</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6454,10 +6435,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374936</v>
+        <v>124375650</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6470,21 +6451,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6497,10 +6478,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467173</v>
+        <v>467134</v>
       </c>
       <c r="R55" t="n">
-        <v>6720889</v>
+        <v>6720941</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6560,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376808</v>
+        <v>124375768</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6576,28 +6557,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6607,10 +6584,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467087</v>
+        <v>467034</v>
       </c>
       <c r="R56" t="n">
-        <v>6720934</v>
+        <v>6720933</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6670,10 +6647,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124376910</v>
+        <v>124375461</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6682,34 +6659,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6717,10 +6699,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R57" t="n">
-        <v>6720805</v>
+        <v>6720908</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6780,10 +6762,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375650</v>
+        <v>124374736</v>
       </c>
       <c r="B58" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6796,21 +6778,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6823,10 +6805,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467134</v>
+        <v>467232</v>
       </c>
       <c r="R58" t="n">
-        <v>6720941</v>
+        <v>6720833</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6886,10 +6868,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375783</v>
+        <v>124376827</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6898,39 +6880,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6938,10 +6915,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467016</v>
+        <v>467053</v>
       </c>
       <c r="R59" t="n">
-        <v>6720909</v>
+        <v>6720938</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7001,10 +6978,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376827</v>
+        <v>124375752</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7013,34 +6990,36 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7048,10 +7027,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467053</v>
+        <v>467047</v>
       </c>
       <c r="R60" t="n">
-        <v>6720938</v>
+        <v>6720974</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7111,10 +7090,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376794</v>
+        <v>124376385</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7123,34 +7102,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7158,10 +7142,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467106</v>
+        <v>467094</v>
       </c>
       <c r="R61" t="n">
-        <v>6720967</v>
+        <v>6720828</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7221,10 +7205,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124374678</v>
+        <v>124374309</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7237,26 +7221,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7264,10 +7257,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467230</v>
+        <v>467236</v>
       </c>
       <c r="R62" t="n">
-        <v>6720817</v>
+        <v>6720773</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7308,7 +7301,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7327,10 +7319,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124374922</v>
+        <v>124375436</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7339,30 +7331,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7370,10 +7371,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467194</v>
+        <v>467164</v>
       </c>
       <c r="R63" t="n">
-        <v>6720885</v>
+        <v>6720898</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7433,10 +7434,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376031</v>
+        <v>124376865</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7445,39 +7446,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7485,10 +7481,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466944</v>
+        <v>466954</v>
       </c>
       <c r="R64" t="n">
-        <v>6720920</v>
+        <v>6720913</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7548,10 +7544,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124375292</v>
+        <v>124374508</v>
       </c>
       <c r="B65" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7564,21 +7560,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7591,10 +7587,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467160</v>
+        <v>467196</v>
       </c>
       <c r="R65" t="n">
-        <v>6720888</v>
+        <v>6720772</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7654,10 +7650,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124375684</v>
+        <v>124375057</v>
       </c>
       <c r="B66" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7670,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7697,10 +7693,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467166</v>
+        <v>467156</v>
       </c>
       <c r="R66" t="n">
-        <v>6720986</v>
+        <v>6720850</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7760,10 +7756,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375713</v>
+        <v>124376910</v>
       </c>
       <c r="B67" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7776,24 +7772,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467042</v>
+        <v>467140</v>
       </c>
       <c r="R67" t="n">
-        <v>6721029</v>
+        <v>6720805</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124375118</v>
+        <v>124375106</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467177</v>
+        <v>467167</v>
       </c>
       <c r="R68" t="n">
-        <v>6720859</v>
+        <v>6720870</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7972,10 +7972,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124375621</v>
+        <v>124376126</v>
       </c>
       <c r="B69" t="n">
-        <v>91032</v>
+        <v>56722</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7984,34 +7984,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8020,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467135</v>
+        <v>466911</v>
       </c>
       <c r="R69" t="n">
-        <v>6720927</v>
+        <v>6720956</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8063,7 +8064,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -3070,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124374476</v>
+        <v>124375400</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,30 +3082,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3113,10 +3122,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467209</v>
+        <v>467157</v>
       </c>
       <c r="R24" t="n">
-        <v>6720770</v>
+        <v>6720898</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3176,10 +3185,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374678</v>
+        <v>124375482</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3188,30 +3197,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3219,10 +3237,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467230</v>
+        <v>467160</v>
       </c>
       <c r="R25" t="n">
-        <v>6720817</v>
+        <v>6720905</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3282,7 +3300,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374936</v>
+        <v>124374476</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3325,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467173</v>
+        <v>467209</v>
       </c>
       <c r="R26" t="n">
-        <v>6720889</v>
+        <v>6720770</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3388,10 +3406,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375621</v>
+        <v>124374678</v>
       </c>
       <c r="B27" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,28 +3422,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3435,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467135</v>
+        <v>467230</v>
       </c>
       <c r="R27" t="n">
-        <v>6720927</v>
+        <v>6720817</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3498,10 +3512,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375400</v>
+        <v>124374936</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,39 +3524,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3550,10 +3555,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467157</v>
+        <v>467173</v>
       </c>
       <c r="R28" t="n">
-        <v>6720898</v>
+        <v>6720889</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3613,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375482</v>
+        <v>124375621</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3625,39 +3630,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467160</v>
+        <v>467135</v>
       </c>
       <c r="R29" t="n">
-        <v>6720905</v>
+        <v>6720927</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124374600</v>
+        <v>124375210</v>
       </c>
       <c r="B49" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5794,25 +5794,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467226</v>
+        <v>467193</v>
       </c>
       <c r="R49" t="n">
-        <v>6720796</v>
+        <v>6720911</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5888,7 +5888,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375210</v>
+        <v>124376750</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5921,7 +5921,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5931,10 +5935,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467193</v>
+        <v>467146</v>
       </c>
       <c r="R50" t="n">
-        <v>6720911</v>
+        <v>6721019</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5994,10 +5998,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124376750</v>
+        <v>124374600</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6006,32 +6010,28 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467146</v>
+        <v>467226</v>
       </c>
       <c r="R51" t="n">
-        <v>6721019</v>
+        <v>6720796</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375713</v>
+        <v>124374845</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,30 +6116,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6147,10 +6156,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467042</v>
+        <v>467251</v>
       </c>
       <c r="R52" t="n">
-        <v>6721029</v>
+        <v>6720866</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6210,10 +6219,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124374845</v>
+        <v>124375713</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6222,39 +6231,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6262,10 +6262,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467251</v>
+        <v>467042</v>
       </c>
       <c r="R53" t="n">
-        <v>6720866</v>
+        <v>6721029</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376320</v>
+        <v>124375752</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>8447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467117</v>
+        <v>467047</v>
       </c>
       <c r="R2" t="n">
-        <v>6720888</v>
+        <v>6720974</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375140</v>
+        <v>124375621</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,24 +803,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467191</v>
+        <v>467135</v>
       </c>
       <c r="R3" t="n">
-        <v>6720859</v>
+        <v>6720927</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375118</v>
+        <v>124374951</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -930,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467177</v>
+        <v>467182</v>
       </c>
       <c r="R4" t="n">
-        <v>6720859</v>
+        <v>6720879</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374995</v>
+        <v>124376126</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,30 +1015,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467162</v>
+        <v>466911</v>
       </c>
       <c r="R5" t="n">
-        <v>6720859</v>
+        <v>6720956</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1080,7 +1095,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376194</v>
+        <v>124375482</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1134,7 +1148,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1151,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466996</v>
+        <v>467160</v>
       </c>
       <c r="R6" t="n">
-        <v>6720894</v>
+        <v>6720905</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1214,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124375292</v>
+        <v>124374620</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,24 +1244,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1257,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467160</v>
+        <v>467213</v>
       </c>
       <c r="R7" t="n">
-        <v>6720888</v>
+        <v>6720795</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1320,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124376031</v>
+        <v>124375783</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1355,7 +1373,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1372,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466944</v>
+        <v>467016</v>
       </c>
       <c r="R8" t="n">
-        <v>6720920</v>
+        <v>6720909</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1435,7 +1453,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124375010</v>
+        <v>124374964</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1478,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467143</v>
+        <v>467169</v>
       </c>
       <c r="R9" t="n">
-        <v>6720866</v>
+        <v>6720904</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1541,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124376233</v>
+        <v>124376750</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,28 +1571,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1584,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467068</v>
+        <v>467146</v>
       </c>
       <c r="R10" t="n">
-        <v>6720851</v>
+        <v>6721019</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1647,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124376843</v>
+        <v>124376923</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1682,7 +1704,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1694,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467041</v>
+        <v>467176</v>
       </c>
       <c r="R11" t="n">
-        <v>6720899</v>
+        <v>6720792</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1757,7 +1779,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375039</v>
+        <v>124376808</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1790,7 +1812,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1800,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467157</v>
+        <v>467087</v>
       </c>
       <c r="R12" t="n">
-        <v>6720881</v>
+        <v>6720934</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1863,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375732</v>
+        <v>124376794</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,36 +1901,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467043</v>
+        <v>467106</v>
       </c>
       <c r="R13" t="n">
-        <v>6720984</v>
+        <v>6720967</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1975,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374804</v>
+        <v>124375270</v>
       </c>
       <c r="B14" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,28 +2015,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2022,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467239</v>
+        <v>467180</v>
       </c>
       <c r="R14" t="n">
-        <v>6720849</v>
+        <v>6720912</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2085,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375684</v>
+        <v>124375106</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,21 +2121,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2148,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467166</v>
+        <v>467167</v>
       </c>
       <c r="R15" t="n">
-        <v>6720986</v>
+        <v>6720870</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2191,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375783</v>
+        <v>124375684</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,39 +2223,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2243,10 +2254,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467016</v>
+        <v>467166</v>
       </c>
       <c r="R16" t="n">
-        <v>6720909</v>
+        <v>6720986</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2306,7 +2317,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124376089</v>
+        <v>124375596</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2341,7 +2352,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2358,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466904</v>
+        <v>467127</v>
       </c>
       <c r="R17" t="n">
-        <v>6720952</v>
+        <v>6720921</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2421,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376046</v>
+        <v>124376889</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,39 +2444,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2473,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466941</v>
+        <v>467053</v>
       </c>
       <c r="R18" t="n">
-        <v>6720908</v>
+        <v>6720874</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2536,7 +2542,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375132</v>
+        <v>124374736</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2579,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467184</v>
+        <v>467232</v>
       </c>
       <c r="R19" t="n">
-        <v>6720843</v>
+        <v>6720833</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2642,10 +2648,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124374694</v>
+        <v>124374309</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,26 +2664,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2685,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467218</v>
+        <v>467236</v>
       </c>
       <c r="R20" t="n">
-        <v>6720814</v>
+        <v>6720773</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2729,7 +2744,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2748,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375270</v>
+        <v>124375732</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,30 +2774,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2791,10 +2811,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467180</v>
+        <v>467043</v>
       </c>
       <c r="R21" t="n">
-        <v>6720912</v>
+        <v>6720984</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2854,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376775</v>
+        <v>124374584</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,28 +2890,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2901,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467056</v>
+        <v>467197</v>
       </c>
       <c r="R22" t="n">
-        <v>6720996</v>
+        <v>6720764</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2964,10 +2980,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374584</v>
+        <v>124374694</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,21 +2996,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3007,10 +3023,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467197</v>
+        <v>467218</v>
       </c>
       <c r="R23" t="n">
-        <v>6720764</v>
+        <v>6720814</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3070,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375400</v>
+        <v>124375118</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,39 +3098,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3122,10 +3129,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467157</v>
+        <v>467177</v>
       </c>
       <c r="R24" t="n">
-        <v>6720898</v>
+        <v>6720859</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3185,10 +3192,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375482</v>
+        <v>124375057</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3197,39 +3204,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3237,10 +3235,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467160</v>
+        <v>467156</v>
       </c>
       <c r="R25" t="n">
-        <v>6720905</v>
+        <v>6720850</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3300,10 +3298,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374476</v>
+        <v>124376295</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3312,25 +3310,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3341,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467209</v>
+        <v>467095</v>
       </c>
       <c r="R26" t="n">
-        <v>6720770</v>
+        <v>6720881</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3406,7 +3404,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124374678</v>
+        <v>124374508</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3449,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467230</v>
+        <v>467196</v>
       </c>
       <c r="R27" t="n">
-        <v>6720817</v>
+        <v>6720772</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3512,10 +3510,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374936</v>
+        <v>124376046</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3524,30 +3522,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3555,10 +3562,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467173</v>
+        <v>466941</v>
       </c>
       <c r="R28" t="n">
-        <v>6720889</v>
+        <v>6720908</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3618,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375621</v>
+        <v>124374995</v>
       </c>
       <c r="B29" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3634,28 +3641,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3665,10 +3668,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467135</v>
+        <v>467162</v>
       </c>
       <c r="R29" t="n">
-        <v>6720927</v>
+        <v>6720859</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3728,7 +3731,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124376794</v>
+        <v>124374436</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3761,11 +3764,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3775,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467106</v>
+        <v>467202</v>
       </c>
       <c r="R30" t="n">
-        <v>6720967</v>
+        <v>6720759</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3838,10 +3837,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124374922</v>
+        <v>124376342</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3850,30 +3849,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467194</v>
+        <v>467083</v>
       </c>
       <c r="R31" t="n">
-        <v>6720885</v>
+        <v>6720839</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124376295</v>
+        <v>124375768</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>78547</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467095</v>
+        <v>467034</v>
       </c>
       <c r="R32" t="n">
-        <v>6720881</v>
+        <v>6720933</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374709</v>
+        <v>124375461</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,30 +4062,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4093,10 +4102,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467216</v>
+        <v>467156</v>
       </c>
       <c r="R33" t="n">
-        <v>6720827</v>
+        <v>6720908</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4156,7 +4165,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124376762</v>
+        <v>124376865</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4203,10 +4212,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467043</v>
+        <v>466954</v>
       </c>
       <c r="R34" t="n">
-        <v>6721047</v>
+        <v>6720913</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4266,7 +4275,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374951</v>
+        <v>124374476</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4309,10 +4318,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467182</v>
+        <v>467209</v>
       </c>
       <c r="R35" t="n">
-        <v>6720879</v>
+        <v>6720770</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4372,7 +4381,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374570</v>
+        <v>124374757</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4415,10 +4424,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467219</v>
+        <v>467204</v>
       </c>
       <c r="R36" t="n">
-        <v>6720761</v>
+        <v>6720836</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4478,7 +4487,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374436</v>
+        <v>124376827</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4511,7 +4520,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4521,10 +4534,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467202</v>
+        <v>467053</v>
       </c>
       <c r="R37" t="n">
-        <v>6720759</v>
+        <v>6720938</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4584,10 +4597,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124375938</v>
+        <v>124375210</v>
       </c>
       <c r="B38" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4596,35 +4609,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4632,10 +4640,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466966</v>
+        <v>467193</v>
       </c>
       <c r="R38" t="n">
-        <v>6720916</v>
+        <v>6720911</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4676,6 +4684,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4694,10 +4703,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124374757</v>
+        <v>124376385</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4706,30 +4715,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4737,10 +4755,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467204</v>
+        <v>467094</v>
       </c>
       <c r="R39" t="n">
-        <v>6720836</v>
+        <v>6720828</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4800,7 +4818,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124374964</v>
+        <v>124376843</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4833,7 +4851,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4843,10 +4865,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467169</v>
+        <v>467041</v>
       </c>
       <c r="R40" t="n">
-        <v>6720904</v>
+        <v>6720899</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4906,10 +4928,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375596</v>
+        <v>124374570</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4918,39 +4940,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4958,10 +4971,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467127</v>
+        <v>467219</v>
       </c>
       <c r="R41" t="n">
-        <v>6720921</v>
+        <v>6720761</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5021,7 +5034,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124374900</v>
+        <v>124376775</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5054,7 +5067,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5064,10 +5081,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467191</v>
+        <v>467056</v>
       </c>
       <c r="R42" t="n">
-        <v>6720901</v>
+        <v>6720996</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5127,10 +5144,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376270</v>
+        <v>124376089</v>
       </c>
       <c r="B43" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5139,36 +5156,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5176,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467075</v>
+        <v>466904</v>
       </c>
       <c r="R43" t="n">
-        <v>6720892</v>
+        <v>6720952</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5239,7 +5259,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124376889</v>
+        <v>124375039</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5272,11 +5292,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5286,10 +5302,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467053</v>
+        <v>467157</v>
       </c>
       <c r="R44" t="n">
-        <v>6720874</v>
+        <v>6720881</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5349,10 +5365,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374553</v>
+        <v>124376270</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5361,30 +5377,36 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5392,10 +5414,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467224</v>
+        <v>467075</v>
       </c>
       <c r="R45" t="n">
-        <v>6720768</v>
+        <v>6720892</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5455,10 +5477,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124376808</v>
+        <v>124375650</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5471,28 +5493,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
@@ -5502,10 +5520,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467087</v>
+        <v>467134</v>
       </c>
       <c r="R46" t="n">
-        <v>6720934</v>
+        <v>6720941</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5565,10 +5583,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374620</v>
+        <v>124375132</v>
       </c>
       <c r="B47" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5581,28 +5599,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5612,10 +5626,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467213</v>
+        <v>467184</v>
       </c>
       <c r="R47" t="n">
-        <v>6720795</v>
+        <v>6720843</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5675,10 +5689,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124376342</v>
+        <v>124376910</v>
       </c>
       <c r="B48" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5687,31 +5701,34 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5719,10 +5736,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467083</v>
+        <v>467140</v>
       </c>
       <c r="R48" t="n">
-        <v>6720839</v>
+        <v>6720805</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5782,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124375210</v>
+        <v>124375938</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5794,30 +5811,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5825,10 +5847,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467193</v>
+        <v>466966</v>
       </c>
       <c r="R49" t="n">
-        <v>6720911</v>
+        <v>6720916</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5869,7 +5891,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5888,10 +5909,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376750</v>
+        <v>124375713</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5904,28 +5925,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5935,10 +5952,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467146</v>
+        <v>467042</v>
       </c>
       <c r="R50" t="n">
-        <v>6721019</v>
+        <v>6721029</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6104,10 +6121,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124374845</v>
+        <v>124375010</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6116,39 +6133,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6156,7 +6164,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467251</v>
+        <v>467143</v>
       </c>
       <c r="R52" t="n">
         <v>6720866</v>
@@ -6219,10 +6227,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124375713</v>
+        <v>124376762</v>
       </c>
       <c r="B53" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6235,24 +6243,28 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6262,10 +6274,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467042</v>
+        <v>467043</v>
       </c>
       <c r="R53" t="n">
-        <v>6721029</v>
+        <v>6721047</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6325,7 +6337,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124376923</v>
+        <v>124374709</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6358,11 +6370,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6372,10 +6380,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467176</v>
+        <v>467216</v>
       </c>
       <c r="R54" t="n">
-        <v>6720792</v>
+        <v>6720827</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6435,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124375650</v>
+        <v>124374804</v>
       </c>
       <c r="B55" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6451,24 +6459,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6478,10 +6490,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467134</v>
+        <v>467239</v>
       </c>
       <c r="R55" t="n">
-        <v>6720941</v>
+        <v>6720849</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6541,10 +6553,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124375768</v>
+        <v>124374845</v>
       </c>
       <c r="B56" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6553,30 +6565,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6584,10 +6605,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467034</v>
+        <v>467251</v>
       </c>
       <c r="R56" t="n">
-        <v>6720933</v>
+        <v>6720866</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6647,10 +6668,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124375461</v>
+        <v>124374553</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6659,39 +6680,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6699,10 +6711,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467156</v>
+        <v>467224</v>
       </c>
       <c r="R57" t="n">
-        <v>6720908</v>
+        <v>6720768</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6762,7 +6774,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124374736</v>
+        <v>124375140</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6805,10 +6817,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467232</v>
+        <v>467191</v>
       </c>
       <c r="R58" t="n">
-        <v>6720833</v>
+        <v>6720859</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6868,10 +6880,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124376827</v>
+        <v>124375292</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6884,28 +6896,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -6915,10 +6923,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467053</v>
+        <v>467160</v>
       </c>
       <c r="R59" t="n">
-        <v>6720938</v>
+        <v>6720888</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6978,10 +6986,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124375752</v>
+        <v>124375436</v>
       </c>
       <c r="B60" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6990,36 +6998,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7027,10 +7038,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467047</v>
+        <v>467164</v>
       </c>
       <c r="R60" t="n">
-        <v>6720974</v>
+        <v>6720898</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7090,10 +7101,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376385</v>
+        <v>124376233</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7102,39 +7113,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7142,10 +7144,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467094</v>
+        <v>467068</v>
       </c>
       <c r="R61" t="n">
-        <v>6720828</v>
+        <v>6720851</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7205,10 +7207,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124374309</v>
+        <v>124376320</v>
       </c>
       <c r="B62" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7221,35 +7223,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7257,10 +7250,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467236</v>
+        <v>467117</v>
       </c>
       <c r="R62" t="n">
-        <v>6720773</v>
+        <v>6720888</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7301,6 +7294,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7319,10 +7313,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124375436</v>
+        <v>124374678</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7331,39 +7325,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7371,10 +7356,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467164</v>
+        <v>467230</v>
       </c>
       <c r="R63" t="n">
-        <v>6720898</v>
+        <v>6720817</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7434,7 +7419,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376865</v>
+        <v>124374900</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7467,11 +7452,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -7481,10 +7462,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466954</v>
+        <v>467191</v>
       </c>
       <c r="R64" t="n">
-        <v>6720913</v>
+        <v>6720901</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7544,7 +7525,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124374508</v>
+        <v>124374922</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7587,10 +7568,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467196</v>
+        <v>467194</v>
       </c>
       <c r="R65" t="n">
-        <v>6720772</v>
+        <v>6720885</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7650,7 +7631,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124375057</v>
+        <v>124374936</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7693,10 +7674,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467156</v>
+        <v>467173</v>
       </c>
       <c r="R66" t="n">
-        <v>6720850</v>
+        <v>6720889</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7756,10 +7737,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124376910</v>
+        <v>124376031</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7768,34 +7749,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7803,10 +7789,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467140</v>
+        <v>466944</v>
       </c>
       <c r="R67" t="n">
-        <v>6720805</v>
+        <v>6720920</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7866,10 +7852,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124375106</v>
+        <v>124376194</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7878,30 +7864,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7909,10 +7904,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467167</v>
+        <v>466996</v>
       </c>
       <c r="R68" t="n">
-        <v>6720870</v>
+        <v>6720894</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7972,10 +7967,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124376126</v>
+        <v>124375400</v>
       </c>
       <c r="B69" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7984,35 +7979,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8020,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466911</v>
+        <v>467157</v>
       </c>
       <c r="R69" t="n">
-        <v>6720956</v>
+        <v>6720898</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8064,6 +8063,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -2211,10 +2211,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375684</v>
+        <v>124375596</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,30 +2223,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2254,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467166</v>
+        <v>467127</v>
       </c>
       <c r="R16" t="n">
-        <v>6720986</v>
+        <v>6720921</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2317,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375596</v>
+        <v>124375684</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2329,39 +2338,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467127</v>
+        <v>467166</v>
       </c>
       <c r="R17" t="n">
-        <v>6720921</v>
+        <v>6720986</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376889</v>
+        <v>124374584</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,28 +2448,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2479,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467053</v>
+        <v>467197</v>
       </c>
       <c r="R18" t="n">
-        <v>6720874</v>
+        <v>6720764</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2542,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374736</v>
+        <v>124374309</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,26 +2554,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2585,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467232</v>
+        <v>467236</v>
       </c>
       <c r="R19" t="n">
-        <v>6720833</v>
+        <v>6720773</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2629,7 +2634,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2648,10 +2652,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124374309</v>
+        <v>124376889</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2664,35 +2668,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2700,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467236</v>
+        <v>467053</v>
       </c>
       <c r="R20" t="n">
-        <v>6720773</v>
+        <v>6720874</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2744,6 +2743,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375732</v>
+        <v>124374736</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,36 +2774,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2811,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467043</v>
+        <v>467232</v>
       </c>
       <c r="R21" t="n">
-        <v>6720984</v>
+        <v>6720833</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2874,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124374584</v>
+        <v>124375732</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,30 +2880,36 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467197</v>
+        <v>467043</v>
       </c>
       <c r="R22" t="n">
-        <v>6720764</v>
+        <v>6720984</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124374508</v>
+        <v>124376046</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3416,30 +3416,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3447,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467196</v>
+        <v>466941</v>
       </c>
       <c r="R27" t="n">
-        <v>6720772</v>
+        <v>6720908</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3510,10 +3519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124376046</v>
+        <v>124374508</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3522,39 +3531,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466941</v>
+        <v>467196</v>
       </c>
       <c r="R28" t="n">
-        <v>6720908</v>
+        <v>6720772</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375132</v>
+        <v>124375938</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5595,30 +5595,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467184</v>
+        <v>466966</v>
       </c>
       <c r="R47" t="n">
-        <v>6720843</v>
+        <v>6720916</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5670,7 +5675,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5689,7 +5693,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124376910</v>
+        <v>124375132</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5722,11 +5726,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467140</v>
+        <v>467184</v>
       </c>
       <c r="R48" t="n">
-        <v>6720805</v>
+        <v>6720843</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124375938</v>
+        <v>124376910</v>
       </c>
       <c r="B49" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5811,35 +5811,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5847,10 +5846,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466966</v>
+        <v>467140</v>
       </c>
       <c r="R49" t="n">
-        <v>6720916</v>
+        <v>6720805</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5891,6 +5890,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6015,10 +6015,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124374600</v>
+        <v>124375010</v>
       </c>
       <c r="B51" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6027,25 +6027,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6058,10 +6058,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467226</v>
+        <v>467143</v>
       </c>
       <c r="R51" t="n">
-        <v>6720796</v>
+        <v>6720866</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6121,7 +6121,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375010</v>
+        <v>124376762</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6154,7 +6154,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6164,10 +6168,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467143</v>
+        <v>467043</v>
       </c>
       <c r="R52" t="n">
-        <v>6720866</v>
+        <v>6721047</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6227,7 +6231,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124376762</v>
+        <v>124374709</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6260,11 +6264,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467043</v>
+        <v>467216</v>
       </c>
       <c r="R53" t="n">
-        <v>6721047</v>
+        <v>6720827</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6337,10 +6337,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374709</v>
+        <v>124374600</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6349,25 +6349,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467216</v>
+        <v>467226</v>
       </c>
       <c r="R54" t="n">
-        <v>6720827</v>
+        <v>6720796</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -7101,10 +7101,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376233</v>
+        <v>124376320</v>
       </c>
       <c r="B61" t="n">
-        <v>90977</v>
+        <v>78546</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7113,25 +7113,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7144,10 +7144,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467068</v>
+        <v>467117</v>
       </c>
       <c r="R61" t="n">
-        <v>6720851</v>
+        <v>6720888</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7207,10 +7207,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376320</v>
+        <v>124374678</v>
       </c>
       <c r="B62" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7223,21 +7223,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467117</v>
+        <v>467230</v>
       </c>
       <c r="R62" t="n">
-        <v>6720888</v>
+        <v>6720817</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124374678</v>
+        <v>124376233</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7325,25 +7325,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467230</v>
+        <v>467068</v>
       </c>
       <c r="R63" t="n">
-        <v>6720817</v>
+        <v>6720851</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124375752</v>
+        <v>124374951</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467047</v>
+        <v>467182</v>
       </c>
       <c r="R2" t="n">
-        <v>6720974</v>
+        <v>6720879</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -897,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374951</v>
+        <v>124375752</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +903,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467182</v>
+        <v>467047</v>
       </c>
       <c r="R4" t="n">
-        <v>6720879</v>
+        <v>6720974</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374995</v>
+        <v>124375461</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3637,30 +3637,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3668,10 +3677,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467162</v>
+        <v>467156</v>
       </c>
       <c r="R29" t="n">
-        <v>6720859</v>
+        <v>6720908</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3731,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124374436</v>
+        <v>124375768</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3747,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3774,10 +3783,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467202</v>
+        <v>467034</v>
       </c>
       <c r="R30" t="n">
-        <v>6720759</v>
+        <v>6720933</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3837,10 +3846,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124376342</v>
+        <v>124374995</v>
       </c>
       <c r="B31" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3849,31 +3858,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3881,10 +3889,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467083</v>
+        <v>467162</v>
       </c>
       <c r="R31" t="n">
-        <v>6720839</v>
+        <v>6720859</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3944,10 +3952,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375768</v>
+        <v>124374436</v>
       </c>
       <c r="B32" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,21 +3968,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3987,10 +3995,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467034</v>
+        <v>467202</v>
       </c>
       <c r="R32" t="n">
-        <v>6720933</v>
+        <v>6720759</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4050,10 +4058,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124375461</v>
+        <v>124376342</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,37 +4070,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467156</v>
+        <v>467083</v>
       </c>
       <c r="R33" t="n">
-        <v>6720908</v>
+        <v>6720839</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124376270</v>
+        <v>124375650</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5377,36 +5377,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5414,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467075</v>
+        <v>467134</v>
       </c>
       <c r="R45" t="n">
-        <v>6720892</v>
+        <v>6720941</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5477,10 +5471,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375650</v>
+        <v>124376270</v>
       </c>
       <c r="B46" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5489,30 +5483,36 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467134</v>
+        <v>467075</v>
       </c>
       <c r="R46" t="n">
-        <v>6720941</v>
+        <v>6720892</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374951</v>
+        <v>124376320</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467182</v>
+        <v>467117</v>
       </c>
       <c r="R2" t="n">
-        <v>6720879</v>
+        <v>6720888</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375621</v>
+        <v>124374620</v>
       </c>
       <c r="B3" t="n">
         <v>91032</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467135</v>
+        <v>467213</v>
       </c>
       <c r="R3" t="n">
-        <v>6720927</v>
+        <v>6720795</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375752</v>
+        <v>124376270</v>
       </c>
       <c r="B4" t="n">
         <v>8447</v>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467047</v>
+        <v>467075</v>
       </c>
       <c r="R4" t="n">
-        <v>6720974</v>
+        <v>6720892</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376126</v>
+        <v>124375783</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,35 +1015,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466911</v>
+        <v>467016</v>
       </c>
       <c r="R5" t="n">
-        <v>6720956</v>
+        <v>6720909</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1095,6 +1099,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124375482</v>
+        <v>124374678</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,39 +1130,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467160</v>
+        <v>467230</v>
       </c>
       <c r="R6" t="n">
-        <v>6720905</v>
+        <v>6720817</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374620</v>
+        <v>124374309</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1266,8 +1262,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467213</v>
+        <v>467236</v>
       </c>
       <c r="R7" t="n">
-        <v>6720795</v>
+        <v>6720773</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1319,7 +1320,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124375783</v>
+        <v>124374845</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467016</v>
+        <v>467251</v>
       </c>
       <c r="R8" t="n">
-        <v>6720909</v>
+        <v>6720866</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1453,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124374964</v>
+        <v>124375482</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,30 +1465,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1496,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467169</v>
+        <v>467160</v>
       </c>
       <c r="R9" t="n">
-        <v>6720904</v>
+        <v>6720905</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1559,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124376750</v>
+        <v>124375596</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,34 +1580,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1606,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467146</v>
+        <v>467127</v>
       </c>
       <c r="R10" t="n">
-        <v>6721019</v>
+        <v>6720921</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1669,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124376923</v>
+        <v>124376342</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,34 +1695,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1716,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467176</v>
+        <v>467083</v>
       </c>
       <c r="R11" t="n">
-        <v>6720792</v>
+        <v>6720839</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1779,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376808</v>
+        <v>124375768</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,28 +1806,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1826,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467087</v>
+        <v>467034</v>
       </c>
       <c r="R12" t="n">
-        <v>6720934</v>
+        <v>6720933</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1889,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124376794</v>
+        <v>124376046</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,34 +1908,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1936,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467106</v>
+        <v>466941</v>
       </c>
       <c r="R13" t="n">
-        <v>6720967</v>
+        <v>6720908</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1999,7 +2011,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375270</v>
+        <v>124375106</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2042,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467180</v>
+        <v>467167</v>
       </c>
       <c r="R14" t="n">
-        <v>6720912</v>
+        <v>6720870</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2105,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375106</v>
+        <v>124374553</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2148,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467167</v>
+        <v>467224</v>
       </c>
       <c r="R15" t="n">
-        <v>6720870</v>
+        <v>6720768</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2211,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375596</v>
+        <v>124376910</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,39 +2235,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2263,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467127</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6720921</v>
+        <v>6720805</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2326,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375684</v>
+        <v>124374709</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2349,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2369,10 +2376,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467166</v>
+        <v>467216</v>
       </c>
       <c r="R17" t="n">
-        <v>6720986</v>
+        <v>6720827</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2432,10 +2439,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124374584</v>
+        <v>124376750</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,24 +2455,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2475,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467197</v>
+        <v>467146</v>
       </c>
       <c r="R18" t="n">
-        <v>6720764</v>
+        <v>6721019</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2538,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374309</v>
+        <v>124376865</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,35 +2565,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2590,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467236</v>
+        <v>466954</v>
       </c>
       <c r="R19" t="n">
-        <v>6720773</v>
+        <v>6720913</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2634,6 +2640,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2652,10 +2659,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124376889</v>
+        <v>124375650</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,28 +2675,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2699,10 +2702,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467053</v>
+        <v>467134</v>
       </c>
       <c r="R20" t="n">
-        <v>6720874</v>
+        <v>6720941</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2762,10 +2765,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124374736</v>
+        <v>124375732</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,30 +2777,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2805,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467232</v>
+        <v>467043</v>
       </c>
       <c r="R21" t="n">
-        <v>6720833</v>
+        <v>6720984</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2868,10 +2877,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124375732</v>
+        <v>124376031</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2880,36 +2889,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2917,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467043</v>
+        <v>466944</v>
       </c>
       <c r="R22" t="n">
-        <v>6720984</v>
+        <v>6720920</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2980,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374694</v>
+        <v>124374804</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2996,24 +3008,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3023,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467218</v>
+        <v>467239</v>
       </c>
       <c r="R23" t="n">
-        <v>6720814</v>
+        <v>6720849</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3086,7 +3102,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375118</v>
+        <v>124375010</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3129,10 +3145,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467177</v>
+        <v>467143</v>
       </c>
       <c r="R24" t="n">
-        <v>6720859</v>
+        <v>6720866</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3192,7 +3208,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375057</v>
+        <v>124374436</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3235,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467156</v>
+        <v>467202</v>
       </c>
       <c r="R25" t="n">
-        <v>6720850</v>
+        <v>6720759</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3298,10 +3314,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124376295</v>
+        <v>124375436</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3310,30 +3326,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3341,10 +3366,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467095</v>
+        <v>467164</v>
       </c>
       <c r="R26" t="n">
-        <v>6720881</v>
+        <v>6720898</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3404,10 +3429,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124376046</v>
+        <v>124375132</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3416,39 +3441,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3456,10 +3472,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466941</v>
+        <v>467184</v>
       </c>
       <c r="R27" t="n">
-        <v>6720908</v>
+        <v>6720843</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3519,7 +3535,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374508</v>
+        <v>124374757</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3562,10 +3578,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467196</v>
+        <v>467204</v>
       </c>
       <c r="R28" t="n">
-        <v>6720772</v>
+        <v>6720836</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3625,10 +3641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375461</v>
+        <v>124375292</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3637,39 +3653,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3677,10 +3684,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467156</v>
+        <v>467160</v>
       </c>
       <c r="R29" t="n">
-        <v>6720908</v>
+        <v>6720888</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3740,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375768</v>
+        <v>124376089</v>
       </c>
       <c r="B30" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,30 +3759,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3783,10 +3799,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467034</v>
+        <v>466904</v>
       </c>
       <c r="R30" t="n">
-        <v>6720933</v>
+        <v>6720952</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3846,7 +3862,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124374995</v>
+        <v>124376794</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3879,7 +3895,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3889,10 +3909,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467162</v>
+        <v>467106</v>
       </c>
       <c r="R31" t="n">
-        <v>6720859</v>
+        <v>6720967</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3952,7 +3972,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124374436</v>
+        <v>124376762</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3985,7 +4005,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -3995,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467202</v>
+        <v>467043</v>
       </c>
       <c r="R32" t="n">
-        <v>6720759</v>
+        <v>6721047</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4058,10 +4082,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124376342</v>
+        <v>124376233</v>
       </c>
       <c r="B33" t="n">
-        <v>96227</v>
+        <v>90977</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4074,27 +4098,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4102,10 +4125,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467083</v>
+        <v>467068</v>
       </c>
       <c r="R33" t="n">
-        <v>6720839</v>
+        <v>6720851</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4165,10 +4188,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124376865</v>
+        <v>124376295</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4177,32 +4200,28 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4212,10 +4231,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466954</v>
+        <v>467095</v>
       </c>
       <c r="R34" t="n">
-        <v>6720913</v>
+        <v>6720881</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4275,10 +4294,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374476</v>
+        <v>124375621</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4291,24 +4310,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4318,10 +4341,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467209</v>
+        <v>467135</v>
       </c>
       <c r="R35" t="n">
-        <v>6720770</v>
+        <v>6720927</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4381,7 +4404,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374757</v>
+        <v>124376843</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4414,7 +4437,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4424,10 +4451,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467204</v>
+        <v>467041</v>
       </c>
       <c r="R36" t="n">
-        <v>6720836</v>
+        <v>6720899</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4487,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124376827</v>
+        <v>124375713</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4503,28 +4530,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4534,10 +4557,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467053</v>
+        <v>467042</v>
       </c>
       <c r="R37" t="n">
-        <v>6720938</v>
+        <v>6721029</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4597,10 +4620,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124375210</v>
+        <v>124374600</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4609,25 +4632,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4640,10 +4663,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467193</v>
+        <v>467226</v>
       </c>
       <c r="R38" t="n">
-        <v>6720911</v>
+        <v>6720796</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4703,10 +4726,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124376385</v>
+        <v>124374694</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4715,39 +4738,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4755,10 +4769,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467094</v>
+        <v>467218</v>
       </c>
       <c r="R39" t="n">
-        <v>6720828</v>
+        <v>6720814</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4818,10 +4832,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124376843</v>
+        <v>124375400</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4830,34 +4844,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4865,10 +4884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467041</v>
+        <v>467157</v>
       </c>
       <c r="R40" t="n">
-        <v>6720899</v>
+        <v>6720898</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4928,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124374570</v>
+        <v>124375752</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4940,30 +4959,36 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4971,10 +4996,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467219</v>
+        <v>467047</v>
       </c>
       <c r="R41" t="n">
-        <v>6720761</v>
+        <v>6720974</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5034,7 +5059,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124376775</v>
+        <v>124374736</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5067,11 +5092,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5081,10 +5102,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467056</v>
+        <v>467232</v>
       </c>
       <c r="R42" t="n">
-        <v>6720996</v>
+        <v>6720833</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5144,10 +5165,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376089</v>
+        <v>124376923</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5156,39 +5177,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5196,10 +5212,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466904</v>
+        <v>467176</v>
       </c>
       <c r="R43" t="n">
-        <v>6720952</v>
+        <v>6720792</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5259,7 +5275,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124375039</v>
+        <v>124374995</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5302,10 +5318,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467157</v>
+        <v>467162</v>
       </c>
       <c r="R44" t="n">
-        <v>6720881</v>
+        <v>6720859</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5365,10 +5381,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375650</v>
+        <v>124376775</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5381,24 +5397,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5408,10 +5428,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467134</v>
+        <v>467056</v>
       </c>
       <c r="R45" t="n">
-        <v>6720941</v>
+        <v>6720996</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5471,10 +5491,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124376270</v>
+        <v>124374964</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5483,36 +5503,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5520,10 +5534,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467075</v>
+        <v>467169</v>
       </c>
       <c r="R46" t="n">
-        <v>6720892</v>
+        <v>6720904</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5583,10 +5597,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375938</v>
+        <v>124374584</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5595,35 +5609,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5631,10 +5640,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466966</v>
+        <v>467197</v>
       </c>
       <c r="R47" t="n">
-        <v>6720916</v>
+        <v>6720764</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5675,6 +5684,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124375132</v>
+        <v>124375461</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5705,30 +5715,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5736,10 +5755,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467184</v>
+        <v>467156</v>
       </c>
       <c r="R48" t="n">
-        <v>6720843</v>
+        <v>6720908</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5799,10 +5818,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376910</v>
+        <v>124376194</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5811,34 +5830,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5846,10 +5870,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467140</v>
+        <v>466996</v>
       </c>
       <c r="R49" t="n">
-        <v>6720805</v>
+        <v>6720894</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5909,10 +5933,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375713</v>
+        <v>124376808</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5925,24 +5949,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5952,10 +5980,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467042</v>
+        <v>467087</v>
       </c>
       <c r="R50" t="n">
-        <v>6721029</v>
+        <v>6720934</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6015,7 +6043,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375010</v>
+        <v>124375210</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6058,10 +6086,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467143</v>
+        <v>467193</v>
       </c>
       <c r="R51" t="n">
-        <v>6720866</v>
+        <v>6720911</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6121,7 +6149,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124376762</v>
+        <v>124375039</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6154,11 +6182,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6168,10 +6192,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467043</v>
+        <v>467157</v>
       </c>
       <c r="R52" t="n">
-        <v>6721047</v>
+        <v>6720881</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6231,7 +6255,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124374709</v>
+        <v>124374508</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6274,10 +6298,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467216</v>
+        <v>467196</v>
       </c>
       <c r="R53" t="n">
-        <v>6720827</v>
+        <v>6720772</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6337,10 +6361,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374600</v>
+        <v>124374900</v>
       </c>
       <c r="B54" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6349,25 +6373,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6380,10 +6404,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467226</v>
+        <v>467191</v>
       </c>
       <c r="R54" t="n">
-        <v>6720796</v>
+        <v>6720901</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6443,10 +6467,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374804</v>
+        <v>124376827</v>
       </c>
       <c r="B55" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6459,26 +6483,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6490,10 +6514,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467239</v>
+        <v>467053</v>
       </c>
       <c r="R55" t="n">
-        <v>6720849</v>
+        <v>6720938</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6553,10 +6577,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124374845</v>
+        <v>124374922</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6565,39 +6589,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6605,10 +6620,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467251</v>
+        <v>467194</v>
       </c>
       <c r="R56" t="n">
-        <v>6720866</v>
+        <v>6720885</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6668,7 +6683,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124374553</v>
+        <v>124374936</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6711,10 +6726,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467224</v>
+        <v>467173</v>
       </c>
       <c r="R57" t="n">
-        <v>6720768</v>
+        <v>6720889</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6774,7 +6789,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375140</v>
+        <v>124374951</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6817,10 +6832,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467191</v>
+        <v>467182</v>
       </c>
       <c r="R58" t="n">
-        <v>6720859</v>
+        <v>6720879</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6880,10 +6895,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375292</v>
+        <v>124374476</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6896,21 +6911,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6923,10 +6938,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467160</v>
+        <v>467209</v>
       </c>
       <c r="R59" t="n">
-        <v>6720888</v>
+        <v>6720770</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6986,10 +7001,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124375436</v>
+        <v>124376126</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6998,39 +7013,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7038,10 +7049,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467164</v>
+        <v>466911</v>
       </c>
       <c r="R60" t="n">
-        <v>6720898</v>
+        <v>6720956</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7082,7 +7093,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7101,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376320</v>
+        <v>124375057</v>
       </c>
       <c r="B61" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7117,21 +7127,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7144,10 +7154,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467117</v>
+        <v>467156</v>
       </c>
       <c r="R61" t="n">
-        <v>6720888</v>
+        <v>6720850</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7207,7 +7217,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124374678</v>
+        <v>124375270</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7250,10 +7260,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467230</v>
+        <v>467180</v>
       </c>
       <c r="R62" t="n">
-        <v>6720817</v>
+        <v>6720912</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7313,10 +7323,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124376233</v>
+        <v>124375140</v>
       </c>
       <c r="B63" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7325,25 +7335,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7356,10 +7366,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467068</v>
+        <v>467191</v>
       </c>
       <c r="R63" t="n">
-        <v>6720851</v>
+        <v>6720859</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7419,10 +7429,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124374900</v>
+        <v>124375938</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7431,30 +7441,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7462,10 +7477,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467191</v>
+        <v>466966</v>
       </c>
       <c r="R64" t="n">
-        <v>6720901</v>
+        <v>6720916</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7506,7 +7521,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7525,10 +7539,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124374922</v>
+        <v>124375684</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7541,21 +7555,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7568,10 +7582,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467194</v>
+        <v>467166</v>
       </c>
       <c r="R65" t="n">
-        <v>6720885</v>
+        <v>6720986</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7631,10 +7645,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124374936</v>
+        <v>124376385</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7643,30 +7657,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7674,10 +7697,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467173</v>
+        <v>467094</v>
       </c>
       <c r="R66" t="n">
-        <v>6720889</v>
+        <v>6720828</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7737,10 +7760,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124376031</v>
+        <v>124376889</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7749,39 +7772,34 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7789,10 +7807,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466944</v>
+        <v>467053</v>
       </c>
       <c r="R67" t="n">
-        <v>6720920</v>
+        <v>6720874</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7852,10 +7870,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376194</v>
+        <v>124375118</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7864,39 +7882,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7904,10 +7913,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466996</v>
+        <v>467177</v>
       </c>
       <c r="R68" t="n">
-        <v>6720894</v>
+        <v>6720859</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7967,10 +7976,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124375400</v>
+        <v>124374570</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7979,39 +7988,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467157</v>
+        <v>467219</v>
       </c>
       <c r="R69" t="n">
-        <v>6720898</v>
+        <v>6720761</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376320</v>
+        <v>124374678</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467117</v>
+        <v>467230</v>
       </c>
       <c r="R2" t="n">
-        <v>6720888</v>
+        <v>6720817</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374620</v>
+        <v>124374736</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,28 +797,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467213</v>
+        <v>467232</v>
       </c>
       <c r="R3" t="n">
-        <v>6720795</v>
+        <v>6720833</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376270</v>
+        <v>124375621</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,36 +899,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467075</v>
+        <v>467135</v>
       </c>
       <c r="R4" t="n">
-        <v>6720892</v>
+        <v>6720927</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1003,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124375783</v>
+        <v>124374553</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,39 +1009,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467016</v>
+        <v>467224</v>
       </c>
       <c r="R5" t="n">
-        <v>6720909</v>
+        <v>6720768</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1118,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374678</v>
+        <v>124376843</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1151,7 +1136,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1161,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467230</v>
+        <v>467041</v>
       </c>
       <c r="R6" t="n">
-        <v>6720817</v>
+        <v>6720899</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1224,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374309</v>
+        <v>124376923</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,35 +1229,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1276,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467236</v>
+        <v>467176</v>
       </c>
       <c r="R7" t="n">
-        <v>6720773</v>
+        <v>6720792</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1320,6 +1304,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374845</v>
+        <v>124376046</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1373,7 +1358,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1390,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467251</v>
+        <v>466941</v>
       </c>
       <c r="R8" t="n">
-        <v>6720866</v>
+        <v>6720908</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1453,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124375482</v>
+        <v>124374620</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,39 +1450,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467160</v>
+        <v>467213</v>
       </c>
       <c r="R9" t="n">
-        <v>6720905</v>
+        <v>6720795</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1568,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375596</v>
+        <v>124375713</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,39 +1560,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467127</v>
+        <v>467042</v>
       </c>
       <c r="R10" t="n">
-        <v>6720921</v>
+        <v>6721029</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1683,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124376342</v>
+        <v>124375400</v>
       </c>
       <c r="B11" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,29 +1666,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1727,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467083</v>
+        <v>467157</v>
       </c>
       <c r="R11" t="n">
-        <v>6720839</v>
+        <v>6720898</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1790,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375768</v>
+        <v>124375461</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,30 +1781,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467034</v>
+        <v>467156</v>
       </c>
       <c r="R12" t="n">
-        <v>6720933</v>
+        <v>6720908</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1896,10 +1884,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124376046</v>
+        <v>124374694</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,39 +1896,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1948,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466941</v>
+        <v>467218</v>
       </c>
       <c r="R13" t="n">
-        <v>6720908</v>
+        <v>6720814</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2011,7 +1990,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375106</v>
+        <v>124375210</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2054,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467167</v>
+        <v>467193</v>
       </c>
       <c r="R14" t="n">
-        <v>6720870</v>
+        <v>6720911</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2117,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374553</v>
+        <v>124376342</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,30 +2108,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2160,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467224</v>
+        <v>467083</v>
       </c>
       <c r="R15" t="n">
-        <v>6720768</v>
+        <v>6720839</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2223,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124376910</v>
+        <v>124374845</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,34 +2215,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2270,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467251</v>
       </c>
       <c r="R16" t="n">
-        <v>6720805</v>
+        <v>6720866</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2333,10 +2318,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124374709</v>
+        <v>124375436</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2345,30 +2330,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2376,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467216</v>
+        <v>467164</v>
       </c>
       <c r="R17" t="n">
-        <v>6720827</v>
+        <v>6720898</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2439,7 +2433,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376750</v>
+        <v>124374508</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2472,11 +2466,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2486,10 +2476,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467146</v>
+        <v>467196</v>
       </c>
       <c r="R18" t="n">
-        <v>6721019</v>
+        <v>6720772</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2549,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124376865</v>
+        <v>124375650</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,28 +2555,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2596,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466954</v>
+        <v>467134</v>
       </c>
       <c r="R19" t="n">
-        <v>6720913</v>
+        <v>6720941</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2659,10 +2645,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124375650</v>
+        <v>124375732</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2671,30 +2657,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2702,10 +2694,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467134</v>
+        <v>467043</v>
       </c>
       <c r="R20" t="n">
-        <v>6720941</v>
+        <v>6720984</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2765,10 +2757,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375732</v>
+        <v>124375292</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2777,36 +2769,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2814,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467043</v>
+        <v>467160</v>
       </c>
       <c r="R21" t="n">
-        <v>6720984</v>
+        <v>6720888</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2877,7 +2863,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376031</v>
+        <v>124375482</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2912,7 +2898,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2929,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466944</v>
+        <v>467160</v>
       </c>
       <c r="R22" t="n">
-        <v>6720920</v>
+        <v>6720905</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2992,10 +2978,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374804</v>
+        <v>124374476</v>
       </c>
       <c r="B23" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,28 +2994,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3039,10 +3021,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467239</v>
+        <v>467209</v>
       </c>
       <c r="R23" t="n">
-        <v>6720849</v>
+        <v>6720770</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3102,7 +3084,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375010</v>
+        <v>124374922</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3145,10 +3127,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467143</v>
+        <v>467194</v>
       </c>
       <c r="R24" t="n">
-        <v>6720866</v>
+        <v>6720885</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3208,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374436</v>
+        <v>124375938</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3220,30 +3202,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3251,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467202</v>
+        <v>466966</v>
       </c>
       <c r="R25" t="n">
-        <v>6720759</v>
+        <v>6720916</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3295,7 +3282,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3314,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124375436</v>
+        <v>124376794</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,39 +3312,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3366,10 +3347,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467164</v>
+        <v>467106</v>
       </c>
       <c r="R26" t="n">
-        <v>6720898</v>
+        <v>6720967</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3429,10 +3410,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375132</v>
+        <v>124376270</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3441,30 +3422,36 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3472,10 +3459,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467184</v>
+        <v>467075</v>
       </c>
       <c r="R27" t="n">
-        <v>6720843</v>
+        <v>6720892</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3535,10 +3522,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374757</v>
+        <v>124375596</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3547,30 +3534,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3578,10 +3574,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467204</v>
+        <v>467127</v>
       </c>
       <c r="R28" t="n">
-        <v>6720836</v>
+        <v>6720921</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3641,10 +3637,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375292</v>
+        <v>124375118</v>
       </c>
       <c r="B29" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3657,21 +3653,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3684,10 +3680,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467160</v>
+        <v>467177</v>
       </c>
       <c r="R29" t="n">
-        <v>6720888</v>
+        <v>6720859</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3747,10 +3743,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124376089</v>
+        <v>124374951</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3759,39 +3755,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3799,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466904</v>
+        <v>467182</v>
       </c>
       <c r="R30" t="n">
-        <v>6720952</v>
+        <v>6720879</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3862,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124376794</v>
+        <v>124375684</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3878,28 +3865,24 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3909,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467106</v>
+        <v>467166</v>
       </c>
       <c r="R31" t="n">
-        <v>6720967</v>
+        <v>6720986</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3972,10 +3955,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124376762</v>
+        <v>124375752</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3984,34 +3967,36 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4019,10 +4004,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467043</v>
+        <v>467047</v>
       </c>
       <c r="R32" t="n">
-        <v>6721047</v>
+        <v>6720974</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4082,10 +4067,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124376233</v>
+        <v>124374995</v>
       </c>
       <c r="B33" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4094,25 +4079,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4125,10 +4110,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467068</v>
+        <v>467162</v>
       </c>
       <c r="R33" t="n">
-        <v>6720851</v>
+        <v>6720859</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4188,10 +4173,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124376295</v>
+        <v>124376089</v>
       </c>
       <c r="B34" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4200,30 +4185,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4231,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467095</v>
+        <v>466904</v>
       </c>
       <c r="R34" t="n">
-        <v>6720881</v>
+        <v>6720952</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4294,10 +4288,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124375621</v>
+        <v>124374436</v>
       </c>
       <c r="B35" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4310,28 +4304,24 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4341,10 +4331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467135</v>
+        <v>467202</v>
       </c>
       <c r="R35" t="n">
-        <v>6720927</v>
+        <v>6720759</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4404,7 +4394,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124376843</v>
+        <v>124375039</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4437,11 +4427,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4451,10 +4437,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467041</v>
+        <v>467157</v>
       </c>
       <c r="R36" t="n">
-        <v>6720899</v>
+        <v>6720881</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4514,10 +4500,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124375713</v>
+        <v>124374900</v>
       </c>
       <c r="B37" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4530,21 +4516,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4557,10 +4543,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467042</v>
+        <v>467191</v>
       </c>
       <c r="R37" t="n">
-        <v>6721029</v>
+        <v>6720901</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4620,10 +4606,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124374600</v>
+        <v>124376750</v>
       </c>
       <c r="B38" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4632,28 +4618,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4663,10 +4653,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467226</v>
+        <v>467146</v>
       </c>
       <c r="R38" t="n">
-        <v>6720796</v>
+        <v>6721019</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4726,10 +4716,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124374694</v>
+        <v>124374600</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4738,25 +4728,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4769,10 +4759,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467218</v>
+        <v>467226</v>
       </c>
       <c r="R39" t="n">
-        <v>6720814</v>
+        <v>6720796</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4832,10 +4822,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375400</v>
+        <v>124376889</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4844,39 +4834,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4884,10 +4869,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467157</v>
+        <v>467053</v>
       </c>
       <c r="R40" t="n">
-        <v>6720898</v>
+        <v>6720874</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4947,10 +4932,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375752</v>
+        <v>124374804</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4959,36 +4944,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4996,10 +4979,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467047</v>
+        <v>467239</v>
       </c>
       <c r="R41" t="n">
-        <v>6720974</v>
+        <v>6720849</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5059,7 +5042,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124374736</v>
+        <v>124376910</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5092,7 +5075,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5102,10 +5089,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467232</v>
+        <v>467140</v>
       </c>
       <c r="R42" t="n">
-        <v>6720833</v>
+        <v>6720805</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5165,7 +5152,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376923</v>
+        <v>124375106</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5198,11 +5185,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5212,10 +5195,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467176</v>
+        <v>467167</v>
       </c>
       <c r="R43" t="n">
-        <v>6720792</v>
+        <v>6720870</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5275,7 +5258,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124374995</v>
+        <v>124375132</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5318,10 +5301,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467162</v>
+        <v>467184</v>
       </c>
       <c r="R44" t="n">
-        <v>6720859</v>
+        <v>6720843</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5381,7 +5364,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124376775</v>
+        <v>124374757</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5414,11 +5397,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5428,10 +5407,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467056</v>
+        <v>467204</v>
       </c>
       <c r="R45" t="n">
-        <v>6720996</v>
+        <v>6720836</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5491,7 +5470,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124374964</v>
+        <v>124375057</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5534,10 +5513,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467169</v>
+        <v>467156</v>
       </c>
       <c r="R46" t="n">
-        <v>6720904</v>
+        <v>6720850</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5597,10 +5576,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374584</v>
+        <v>124376295</v>
       </c>
       <c r="B47" t="n">
-        <v>78547</v>
+        <v>90977</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5609,25 +5588,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5640,10 +5619,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467197</v>
+        <v>467095</v>
       </c>
       <c r="R47" t="n">
-        <v>6720764</v>
+        <v>6720881</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5703,7 +5682,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124375461</v>
+        <v>124376385</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5738,7 +5717,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5755,10 +5734,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467156</v>
+        <v>467094</v>
       </c>
       <c r="R48" t="n">
-        <v>6720908</v>
+        <v>6720828</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5818,7 +5797,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376194</v>
+        <v>124376031</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5853,7 +5832,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5870,10 +5849,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466996</v>
+        <v>466944</v>
       </c>
       <c r="R49" t="n">
-        <v>6720894</v>
+        <v>6720920</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5933,7 +5912,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376808</v>
+        <v>124375140</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5966,11 +5945,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5980,10 +5955,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467087</v>
+        <v>467191</v>
       </c>
       <c r="R50" t="n">
-        <v>6720934</v>
+        <v>6720859</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6043,7 +6018,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375210</v>
+        <v>124374570</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6086,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467193</v>
+        <v>467219</v>
       </c>
       <c r="R51" t="n">
-        <v>6720911</v>
+        <v>6720761</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6149,7 +6124,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375039</v>
+        <v>124376775</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6182,7 +6157,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6192,10 +6171,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467157</v>
+        <v>467056</v>
       </c>
       <c r="R52" t="n">
-        <v>6720881</v>
+        <v>6720996</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6255,10 +6234,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124374508</v>
+        <v>124376194</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6267,30 +6246,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6298,10 +6286,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467196</v>
+        <v>466996</v>
       </c>
       <c r="R53" t="n">
-        <v>6720772</v>
+        <v>6720894</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6361,7 +6349,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374900</v>
+        <v>124375270</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6404,10 +6392,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467191</v>
+        <v>467180</v>
       </c>
       <c r="R54" t="n">
-        <v>6720901</v>
+        <v>6720912</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6467,7 +6455,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124376827</v>
+        <v>124374964</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6500,11 +6488,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6514,10 +6498,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467053</v>
+        <v>467169</v>
       </c>
       <c r="R55" t="n">
-        <v>6720938</v>
+        <v>6720904</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6577,7 +6561,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124374922</v>
+        <v>124376865</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6610,7 +6594,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6620,10 +6608,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467194</v>
+        <v>466954</v>
       </c>
       <c r="R56" t="n">
-        <v>6720885</v>
+        <v>6720913</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6683,7 +6671,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124374936</v>
+        <v>124374709</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6726,10 +6714,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467173</v>
+        <v>467216</v>
       </c>
       <c r="R57" t="n">
-        <v>6720889</v>
+        <v>6720827</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6789,10 +6777,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124374951</v>
+        <v>124375783</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6801,30 +6789,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6832,10 +6829,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467182</v>
+        <v>467016</v>
       </c>
       <c r="R58" t="n">
-        <v>6720879</v>
+        <v>6720909</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6895,10 +6892,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124374476</v>
+        <v>124374309</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6911,26 +6908,35 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6938,10 +6944,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467209</v>
+        <v>467236</v>
       </c>
       <c r="R59" t="n">
-        <v>6720770</v>
+        <v>6720773</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6982,7 +6988,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7001,10 +7006,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376126</v>
+        <v>124376808</v>
       </c>
       <c r="B60" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7013,35 +7018,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7049,10 +7053,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466911</v>
+        <v>467087</v>
       </c>
       <c r="R60" t="n">
-        <v>6720956</v>
+        <v>6720934</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7093,6 +7097,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7111,7 +7116,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124375057</v>
+        <v>124376827</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -7144,7 +7149,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7154,10 +7163,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467156</v>
+        <v>467053</v>
       </c>
       <c r="R61" t="n">
-        <v>6720850</v>
+        <v>6720938</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7217,7 +7226,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124375270</v>
+        <v>124376762</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7250,7 +7259,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7260,10 +7273,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467180</v>
+        <v>467043</v>
       </c>
       <c r="R62" t="n">
-        <v>6720912</v>
+        <v>6721047</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7323,10 +7336,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124375140</v>
+        <v>124375768</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7339,21 +7352,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7366,10 +7379,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467191</v>
+        <v>467034</v>
       </c>
       <c r="R63" t="n">
-        <v>6720859</v>
+        <v>6720933</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7429,7 +7442,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124375938</v>
+        <v>124376126</v>
       </c>
       <c r="B64" t="n">
         <v>56722</v>
@@ -7477,10 +7490,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466966</v>
+        <v>466911</v>
       </c>
       <c r="R64" t="n">
-        <v>6720916</v>
+        <v>6720956</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7539,10 +7552,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124375684</v>
+        <v>124376320</v>
       </c>
       <c r="B65" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7555,21 +7568,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7582,10 +7595,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467166</v>
+        <v>467117</v>
       </c>
       <c r="R65" t="n">
-        <v>6720986</v>
+        <v>6720888</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7645,10 +7658,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124376385</v>
+        <v>124374584</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7657,39 +7670,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7697,10 +7701,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467094</v>
+        <v>467197</v>
       </c>
       <c r="R66" t="n">
-        <v>6720828</v>
+        <v>6720764</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7760,10 +7764,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124376889</v>
+        <v>124376233</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7772,32 +7776,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467053</v>
+        <v>467068</v>
       </c>
       <c r="R67" t="n">
-        <v>6720874</v>
+        <v>6720851</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7870,7 +7870,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124375118</v>
+        <v>124374936</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467177</v>
+        <v>467173</v>
       </c>
       <c r="R68" t="n">
-        <v>6720859</v>
+        <v>6720889</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124374570</v>
+        <v>124375010</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467219</v>
+        <v>467143</v>
       </c>
       <c r="R69" t="n">
-        <v>6720761</v>
+        <v>6720866</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124375400</v>
+        <v>124374694</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,39 +1666,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467157</v>
+        <v>467218</v>
       </c>
       <c r="R11" t="n">
-        <v>6720898</v>
+        <v>6720814</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1769,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375461</v>
+        <v>124375400</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1821,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467156</v>
+        <v>467157</v>
       </c>
       <c r="R12" t="n">
-        <v>6720908</v>
+        <v>6720898</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1884,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124374694</v>
+        <v>124375461</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,30 +1887,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467218</v>
+        <v>467156</v>
       </c>
       <c r="R13" t="n">
-        <v>6720814</v>
+        <v>6720908</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1990,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375210</v>
+        <v>124375650</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,21 +2006,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467193</v>
+        <v>467134</v>
       </c>
       <c r="R14" t="n">
-        <v>6720911</v>
+        <v>6720941</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124376342</v>
+        <v>124374508</v>
       </c>
       <c r="B15" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,31 +2108,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467083</v>
+        <v>467196</v>
       </c>
       <c r="R15" t="n">
-        <v>6720839</v>
+        <v>6720772</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2203,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374845</v>
+        <v>124376342</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2215,37 +2214,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2255,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467251</v>
+        <v>467083</v>
       </c>
       <c r="R16" t="n">
-        <v>6720866</v>
+        <v>6720839</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2433,7 +2424,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124374508</v>
+        <v>124375210</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2476,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467196</v>
+        <v>467193</v>
       </c>
       <c r="R18" t="n">
-        <v>6720772</v>
+        <v>6720911</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2539,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375650</v>
+        <v>124374845</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2551,30 +2542,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467134</v>
+        <v>467251</v>
       </c>
       <c r="R19" t="n">
-        <v>6720941</v>
+        <v>6720866</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124376910</v>
+        <v>124375132</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5075,11 +5075,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5089,10 +5085,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467140</v>
+        <v>467184</v>
       </c>
       <c r="R42" t="n">
-        <v>6720805</v>
+        <v>6720843</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5152,7 +5148,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375106</v>
+        <v>124374757</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5195,10 +5191,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467167</v>
+        <v>467204</v>
       </c>
       <c r="R43" t="n">
-        <v>6720870</v>
+        <v>6720836</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5258,7 +5254,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124375132</v>
+        <v>124375106</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5301,10 +5297,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467184</v>
+        <v>467167</v>
       </c>
       <c r="R44" t="n">
-        <v>6720843</v>
+        <v>6720870</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5364,7 +5360,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374757</v>
+        <v>124376910</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5397,7 +5393,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467204</v>
+        <v>467140</v>
       </c>
       <c r="R45" t="n">
-        <v>6720836</v>
+        <v>6720805</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376865</v>
+        <v>124375783</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6573,34 +6573,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6608,10 +6613,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466954</v>
+        <v>467016</v>
       </c>
       <c r="R56" t="n">
-        <v>6720913</v>
+        <v>6720909</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6671,7 +6676,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124374709</v>
+        <v>124376865</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6704,7 +6709,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6714,10 +6723,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467216</v>
+        <v>466954</v>
       </c>
       <c r="R57" t="n">
-        <v>6720827</v>
+        <v>6720913</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6777,10 +6786,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375783</v>
+        <v>124374309</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6789,39 +6798,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6829,10 +6838,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467016</v>
+        <v>467236</v>
       </c>
       <c r="R58" t="n">
-        <v>6720909</v>
+        <v>6720773</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6873,7 +6882,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6892,10 +6900,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124374309</v>
+        <v>124374709</v>
       </c>
       <c r="B59" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6908,35 +6916,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6944,10 +6943,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467236</v>
+        <v>467216</v>
       </c>
       <c r="R59" t="n">
-        <v>6720773</v>
+        <v>6720827</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6988,6 +6987,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7764,10 +7764,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124376233</v>
+        <v>124375010</v>
       </c>
       <c r="B67" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7776,25 +7776,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467068</v>
+        <v>467143</v>
       </c>
       <c r="R67" t="n">
-        <v>6720851</v>
+        <v>6720866</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124374936</v>
+        <v>124376233</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7882,25 +7882,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467173</v>
+        <v>467068</v>
       </c>
       <c r="R68" t="n">
-        <v>6720889</v>
+        <v>6720851</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124375010</v>
+        <v>124374936</v>
       </c>
       <c r="B69" t="n">
         <v>78810</v>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467143</v>
+        <v>467173</v>
       </c>
       <c r="R69" t="n">
-        <v>6720866</v>
+        <v>6720889</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374678</v>
+        <v>124375210</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467230</v>
+        <v>467193</v>
       </c>
       <c r="R2" t="n">
-        <v>6720817</v>
+        <v>6720911</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374736</v>
+        <v>124375783</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467232</v>
+        <v>467016</v>
       </c>
       <c r="R3" t="n">
-        <v>6720833</v>
+        <v>6720909</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375621</v>
+        <v>124374736</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +912,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467135</v>
+        <v>467232</v>
       </c>
       <c r="R4" t="n">
-        <v>6720927</v>
+        <v>6720833</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -997,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374553</v>
+        <v>124376923</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1030,7 +1035,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1040,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467224</v>
+        <v>467176</v>
       </c>
       <c r="R5" t="n">
-        <v>6720768</v>
+        <v>6720792</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376843</v>
+        <v>124376808</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1150,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467041</v>
+        <v>467087</v>
       </c>
       <c r="R6" t="n">
-        <v>6720899</v>
+        <v>6720934</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1213,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124376923</v>
+        <v>124376794</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1248,7 +1257,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1260,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467176</v>
+        <v>467106</v>
       </c>
       <c r="R7" t="n">
-        <v>6720792</v>
+        <v>6720967</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1323,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124376046</v>
+        <v>124374600</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,39 +1344,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466941</v>
+        <v>467226</v>
       </c>
       <c r="R8" t="n">
-        <v>6720908</v>
+        <v>6720796</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124374620</v>
+        <v>124376889</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,26 +1454,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467213</v>
+        <v>467053</v>
       </c>
       <c r="R9" t="n">
-        <v>6720795</v>
+        <v>6720874</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375713</v>
+        <v>124374964</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467042</v>
+        <v>467169</v>
       </c>
       <c r="R10" t="n">
-        <v>6721029</v>
+        <v>6720904</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374694</v>
+        <v>124376843</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1687,7 +1687,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1697,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467218</v>
+        <v>467041</v>
       </c>
       <c r="R11" t="n">
-        <v>6720814</v>
+        <v>6720899</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1760,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375400</v>
+        <v>124375106</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,39 +1776,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1812,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467157</v>
+        <v>467167</v>
       </c>
       <c r="R12" t="n">
-        <v>6720898</v>
+        <v>6720870</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1875,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375461</v>
+        <v>124374436</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,39 +1882,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467156</v>
+        <v>467202</v>
       </c>
       <c r="R13" t="n">
-        <v>6720908</v>
+        <v>6720759</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1990,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375650</v>
+        <v>124374553</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,21 +1992,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2033,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467134</v>
+        <v>467224</v>
       </c>
       <c r="R14" t="n">
-        <v>6720941</v>
+        <v>6720768</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2096,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374508</v>
+        <v>124374678</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2139,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467196</v>
+        <v>467230</v>
       </c>
       <c r="R15" t="n">
-        <v>6720772</v>
+        <v>6720817</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2202,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124376342</v>
+        <v>124375436</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2214,29 +2200,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2246,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467083</v>
+        <v>467164</v>
       </c>
       <c r="R16" t="n">
-        <v>6720839</v>
+        <v>6720898</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2309,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375436</v>
+        <v>124375057</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2321,39 +2315,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2361,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467164</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6720898</v>
+        <v>6720850</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2424,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124375210</v>
+        <v>124376295</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2436,25 +2421,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467193</v>
+        <v>467095</v>
       </c>
       <c r="R18" t="n">
-        <v>6720911</v>
+        <v>6720881</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2530,10 +2515,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374845</v>
+        <v>124374757</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,39 +2527,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2582,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467251</v>
+        <v>467204</v>
       </c>
       <c r="R19" t="n">
-        <v>6720866</v>
+        <v>6720836</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2645,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124375732</v>
+        <v>124376194</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2657,36 +2633,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2694,10 +2673,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467043</v>
+        <v>466996</v>
       </c>
       <c r="R20" t="n">
-        <v>6720984</v>
+        <v>6720894</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2757,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375292</v>
+        <v>124374845</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2769,30 +2748,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2800,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467160</v>
+        <v>467251</v>
       </c>
       <c r="R21" t="n">
-        <v>6720888</v>
+        <v>6720866</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2863,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124375482</v>
+        <v>124376320</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2875,39 +2863,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2915,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467160</v>
+        <v>467117</v>
       </c>
       <c r="R22" t="n">
-        <v>6720905</v>
+        <v>6720888</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2978,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374476</v>
+        <v>124376342</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,30 +2969,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3021,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467209</v>
+        <v>467083</v>
       </c>
       <c r="R23" t="n">
-        <v>6720770</v>
+        <v>6720839</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3084,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124374922</v>
+        <v>124375292</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,21 +3080,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3127,10 +3107,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467194</v>
+        <v>467160</v>
       </c>
       <c r="R24" t="n">
-        <v>6720885</v>
+        <v>6720888</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3190,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375938</v>
+        <v>124376827</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3202,35 +3182,34 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3238,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>466966</v>
+        <v>467053</v>
       </c>
       <c r="R25" t="n">
-        <v>6720916</v>
+        <v>6720938</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3282,6 +3261,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3300,7 +3280,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124376794</v>
+        <v>124374900</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3333,11 +3313,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3347,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467106</v>
+        <v>467191</v>
       </c>
       <c r="R26" t="n">
-        <v>6720967</v>
+        <v>6720901</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3410,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124376270</v>
+        <v>124375938</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3426,30 +3402,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3459,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467075</v>
+        <v>466966</v>
       </c>
       <c r="R27" t="n">
-        <v>6720892</v>
+        <v>6720916</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3503,7 +3478,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3522,10 +3496,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375596</v>
+        <v>124375713</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,39 +3508,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3574,10 +3539,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467127</v>
+        <v>467042</v>
       </c>
       <c r="R28" t="n">
-        <v>6720921</v>
+        <v>6721029</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3743,7 +3708,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124374951</v>
+        <v>124376762</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3776,7 +3741,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3786,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467182</v>
+        <v>467043</v>
       </c>
       <c r="R30" t="n">
-        <v>6720879</v>
+        <v>6721047</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3849,10 +3818,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124375684</v>
+        <v>124376233</v>
       </c>
       <c r="B31" t="n">
-        <v>78547</v>
+        <v>90977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3861,25 +3830,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3892,10 +3861,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467166</v>
+        <v>467068</v>
       </c>
       <c r="R31" t="n">
-        <v>6720986</v>
+        <v>6720851</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3955,10 +3924,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375752</v>
+        <v>124374694</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3967,36 +3936,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4004,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467047</v>
+        <v>467218</v>
       </c>
       <c r="R32" t="n">
-        <v>6720974</v>
+        <v>6720814</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4067,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374995</v>
+        <v>124375621</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4083,24 +4046,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4110,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467162</v>
+        <v>467135</v>
       </c>
       <c r="R33" t="n">
-        <v>6720859</v>
+        <v>6720927</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4173,7 +4140,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124376089</v>
+        <v>124376046</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4208,7 +4175,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4225,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466904</v>
+        <v>466941</v>
       </c>
       <c r="R34" t="n">
-        <v>6720952</v>
+        <v>6720908</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4288,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374436</v>
+        <v>124376385</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4300,30 +4267,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4331,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467202</v>
+        <v>467094</v>
       </c>
       <c r="R35" t="n">
-        <v>6720759</v>
+        <v>6720828</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4394,10 +4370,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375039</v>
+        <v>124375650</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4410,21 +4386,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4437,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467157</v>
+        <v>467134</v>
       </c>
       <c r="R36" t="n">
-        <v>6720881</v>
+        <v>6720941</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4500,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374900</v>
+        <v>124375684</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4516,21 +4492,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4543,10 +4519,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467191</v>
+        <v>467166</v>
       </c>
       <c r="R37" t="n">
-        <v>6720901</v>
+        <v>6720986</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4606,7 +4582,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124376750</v>
+        <v>124375010</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4639,11 +4615,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4653,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467146</v>
+        <v>467143</v>
       </c>
       <c r="R38" t="n">
-        <v>6721019</v>
+        <v>6720866</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4716,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124374600</v>
+        <v>124375732</v>
       </c>
       <c r="B39" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4732,26 +4704,32 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4759,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467226</v>
+        <v>467043</v>
       </c>
       <c r="R39" t="n">
-        <v>6720796</v>
+        <v>6720984</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4822,10 +4800,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124376889</v>
+        <v>124375596</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4834,34 +4812,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4869,10 +4852,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467053</v>
+        <v>467127</v>
       </c>
       <c r="R40" t="n">
-        <v>6720874</v>
+        <v>6720921</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4932,10 +4915,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124374804</v>
+        <v>124374584</v>
       </c>
       <c r="B41" t="n">
-        <v>91032</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4948,28 +4931,24 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -4979,10 +4958,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467239</v>
+        <v>467197</v>
       </c>
       <c r="R41" t="n">
-        <v>6720849</v>
+        <v>6720764</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5148,7 +5127,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124374757</v>
+        <v>124375270</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5191,10 +5170,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467204</v>
+        <v>467180</v>
       </c>
       <c r="R43" t="n">
-        <v>6720836</v>
+        <v>6720912</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5254,7 +5233,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124375106</v>
+        <v>124374570</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5297,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467167</v>
+        <v>467219</v>
       </c>
       <c r="R44" t="n">
-        <v>6720870</v>
+        <v>6720761</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5360,7 +5339,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124376910</v>
+        <v>124375039</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5393,11 +5372,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5407,10 +5382,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467140</v>
+        <v>467157</v>
       </c>
       <c r="R45" t="n">
-        <v>6720805</v>
+        <v>6720881</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5470,10 +5445,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375057</v>
+        <v>124376126</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5482,30 +5457,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5513,10 +5493,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467156</v>
+        <v>466911</v>
       </c>
       <c r="R46" t="n">
-        <v>6720850</v>
+        <v>6720956</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5557,7 +5537,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5576,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124376295</v>
+        <v>124375400</v>
       </c>
       <c r="B47" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5588,30 +5567,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5619,10 +5607,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467095</v>
+        <v>467157</v>
       </c>
       <c r="R47" t="n">
-        <v>6720881</v>
+        <v>6720898</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5682,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124376385</v>
+        <v>124374476</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5694,39 +5682,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5734,10 +5713,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467094</v>
+        <v>467209</v>
       </c>
       <c r="R48" t="n">
-        <v>6720828</v>
+        <v>6720770</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5797,10 +5776,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376031</v>
+        <v>124374508</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5809,39 +5788,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5849,10 +5819,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466944</v>
+        <v>467196</v>
       </c>
       <c r="R49" t="n">
-        <v>6720920</v>
+        <v>6720772</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5912,10 +5882,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375140</v>
+        <v>124375768</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5928,21 +5898,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5955,10 +5925,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467191</v>
+        <v>467034</v>
       </c>
       <c r="R50" t="n">
-        <v>6720859</v>
+        <v>6720933</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6018,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124374570</v>
+        <v>124375482</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6030,30 +6000,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6061,10 +6040,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467219</v>
+        <v>467160</v>
       </c>
       <c r="R51" t="n">
-        <v>6720761</v>
+        <v>6720905</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6124,10 +6103,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124376775</v>
+        <v>124376031</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6136,34 +6115,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6171,10 +6155,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467056</v>
+        <v>466944</v>
       </c>
       <c r="R52" t="n">
-        <v>6720996</v>
+        <v>6720920</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6234,7 +6218,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124376194</v>
+        <v>124375461</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6269,7 +6253,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6286,10 +6270,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466996</v>
+        <v>467156</v>
       </c>
       <c r="R53" t="n">
-        <v>6720894</v>
+        <v>6720908</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6349,7 +6333,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124375270</v>
+        <v>124376910</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6382,7 +6366,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6392,10 +6380,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467180</v>
+        <v>467140</v>
       </c>
       <c r="R54" t="n">
-        <v>6720912</v>
+        <v>6720805</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6455,10 +6443,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374964</v>
+        <v>124374620</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6471,24 +6459,28 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6498,10 +6490,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467169</v>
+        <v>467213</v>
       </c>
       <c r="R55" t="n">
-        <v>6720904</v>
+        <v>6720795</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6561,10 +6553,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124375783</v>
+        <v>124376750</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6573,39 +6565,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6613,10 +6600,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467016</v>
+        <v>467146</v>
       </c>
       <c r="R56" t="n">
-        <v>6720909</v>
+        <v>6721019</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6676,10 +6663,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124376865</v>
+        <v>124376270</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6688,34 +6675,36 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6723,10 +6712,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466954</v>
+        <v>467075</v>
       </c>
       <c r="R57" t="n">
-        <v>6720913</v>
+        <v>6720892</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6786,10 +6775,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124374309</v>
+        <v>124375752</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
+        <v>8447</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6798,37 +6787,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -6838,10 +6824,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467236</v>
+        <v>467047</v>
       </c>
       <c r="R58" t="n">
-        <v>6720773</v>
+        <v>6720974</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6882,6 +6868,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6900,7 +6887,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124374709</v>
+        <v>124376865</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6933,7 +6920,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -6943,10 +6934,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467216</v>
+        <v>466954</v>
       </c>
       <c r="R59" t="n">
-        <v>6720827</v>
+        <v>6720913</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7006,7 +6997,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376808</v>
+        <v>124374995</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7039,11 +7030,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7053,10 +7040,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467087</v>
+        <v>467162</v>
       </c>
       <c r="R60" t="n">
-        <v>6720934</v>
+        <v>6720859</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7116,7 +7103,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376827</v>
+        <v>124374922</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -7149,11 +7136,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7163,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467053</v>
+        <v>467194</v>
       </c>
       <c r="R61" t="n">
-        <v>6720938</v>
+        <v>6720885</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7226,7 +7209,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376762</v>
+        <v>124374936</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7259,11 +7242,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7273,10 +7252,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467043</v>
+        <v>467173</v>
       </c>
       <c r="R62" t="n">
-        <v>6721047</v>
+        <v>6720889</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7336,10 +7315,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124375768</v>
+        <v>124374709</v>
       </c>
       <c r="B63" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7352,21 +7331,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7379,10 +7358,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467034</v>
+        <v>467216</v>
       </c>
       <c r="R63" t="n">
-        <v>6720933</v>
+        <v>6720827</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7442,10 +7421,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376126</v>
+        <v>124374951</v>
       </c>
       <c r="B64" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7454,35 +7433,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7490,10 +7464,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466911</v>
+        <v>467182</v>
       </c>
       <c r="R64" t="n">
-        <v>6720956</v>
+        <v>6720879</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7534,6 +7508,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7552,10 +7527,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124376320</v>
+        <v>124376089</v>
       </c>
       <c r="B65" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7564,30 +7539,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7595,10 +7579,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467117</v>
+        <v>466904</v>
       </c>
       <c r="R65" t="n">
-        <v>6720888</v>
+        <v>6720952</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7658,10 +7642,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124374584</v>
+        <v>124374804</v>
       </c>
       <c r="B66" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7674,24 +7658,28 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -7701,10 +7689,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467197</v>
+        <v>467239</v>
       </c>
       <c r="R66" t="n">
-        <v>6720764</v>
+        <v>6720849</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7764,7 +7752,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375010</v>
+        <v>124375140</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7807,10 +7795,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467143</v>
+        <v>467191</v>
       </c>
       <c r="R67" t="n">
-        <v>6720866</v>
+        <v>6720859</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7870,10 +7858,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376233</v>
+        <v>124376775</v>
       </c>
       <c r="B68" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7882,28 +7870,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -7913,10 +7905,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467068</v>
+        <v>467056</v>
       </c>
       <c r="R68" t="n">
-        <v>6720851</v>
+        <v>6720996</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7976,10 +7968,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124374936</v>
+        <v>124374309</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7992,26 +7984,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8020,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467173</v>
+        <v>467236</v>
       </c>
       <c r="R69" t="n">
-        <v>6720889</v>
+        <v>6720773</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8063,7 +8064,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375783</v>
+        <v>124374736</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467016</v>
+        <v>467232</v>
       </c>
       <c r="R3" t="n">
-        <v>6720909</v>
+        <v>6720833</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374736</v>
+        <v>124375783</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +899,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467232</v>
+        <v>467016</v>
       </c>
       <c r="R4" t="n">
-        <v>6720833</v>
+        <v>6720909</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376889</v>
+        <v>124374553</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1471,11 +1471,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1485,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467053</v>
+        <v>467224</v>
       </c>
       <c r="R9" t="n">
-        <v>6720874</v>
+        <v>6720768</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1548,7 +1544,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124374964</v>
+        <v>124376889</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1581,7 +1577,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467169</v>
+        <v>467053</v>
       </c>
       <c r="R10" t="n">
-        <v>6720904</v>
+        <v>6720874</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124376843</v>
+        <v>124374964</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1687,11 +1687,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1701,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467041</v>
+        <v>467169</v>
       </c>
       <c r="R11" t="n">
-        <v>6720899</v>
+        <v>6720904</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1764,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375106</v>
+        <v>124376843</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1797,7 +1793,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467167</v>
+        <v>467041</v>
       </c>
       <c r="R12" t="n">
-        <v>6720870</v>
+        <v>6720899</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124374436</v>
+        <v>124375106</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467202</v>
+        <v>467167</v>
       </c>
       <c r="R13" t="n">
-        <v>6720759</v>
+        <v>6720870</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374553</v>
+        <v>124374436</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467224</v>
+        <v>467202</v>
       </c>
       <c r="R14" t="n">
-        <v>6720768</v>
+        <v>6720759</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374678</v>
+        <v>124375436</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,30 +2094,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2125,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467230</v>
+        <v>467164</v>
       </c>
       <c r="R15" t="n">
-        <v>6720817</v>
+        <v>6720898</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2188,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375436</v>
+        <v>124374678</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,39 +2209,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467164</v>
+        <v>467230</v>
       </c>
       <c r="R16" t="n">
-        <v>6720898</v>
+        <v>6720817</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374757</v>
+        <v>124376194</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,30 +2527,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2558,10 +2567,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467204</v>
+        <v>466996</v>
       </c>
       <c r="R19" t="n">
-        <v>6720836</v>
+        <v>6720894</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2621,10 +2630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124376194</v>
+        <v>124374757</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,39 +2642,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466996</v>
+        <v>467204</v>
       </c>
       <c r="R20" t="n">
-        <v>6720894</v>
+        <v>6720836</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375938</v>
+        <v>124375713</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3398,35 +3398,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3434,10 +3429,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>466966</v>
+        <v>467042</v>
       </c>
       <c r="R27" t="n">
-        <v>6720916</v>
+        <v>6721029</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3478,6 +3473,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3496,10 +3492,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375713</v>
+        <v>124375118</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,21 +3508,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3539,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467042</v>
+        <v>467177</v>
       </c>
       <c r="R28" t="n">
-        <v>6721029</v>
+        <v>6720859</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3602,10 +3598,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375118</v>
+        <v>124375938</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3614,30 +3610,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3645,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467177</v>
+        <v>466966</v>
       </c>
       <c r="R29" t="n">
-        <v>6720859</v>
+        <v>6720916</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3689,7 +3690,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4688,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124375732</v>
+        <v>124376126</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4704,30 +4704,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4737,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467043</v>
+        <v>466911</v>
       </c>
       <c r="R39" t="n">
-        <v>6720984</v>
+        <v>6720956</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4781,7 +4780,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4800,10 +4798,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375596</v>
+        <v>124375732</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4812,39 +4810,36 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4852,10 +4847,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467127</v>
+        <v>467043</v>
       </c>
       <c r="R40" t="n">
-        <v>6720921</v>
+        <v>6720984</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4915,10 +4910,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124374584</v>
+        <v>124375596</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4927,30 +4922,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4958,10 +4962,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467197</v>
+        <v>467127</v>
       </c>
       <c r="R41" t="n">
-        <v>6720764</v>
+        <v>6720921</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5021,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124375132</v>
+        <v>124374584</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5037,21 +5041,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5064,10 +5068,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467184</v>
+        <v>467197</v>
       </c>
       <c r="R42" t="n">
-        <v>6720843</v>
+        <v>6720764</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5127,7 +5131,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375270</v>
+        <v>124375132</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5170,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467180</v>
+        <v>467184</v>
       </c>
       <c r="R43" t="n">
-        <v>6720912</v>
+        <v>6720843</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5233,7 +5237,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124374570</v>
+        <v>124375270</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5276,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467219</v>
+        <v>467180</v>
       </c>
       <c r="R44" t="n">
-        <v>6720761</v>
+        <v>6720912</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5339,7 +5343,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375039</v>
+        <v>124374570</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5382,10 +5386,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467157</v>
+        <v>467219</v>
       </c>
       <c r="R45" t="n">
-        <v>6720881</v>
+        <v>6720761</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5445,10 +5449,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124376126</v>
+        <v>124375039</v>
       </c>
       <c r="B46" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5457,35 +5461,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5493,10 +5492,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466911</v>
+        <v>467157</v>
       </c>
       <c r="R46" t="n">
-        <v>6720956</v>
+        <v>6720881</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5537,6 +5536,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124375210</v>
+        <v>124376320</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467193</v>
+        <v>467117</v>
       </c>
       <c r="R2" t="n">
-        <v>6720911</v>
+        <v>6720888</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374736</v>
+        <v>124374757</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467232</v>
+        <v>467204</v>
       </c>
       <c r="R3" t="n">
-        <v>6720833</v>
+        <v>6720836</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375783</v>
+        <v>124374922</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467016</v>
+        <v>467194</v>
       </c>
       <c r="R4" t="n">
-        <v>6720909</v>
+        <v>6720885</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376923</v>
+        <v>124376295</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,32 +1005,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1049,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467176</v>
+        <v>467095</v>
       </c>
       <c r="R5" t="n">
-        <v>6720792</v>
+        <v>6720881</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1112,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376808</v>
+        <v>124376775</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1159,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467087</v>
+        <v>467056</v>
       </c>
       <c r="R6" t="n">
-        <v>6720934</v>
+        <v>6720996</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1222,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124376794</v>
+        <v>124375106</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1255,11 +1242,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1269,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467106</v>
+        <v>467167</v>
       </c>
       <c r="R7" t="n">
-        <v>6720967</v>
+        <v>6720870</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124374600</v>
+        <v>124375684</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467226</v>
+        <v>467166</v>
       </c>
       <c r="R8" t="n">
-        <v>6720796</v>
+        <v>6720986</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1438,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124374553</v>
+        <v>124374845</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,30 +1433,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467224</v>
+        <v>467251</v>
       </c>
       <c r="R9" t="n">
-        <v>6720768</v>
+        <v>6720866</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1544,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124376889</v>
+        <v>124376089</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,34 +1548,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467053</v>
+        <v>466904</v>
       </c>
       <c r="R10" t="n">
-        <v>6720874</v>
+        <v>6720952</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1654,7 +1651,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374964</v>
+        <v>124374995</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1697,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467169</v>
+        <v>467162</v>
       </c>
       <c r="R11" t="n">
-        <v>6720904</v>
+        <v>6720859</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1760,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376843</v>
+        <v>124376827</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1807,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467041</v>
+        <v>467053</v>
       </c>
       <c r="R12" t="n">
-        <v>6720899</v>
+        <v>6720938</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1870,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375106</v>
+        <v>124374600</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,25 +1879,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467167</v>
+        <v>467226</v>
       </c>
       <c r="R13" t="n">
-        <v>6720870</v>
+        <v>6720796</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1976,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374436</v>
+        <v>124375039</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2019,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467202</v>
+        <v>467157</v>
       </c>
       <c r="R14" t="n">
-        <v>6720759</v>
+        <v>6720881</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2082,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375436</v>
+        <v>124374309</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,39 +2091,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467164</v>
+        <v>467236</v>
       </c>
       <c r="R15" t="n">
-        <v>6720898</v>
+        <v>6720773</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2178,7 +2175,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2197,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374678</v>
+        <v>124376385</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,30 +2205,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2240,10 +2245,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467230</v>
+        <v>467094</v>
       </c>
       <c r="R16" t="n">
-        <v>6720817</v>
+        <v>6720828</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2303,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375057</v>
+        <v>124375713</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,21 +2324,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>467042</v>
       </c>
       <c r="R17" t="n">
-        <v>6720850</v>
+        <v>6721029</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2409,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376295</v>
+        <v>124376031</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,30 +2426,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2452,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467095</v>
+        <v>466944</v>
       </c>
       <c r="R18" t="n">
-        <v>6720881</v>
+        <v>6720920</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2515,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124376194</v>
+        <v>124375768</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2527,39 +2541,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2567,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466996</v>
+        <v>467034</v>
       </c>
       <c r="R19" t="n">
-        <v>6720894</v>
+        <v>6720933</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2630,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124374757</v>
+        <v>124375118</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2673,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467204</v>
+        <v>467177</v>
       </c>
       <c r="R20" t="n">
-        <v>6720836</v>
+        <v>6720859</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2736,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124374845</v>
+        <v>124374900</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,39 +2753,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2788,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467251</v>
+        <v>467191</v>
       </c>
       <c r="R21" t="n">
-        <v>6720866</v>
+        <v>6720901</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2851,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376320</v>
+        <v>124374436</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,21 +2863,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2894,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467117</v>
+        <v>467202</v>
       </c>
       <c r="R22" t="n">
-        <v>6720888</v>
+        <v>6720759</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2957,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124376342</v>
+        <v>124374964</v>
       </c>
       <c r="B23" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,31 +2965,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3001,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467083</v>
+        <v>467169</v>
       </c>
       <c r="R23" t="n">
-        <v>6720839</v>
+        <v>6720904</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3064,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375292</v>
+        <v>124376750</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,24 +3075,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3107,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467160</v>
+        <v>467146</v>
       </c>
       <c r="R24" t="n">
-        <v>6720888</v>
+        <v>6721019</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3170,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124376827</v>
+        <v>124375436</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,34 +3181,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3217,10 +3221,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467053</v>
+        <v>467164</v>
       </c>
       <c r="R25" t="n">
-        <v>6720938</v>
+        <v>6720898</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3280,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374900</v>
+        <v>124375938</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3292,30 +3296,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3323,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467191</v>
+        <v>466966</v>
       </c>
       <c r="R26" t="n">
-        <v>6720901</v>
+        <v>6720916</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3367,7 +3376,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3386,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375713</v>
+        <v>124375461</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3398,30 +3406,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3429,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467042</v>
+        <v>467156</v>
       </c>
       <c r="R27" t="n">
-        <v>6721029</v>
+        <v>6720908</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3492,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375118</v>
+        <v>124375482</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3504,30 +3521,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3535,10 +3561,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467177</v>
+        <v>467160</v>
       </c>
       <c r="R28" t="n">
-        <v>6720859</v>
+        <v>6720905</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3598,10 +3624,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375938</v>
+        <v>124376808</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3610,35 +3636,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3646,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>466966</v>
+        <v>467087</v>
       </c>
       <c r="R29" t="n">
-        <v>6720916</v>
+        <v>6720934</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3690,6 +3715,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3708,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124376762</v>
+        <v>124375783</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3720,34 +3746,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3755,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467043</v>
+        <v>467016</v>
       </c>
       <c r="R30" t="n">
-        <v>6721047</v>
+        <v>6720909</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3818,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124376233</v>
+        <v>124375132</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3830,25 +3861,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3861,10 +3892,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467068</v>
+        <v>467184</v>
       </c>
       <c r="R31" t="n">
-        <v>6720851</v>
+        <v>6720843</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3924,7 +3955,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124374694</v>
+        <v>124374508</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3967,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467218</v>
+        <v>467196</v>
       </c>
       <c r="R32" t="n">
-        <v>6720814</v>
+        <v>6720772</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4030,10 +4061,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124375621</v>
+        <v>124374709</v>
       </c>
       <c r="B33" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4046,28 +4077,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4077,10 +4104,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467135</v>
+        <v>467216</v>
       </c>
       <c r="R33" t="n">
-        <v>6720927</v>
+        <v>6720827</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4140,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124376046</v>
+        <v>124374584</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4152,39 +4179,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4192,10 +4210,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466941</v>
+        <v>467197</v>
       </c>
       <c r="R34" t="n">
-        <v>6720908</v>
+        <v>6720764</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4255,10 +4273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124376385</v>
+        <v>124376843</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4267,39 +4285,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4307,10 +4320,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467094</v>
+        <v>467041</v>
       </c>
       <c r="R35" t="n">
-        <v>6720828</v>
+        <v>6720899</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4370,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375650</v>
+        <v>124375400</v>
       </c>
       <c r="B36" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,30 +4395,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4413,10 +4435,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467134</v>
+        <v>467157</v>
       </c>
       <c r="R36" t="n">
-        <v>6720941</v>
+        <v>6720898</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4476,10 +4498,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124375684</v>
+        <v>124374694</v>
       </c>
       <c r="B37" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4492,21 +4514,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4519,10 +4541,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467166</v>
+        <v>467218</v>
       </c>
       <c r="R37" t="n">
-        <v>6720986</v>
+        <v>6720814</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4582,7 +4604,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124375010</v>
+        <v>124376910</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4615,7 +4637,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4625,10 +4651,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467143</v>
+        <v>467140</v>
       </c>
       <c r="R38" t="n">
-        <v>6720866</v>
+        <v>6720805</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4688,10 +4714,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124376126</v>
+        <v>124374678</v>
       </c>
       <c r="B39" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,35 +4726,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4736,10 +4757,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466911</v>
+        <v>467230</v>
       </c>
       <c r="R39" t="n">
-        <v>6720956</v>
+        <v>6720817</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4780,6 +4801,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4798,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375732</v>
+        <v>124375621</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>91032</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4810,36 +4832,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4847,10 +4867,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467043</v>
+        <v>467135</v>
       </c>
       <c r="R40" t="n">
-        <v>6720984</v>
+        <v>6720927</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4910,10 +4930,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375596</v>
+        <v>124374804</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4922,39 +4942,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4962,10 +4977,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467127</v>
+        <v>467239</v>
       </c>
       <c r="R41" t="n">
-        <v>6720921</v>
+        <v>6720849</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5025,10 +5040,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124374584</v>
+        <v>124374476</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5041,21 +5056,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5068,10 +5083,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467197</v>
+        <v>467209</v>
       </c>
       <c r="R42" t="n">
-        <v>6720764</v>
+        <v>6720770</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5131,10 +5146,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375132</v>
+        <v>124375650</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5147,21 +5162,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5174,10 +5189,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467184</v>
+        <v>467134</v>
       </c>
       <c r="R43" t="n">
-        <v>6720843</v>
+        <v>6720941</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5237,10 +5252,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124375270</v>
+        <v>124376126</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5249,30 +5264,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5280,10 +5300,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467180</v>
+        <v>466911</v>
       </c>
       <c r="R44" t="n">
-        <v>6720912</v>
+        <v>6720956</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5324,7 +5344,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5343,10 +5362,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374570</v>
+        <v>124375596</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5355,30 +5374,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5386,10 +5414,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467219</v>
+        <v>467127</v>
       </c>
       <c r="R45" t="n">
-        <v>6720761</v>
+        <v>6720921</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5449,10 +5477,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375039</v>
+        <v>124375732</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5461,30 +5489,36 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5492,10 +5526,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467157</v>
+        <v>467043</v>
       </c>
       <c r="R46" t="n">
-        <v>6720881</v>
+        <v>6720984</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5555,10 +5589,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375400</v>
+        <v>124375752</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5567,39 +5601,36 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5607,10 +5638,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467157</v>
+        <v>467047</v>
       </c>
       <c r="R47" t="n">
-        <v>6720898</v>
+        <v>6720974</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5670,10 +5701,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124374476</v>
+        <v>124376194</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5682,30 +5713,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5713,10 +5753,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467209</v>
+        <v>466996</v>
       </c>
       <c r="R48" t="n">
-        <v>6720770</v>
+        <v>6720894</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5776,10 +5816,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124374508</v>
+        <v>124375292</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5792,21 +5832,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5819,10 +5859,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467196</v>
+        <v>467160</v>
       </c>
       <c r="R49" t="n">
-        <v>6720772</v>
+        <v>6720888</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5882,10 +5922,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375768</v>
+        <v>124376889</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5898,24 +5938,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5925,10 +5969,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467034</v>
+        <v>467053</v>
       </c>
       <c r="R50" t="n">
-        <v>6720933</v>
+        <v>6720874</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5988,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375482</v>
+        <v>124374736</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6000,39 +6044,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6040,10 +6075,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467160</v>
+        <v>467232</v>
       </c>
       <c r="R51" t="n">
-        <v>6720905</v>
+        <v>6720833</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6103,10 +6138,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124376031</v>
+        <v>124374553</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6115,39 +6150,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6155,10 +6181,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466944</v>
+        <v>467224</v>
       </c>
       <c r="R52" t="n">
-        <v>6720920</v>
+        <v>6720768</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6218,10 +6244,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124375461</v>
+        <v>124375140</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6230,39 +6256,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6270,10 +6287,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467156</v>
+        <v>467191</v>
       </c>
       <c r="R53" t="n">
-        <v>6720908</v>
+        <v>6720859</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6333,7 +6350,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124376910</v>
+        <v>124376794</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6368,7 +6385,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6380,10 +6397,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467140</v>
+        <v>467106</v>
       </c>
       <c r="R54" t="n">
-        <v>6720805</v>
+        <v>6720967</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6443,10 +6460,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374620</v>
+        <v>124374951</v>
       </c>
       <c r="B55" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6459,28 +6476,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6490,10 +6503,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467213</v>
+        <v>467182</v>
       </c>
       <c r="R55" t="n">
-        <v>6720795</v>
+        <v>6720879</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6553,7 +6566,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376750</v>
+        <v>124375210</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6586,11 +6599,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6600,10 +6609,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467146</v>
+        <v>467193</v>
       </c>
       <c r="R56" t="n">
-        <v>6721019</v>
+        <v>6720911</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6663,10 +6672,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124376270</v>
+        <v>124376923</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6675,36 +6684,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6712,10 +6719,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467075</v>
+        <v>467176</v>
       </c>
       <c r="R57" t="n">
-        <v>6720892</v>
+        <v>6720792</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6775,10 +6782,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375752</v>
+        <v>124375010</v>
       </c>
       <c r="B58" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6787,36 +6794,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6824,10 +6825,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467047</v>
+        <v>467143</v>
       </c>
       <c r="R58" t="n">
-        <v>6720974</v>
+        <v>6720866</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6887,7 +6888,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124376865</v>
+        <v>124376762</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6934,10 +6935,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466954</v>
+        <v>467043</v>
       </c>
       <c r="R59" t="n">
-        <v>6720913</v>
+        <v>6721047</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6997,10 +6998,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124374995</v>
+        <v>124376342</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7009,30 +7010,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7040,10 +7042,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467162</v>
+        <v>467083</v>
       </c>
       <c r="R60" t="n">
-        <v>6720859</v>
+        <v>6720839</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7103,10 +7105,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124374922</v>
+        <v>124376046</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7115,30 +7117,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7146,10 +7157,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467194</v>
+        <v>466941</v>
       </c>
       <c r="R61" t="n">
-        <v>6720885</v>
+        <v>6720908</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7209,10 +7220,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124374936</v>
+        <v>124376270</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7221,30 +7232,36 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7252,10 +7269,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467173</v>
+        <v>467075</v>
       </c>
       <c r="R62" t="n">
-        <v>6720889</v>
+        <v>6720892</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7315,7 +7332,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124374709</v>
+        <v>124376865</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7348,7 +7365,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7358,10 +7379,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467216</v>
+        <v>466954</v>
       </c>
       <c r="R63" t="n">
-        <v>6720827</v>
+        <v>6720913</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7421,10 +7442,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124374951</v>
+        <v>124376233</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7433,25 +7454,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7464,10 +7485,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467182</v>
+        <v>467068</v>
       </c>
       <c r="R64" t="n">
-        <v>6720879</v>
+        <v>6720851</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7527,10 +7548,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124376089</v>
+        <v>124375270</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7539,39 +7560,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7579,10 +7591,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466904</v>
+        <v>467180</v>
       </c>
       <c r="R65" t="n">
-        <v>6720952</v>
+        <v>6720912</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7642,10 +7654,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124374804</v>
+        <v>124374936</v>
       </c>
       <c r="B66" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7658,28 +7670,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -7689,10 +7697,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467239</v>
+        <v>467173</v>
       </c>
       <c r="R66" t="n">
-        <v>6720849</v>
+        <v>6720889</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7752,7 +7760,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375140</v>
+        <v>124374570</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7795,10 +7803,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467191</v>
+        <v>467219</v>
       </c>
       <c r="R67" t="n">
-        <v>6720859</v>
+        <v>6720761</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7858,10 +7866,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376775</v>
+        <v>124374620</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7874,26 +7882,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -7905,10 +7913,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467056</v>
+        <v>467213</v>
       </c>
       <c r="R68" t="n">
-        <v>6720996</v>
+        <v>6720795</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7968,10 +7976,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124374309</v>
+        <v>124375057</v>
       </c>
       <c r="B69" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7984,35 +7992,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8020,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467236</v>
+        <v>467156</v>
       </c>
       <c r="R69" t="n">
-        <v>6720773</v>
+        <v>6720850</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
@@ -8064,6 +8063,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376320</v>
+        <v>124374620</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467117</v>
+        <v>467213</v>
       </c>
       <c r="R2" t="n">
-        <v>6720888</v>
+        <v>6720795</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374757</v>
+        <v>124374309</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +801,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467204</v>
+        <v>467236</v>
       </c>
       <c r="R3" t="n">
-        <v>6720836</v>
+        <v>6720773</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124374922</v>
+        <v>124376046</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +911,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467194</v>
+        <v>466941</v>
       </c>
       <c r="R4" t="n">
-        <v>6720885</v>
+        <v>6720908</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -993,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376295</v>
+        <v>124374553</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467095</v>
+        <v>467224</v>
       </c>
       <c r="R5" t="n">
-        <v>6720881</v>
+        <v>6720768</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,7 +1120,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124376775</v>
+        <v>124374736</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1132,11 +1153,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1146,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467056</v>
+        <v>467232</v>
       </c>
       <c r="R6" t="n">
-        <v>6720996</v>
+        <v>6720833</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1209,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124375106</v>
+        <v>124374678</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1252,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467167</v>
+        <v>467230</v>
       </c>
       <c r="R7" t="n">
-        <v>6720870</v>
+        <v>6720817</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1315,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124375684</v>
+        <v>124376794</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,24 +1348,28 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1358,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467166</v>
+        <v>467106</v>
       </c>
       <c r="R8" t="n">
-        <v>6720986</v>
+        <v>6720967</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1421,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124374845</v>
+        <v>124376910</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,39 +1454,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467251</v>
+        <v>467140</v>
       </c>
       <c r="R9" t="n">
-        <v>6720866</v>
+        <v>6720805</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1536,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124376089</v>
+        <v>124376865</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,39 +1564,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466904</v>
+        <v>466954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720952</v>
+        <v>6720913</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374995</v>
+        <v>124375752</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,30 +1674,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467162</v>
+        <v>467047</v>
       </c>
       <c r="R11" t="n">
-        <v>6720859</v>
+        <v>6720974</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1757,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376827</v>
+        <v>124375461</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,34 +1786,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467053</v>
+        <v>467156</v>
       </c>
       <c r="R12" t="n">
-        <v>6720938</v>
+        <v>6720908</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1867,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124374600</v>
+        <v>124375132</v>
       </c>
       <c r="B13" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,25 +1901,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467226</v>
+        <v>467184</v>
       </c>
       <c r="R13" t="n">
-        <v>6720796</v>
+        <v>6720843</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1973,7 +1995,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375039</v>
+        <v>124374922</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2016,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467157</v>
+        <v>467194</v>
       </c>
       <c r="R14" t="n">
-        <v>6720881</v>
+        <v>6720885</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2079,10 +2101,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374309</v>
+        <v>124374936</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,35 +2117,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2131,10 +2144,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467236</v>
+        <v>467173</v>
       </c>
       <c r="R15" t="n">
-        <v>6720773</v>
+        <v>6720889</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2175,6 +2188,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2193,10 +2207,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124376385</v>
+        <v>124374584</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,39 +2219,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,10 +2250,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467094</v>
+        <v>467197</v>
       </c>
       <c r="R16" t="n">
-        <v>6720828</v>
+        <v>6720764</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2308,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375713</v>
+        <v>124374804</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,24 +2329,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2351,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467042</v>
+        <v>467239</v>
       </c>
       <c r="R17" t="n">
-        <v>6721029</v>
+        <v>6720849</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2414,10 +2423,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376031</v>
+        <v>124376320</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,39 +2435,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466944</v>
+        <v>467117</v>
       </c>
       <c r="R18" t="n">
-        <v>6720920</v>
+        <v>6720888</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375768</v>
+        <v>124374900</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467034</v>
+        <v>467191</v>
       </c>
       <c r="R19" t="n">
-        <v>6720933</v>
+        <v>6720901</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2635,7 +2635,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124375118</v>
+        <v>124374709</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467177</v>
+        <v>467216</v>
       </c>
       <c r="R20" t="n">
-        <v>6720859</v>
+        <v>6720827</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124374900</v>
+        <v>124374570</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467191</v>
+        <v>467219</v>
       </c>
       <c r="R21" t="n">
-        <v>6720901</v>
+        <v>6720761</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374964</v>
+        <v>124374757</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467169</v>
+        <v>467204</v>
       </c>
       <c r="R23" t="n">
-        <v>6720904</v>
+        <v>6720836</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124376750</v>
+        <v>124375732</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,34 +3071,36 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3106,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467146</v>
+        <v>467043</v>
       </c>
       <c r="R24" t="n">
-        <v>6721019</v>
+        <v>6720984</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3169,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375436</v>
+        <v>124374476</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3181,39 +3183,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3221,10 +3214,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467164</v>
+        <v>467209</v>
       </c>
       <c r="R25" t="n">
-        <v>6720898</v>
+        <v>6720770</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3284,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124375938</v>
+        <v>124374995</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,35 +3289,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3332,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>466966</v>
+        <v>467162</v>
       </c>
       <c r="R26" t="n">
-        <v>6720916</v>
+        <v>6720859</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3376,6 +3364,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,10 +3383,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375461</v>
+        <v>124376843</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3406,39 +3395,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3446,10 +3430,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467156</v>
+        <v>467041</v>
       </c>
       <c r="R27" t="n">
-        <v>6720908</v>
+        <v>6720899</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3509,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124375482</v>
+        <v>124376295</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,39 +3505,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3561,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467160</v>
+        <v>467095</v>
       </c>
       <c r="R28" t="n">
-        <v>6720905</v>
+        <v>6720881</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3624,7 +3599,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124376808</v>
+        <v>124375140</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3657,11 +3632,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3671,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467087</v>
+        <v>467191</v>
       </c>
       <c r="R29" t="n">
-        <v>6720934</v>
+        <v>6720859</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3734,10 +3705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375783</v>
+        <v>124374951</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3746,39 +3717,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3786,10 +3748,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467016</v>
+        <v>467182</v>
       </c>
       <c r="R30" t="n">
-        <v>6720909</v>
+        <v>6720879</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3849,10 +3811,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124375132</v>
+        <v>124375684</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3865,21 +3827,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3892,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467184</v>
+        <v>467166</v>
       </c>
       <c r="R31" t="n">
-        <v>6720843</v>
+        <v>6720986</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3955,7 +3917,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124374508</v>
+        <v>124376762</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3988,7 +3950,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -3998,10 +3964,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467196</v>
+        <v>467043</v>
       </c>
       <c r="R32" t="n">
-        <v>6720772</v>
+        <v>6721047</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4061,10 +4027,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374709</v>
+        <v>124374600</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4073,25 +4039,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4104,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467216</v>
+        <v>467226</v>
       </c>
       <c r="R33" t="n">
-        <v>6720827</v>
+        <v>6720796</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4167,10 +4133,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374584</v>
+        <v>124376775</v>
       </c>
       <c r="B34" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4183,24 +4149,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4210,10 +4180,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467197</v>
+        <v>467056</v>
       </c>
       <c r="R34" t="n">
-        <v>6720764</v>
+        <v>6720996</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4273,7 +4243,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124376843</v>
+        <v>124375106</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4306,11 +4276,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4320,10 +4286,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467041</v>
+        <v>467167</v>
       </c>
       <c r="R35" t="n">
-        <v>6720899</v>
+        <v>6720870</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4383,10 +4349,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375400</v>
+        <v>124376126</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4395,39 +4361,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4435,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467157</v>
+        <v>466911</v>
       </c>
       <c r="R36" t="n">
-        <v>6720898</v>
+        <v>6720956</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4479,7 +4441,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4498,10 +4459,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374694</v>
+        <v>124376342</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4510,30 +4471,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4541,10 +4503,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467218</v>
+        <v>467083</v>
       </c>
       <c r="R37" t="n">
-        <v>6720814</v>
+        <v>6720839</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4604,7 +4566,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124376910</v>
+        <v>124374694</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4637,11 +4599,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4651,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467140</v>
+        <v>467218</v>
       </c>
       <c r="R38" t="n">
-        <v>6720805</v>
+        <v>6720814</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4714,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124374678</v>
+        <v>124374845</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4726,30 +4684,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4757,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467230</v>
+        <v>467251</v>
       </c>
       <c r="R39" t="n">
-        <v>6720817</v>
+        <v>6720866</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4820,10 +4787,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375621</v>
+        <v>124375436</v>
       </c>
       <c r="B40" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4832,34 +4799,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4867,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467135</v>
+        <v>467164</v>
       </c>
       <c r="R40" t="n">
-        <v>6720927</v>
+        <v>6720898</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4930,10 +4902,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124374804</v>
+        <v>124376031</v>
       </c>
       <c r="B41" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4942,34 +4914,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4977,10 +4954,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467239</v>
+        <v>466944</v>
       </c>
       <c r="R41" t="n">
-        <v>6720849</v>
+        <v>6720920</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5040,10 +5017,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124374476</v>
+        <v>124376194</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5052,30 +5029,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5083,10 +5069,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467209</v>
+        <v>466996</v>
       </c>
       <c r="R42" t="n">
-        <v>6720770</v>
+        <v>6720894</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5146,10 +5132,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375650</v>
+        <v>124375596</v>
       </c>
       <c r="B43" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5158,30 +5144,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5189,10 +5184,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467134</v>
+        <v>467127</v>
       </c>
       <c r="R43" t="n">
-        <v>6720941</v>
+        <v>6720921</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5252,10 +5247,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124376126</v>
+        <v>124375713</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5264,35 +5259,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5300,10 +5290,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466911</v>
+        <v>467042</v>
       </c>
       <c r="R44" t="n">
-        <v>6720956</v>
+        <v>6721029</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5344,6 +5334,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5362,10 +5353,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375596</v>
+        <v>124375292</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5374,39 +5365,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5414,10 +5396,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467127</v>
+        <v>467160</v>
       </c>
       <c r="R45" t="n">
-        <v>6720921</v>
+        <v>6720888</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5477,10 +5459,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375732</v>
+        <v>124375118</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5489,36 +5471,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5526,10 +5502,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467043</v>
+        <v>467177</v>
       </c>
       <c r="R46" t="n">
-        <v>6720984</v>
+        <v>6720859</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5589,10 +5565,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375752</v>
+        <v>124375400</v>
       </c>
       <c r="B47" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5601,36 +5577,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5638,10 +5617,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467047</v>
+        <v>467157</v>
       </c>
       <c r="R47" t="n">
-        <v>6720974</v>
+        <v>6720898</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5701,7 +5680,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124376194</v>
+        <v>124375783</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5753,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466996</v>
+        <v>467016</v>
       </c>
       <c r="R48" t="n">
-        <v>6720894</v>
+        <v>6720909</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5816,10 +5795,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124375292</v>
+        <v>124376270</v>
       </c>
       <c r="B49" t="n">
-        <v>78547</v>
+        <v>8447</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5828,30 +5807,36 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5859,10 +5844,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467160</v>
+        <v>467075</v>
       </c>
       <c r="R49" t="n">
-        <v>6720888</v>
+        <v>6720892</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5922,10 +5907,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376889</v>
+        <v>124375768</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5938,28 +5923,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5969,10 +5950,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467053</v>
+        <v>467034</v>
       </c>
       <c r="R50" t="n">
-        <v>6720874</v>
+        <v>6720933</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6032,10 +6013,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124374736</v>
+        <v>124375938</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6044,30 +6025,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6075,10 +6061,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467232</v>
+        <v>466966</v>
       </c>
       <c r="R51" t="n">
-        <v>6720833</v>
+        <v>6720916</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6119,7 +6105,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6138,7 +6123,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124374553</v>
+        <v>124374508</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6181,10 +6166,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467224</v>
+        <v>467196</v>
       </c>
       <c r="R52" t="n">
-        <v>6720768</v>
+        <v>6720772</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6244,7 +6229,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124375140</v>
+        <v>124376923</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6277,7 +6262,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6287,10 +6276,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467191</v>
+        <v>467176</v>
       </c>
       <c r="R53" t="n">
-        <v>6720859</v>
+        <v>6720792</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6350,7 +6339,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124376794</v>
+        <v>124375057</v>
       </c>
       <c r="B54" t="n">
         <v>78810</v>
@@ -6383,11 +6372,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6397,10 +6382,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467106</v>
+        <v>467156</v>
       </c>
       <c r="R54" t="n">
-        <v>6720967</v>
+        <v>6720850</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6460,7 +6445,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124374951</v>
+        <v>124375270</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6503,10 +6488,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467182</v>
+        <v>467180</v>
       </c>
       <c r="R55" t="n">
-        <v>6720879</v>
+        <v>6720912</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6566,7 +6551,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124375210</v>
+        <v>124376827</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6599,7 +6584,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6609,10 +6598,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467193</v>
+        <v>467053</v>
       </c>
       <c r="R56" t="n">
-        <v>6720911</v>
+        <v>6720938</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6672,7 +6661,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124376923</v>
+        <v>124375039</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6705,11 +6694,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -6719,10 +6704,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467176</v>
+        <v>467157</v>
       </c>
       <c r="R57" t="n">
-        <v>6720792</v>
+        <v>6720881</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6888,10 +6873,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124376762</v>
+        <v>124375650</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6904,28 +6889,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -6935,10 +6916,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467043</v>
+        <v>467134</v>
       </c>
       <c r="R59" t="n">
-        <v>6721047</v>
+        <v>6720941</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6998,10 +6979,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376342</v>
+        <v>124375482</v>
       </c>
       <c r="B60" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7010,29 +6991,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7042,10 +7031,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467083</v>
+        <v>467160</v>
       </c>
       <c r="R60" t="n">
-        <v>6720839</v>
+        <v>6720905</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7105,10 +7094,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376046</v>
+        <v>124374964</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7117,39 +7106,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7157,10 +7137,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466941</v>
+        <v>467169</v>
       </c>
       <c r="R61" t="n">
-        <v>6720908</v>
+        <v>6720904</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7220,10 +7200,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376270</v>
+        <v>124376233</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>90977</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7236,32 +7216,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7269,10 +7243,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467075</v>
+        <v>467068</v>
       </c>
       <c r="R62" t="n">
-        <v>6720892</v>
+        <v>6720851</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7332,7 +7306,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124376865</v>
+        <v>124375210</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7365,11 +7339,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7379,10 +7349,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466954</v>
+        <v>467193</v>
       </c>
       <c r="R63" t="n">
-        <v>6720913</v>
+        <v>6720911</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7442,10 +7412,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376233</v>
+        <v>124376750</v>
       </c>
       <c r="B64" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7454,28 +7424,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -7485,10 +7459,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467068</v>
+        <v>467146</v>
       </c>
       <c r="R64" t="n">
-        <v>6720851</v>
+        <v>6721019</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7548,10 +7522,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124375270</v>
+        <v>124375621</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7564,24 +7538,28 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7591,10 +7569,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467180</v>
+        <v>467135</v>
       </c>
       <c r="R65" t="n">
-        <v>6720912</v>
+        <v>6720927</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7654,7 +7632,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124374936</v>
+        <v>124376889</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7687,7 +7665,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -7697,10 +7679,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467173</v>
+        <v>467053</v>
       </c>
       <c r="R66" t="n">
-        <v>6720889</v>
+        <v>6720874</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7760,7 +7742,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124374570</v>
+        <v>124376808</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7793,7 +7775,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7803,10 +7789,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467219</v>
+        <v>467087</v>
       </c>
       <c r="R67" t="n">
-        <v>6720761</v>
+        <v>6720934</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7866,10 +7852,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124374620</v>
+        <v>124376089</v>
       </c>
       <c r="B68" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7878,34 +7864,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7913,10 +7904,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467213</v>
+        <v>466904</v>
       </c>
       <c r="R68" t="n">
-        <v>6720795</v>
+        <v>6720952</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7976,10 +7967,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124375057</v>
+        <v>124376385</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7988,30 +7979,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467156</v>
+        <v>467094</v>
       </c>
       <c r="R69" t="n">
-        <v>6720850</v>
+        <v>6720828</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374620</v>
+        <v>124375938</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467213</v>
+        <v>466966</v>
       </c>
       <c r="R2" t="n">
-        <v>6720795</v>
+        <v>6720916</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -766,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374309</v>
+        <v>124374757</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467236</v>
+        <v>467204</v>
       </c>
       <c r="R3" t="n">
-        <v>6720773</v>
+        <v>6720836</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124376046</v>
+        <v>124375270</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +903,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466941</v>
+        <v>467180</v>
       </c>
       <c r="R4" t="n">
-        <v>6720908</v>
+        <v>6720912</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1014,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374553</v>
+        <v>124376794</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1047,7 +1030,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1057,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467224</v>
+        <v>467106</v>
       </c>
       <c r="R5" t="n">
-        <v>6720768</v>
+        <v>6720967</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1120,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374736</v>
+        <v>124375106</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1163,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467232</v>
+        <v>467167</v>
       </c>
       <c r="R6" t="n">
-        <v>6720833</v>
+        <v>6720870</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1226,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374678</v>
+        <v>124374309</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,26 +1229,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467230</v>
+        <v>467236</v>
       </c>
       <c r="R7" t="n">
-        <v>6720817</v>
+        <v>6720773</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1313,7 +1309,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124376794</v>
+        <v>124375768</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,28 +1343,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1379,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467106</v>
+        <v>467034</v>
       </c>
       <c r="R8" t="n">
-        <v>6720967</v>
+        <v>6720933</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1442,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376910</v>
+        <v>124375436</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,34 +1445,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467140</v>
+        <v>467164</v>
       </c>
       <c r="R9" t="n">
-        <v>6720805</v>
+        <v>6720898</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1552,7 +1548,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124376865</v>
+        <v>124375210</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1585,11 +1581,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1599,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>466954</v>
+        <v>467193</v>
       </c>
       <c r="R10" t="n">
-        <v>6720913</v>
+        <v>6720911</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1662,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124375752</v>
+        <v>124375684</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,36 +1666,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1711,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467047</v>
+        <v>467166</v>
       </c>
       <c r="R11" t="n">
-        <v>6720974</v>
+        <v>6720986</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1774,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375461</v>
+        <v>124376270</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,39 +1772,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1826,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467156</v>
+        <v>467075</v>
       </c>
       <c r="R12" t="n">
-        <v>6720908</v>
+        <v>6720892</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1889,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124375132</v>
+        <v>124376865</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1922,7 +1905,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1932,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467184</v>
+        <v>466954</v>
       </c>
       <c r="R13" t="n">
-        <v>6720843</v>
+        <v>6720913</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1995,7 +1982,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374922</v>
+        <v>124374678</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2038,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467194</v>
+        <v>467230</v>
       </c>
       <c r="R14" t="n">
-        <v>6720885</v>
+        <v>6720817</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2101,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124374936</v>
+        <v>124375732</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,30 +2100,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2144,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467173</v>
+        <v>467043</v>
       </c>
       <c r="R15" t="n">
-        <v>6720889</v>
+        <v>6720984</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2207,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374584</v>
+        <v>124375461</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2219,30 +2212,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2250,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467197</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6720764</v>
+        <v>6720908</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2313,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124374804</v>
+        <v>124375752</v>
       </c>
       <c r="B17" t="n">
-        <v>91032</v>
+        <v>8447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2325,34 +2327,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2360,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467239</v>
+        <v>467047</v>
       </c>
       <c r="R17" t="n">
-        <v>6720849</v>
+        <v>6720974</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2423,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376320</v>
+        <v>124376385</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,30 +2439,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2466,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467117</v>
+        <v>467094</v>
       </c>
       <c r="R18" t="n">
-        <v>6720888</v>
+        <v>6720828</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2529,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374900</v>
+        <v>124375596</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,30 +2554,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2572,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467191</v>
+        <v>467127</v>
       </c>
       <c r="R19" t="n">
-        <v>6720901</v>
+        <v>6720921</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2635,7 +2657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124374709</v>
+        <v>124374964</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2678,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467216</v>
+        <v>467169</v>
       </c>
       <c r="R20" t="n">
-        <v>6720827</v>
+        <v>6720904</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2741,7 +2763,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124374570</v>
+        <v>124375057</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2784,10 +2806,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467219</v>
+        <v>467156</v>
       </c>
       <c r="R21" t="n">
-        <v>6720761</v>
+        <v>6720850</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2847,10 +2869,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124374436</v>
+        <v>124376320</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2863,21 +2885,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2912,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467202</v>
+        <v>467117</v>
       </c>
       <c r="R22" t="n">
-        <v>6720759</v>
+        <v>6720888</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2953,7 +2975,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374757</v>
+        <v>124374736</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2996,10 +3018,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467204</v>
+        <v>467232</v>
       </c>
       <c r="R23" t="n">
-        <v>6720836</v>
+        <v>6720833</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3059,10 +3081,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375732</v>
+        <v>124376910</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,36 +3093,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3108,10 +3128,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467043</v>
+        <v>467140</v>
       </c>
       <c r="R24" t="n">
-        <v>6720984</v>
+        <v>6720805</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3171,7 +3191,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374476</v>
+        <v>124374694</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3214,10 +3234,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467209</v>
+        <v>467218</v>
       </c>
       <c r="R25" t="n">
-        <v>6720770</v>
+        <v>6720814</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3277,7 +3297,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374995</v>
+        <v>124374508</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3320,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467162</v>
+        <v>467196</v>
       </c>
       <c r="R26" t="n">
-        <v>6720859</v>
+        <v>6720772</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3383,7 +3403,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124376843</v>
+        <v>124374936</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3416,11 +3436,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3430,10 +3446,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467041</v>
+        <v>467173</v>
       </c>
       <c r="R27" t="n">
-        <v>6720899</v>
+        <v>6720889</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3493,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124376295</v>
+        <v>124374709</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3505,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3536,10 +3552,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467095</v>
+        <v>467216</v>
       </c>
       <c r="R28" t="n">
-        <v>6720881</v>
+        <v>6720827</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3599,7 +3615,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124375140</v>
+        <v>124374570</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3642,10 +3658,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467191</v>
+        <v>467219</v>
       </c>
       <c r="R29" t="n">
-        <v>6720859</v>
+        <v>6720761</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3705,7 +3721,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124374951</v>
+        <v>124375132</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3748,10 +3764,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467182</v>
+        <v>467184</v>
       </c>
       <c r="R30" t="n">
-        <v>6720879</v>
+        <v>6720843</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3811,10 +3827,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124375684</v>
+        <v>124374995</v>
       </c>
       <c r="B31" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3827,21 +3843,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3854,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467166</v>
+        <v>467162</v>
       </c>
       <c r="R31" t="n">
-        <v>6720986</v>
+        <v>6720859</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3917,10 +3933,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124376762</v>
+        <v>124375400</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3929,34 +3945,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3964,10 +3985,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467043</v>
+        <v>467157</v>
       </c>
       <c r="R32" t="n">
-        <v>6721047</v>
+        <v>6720898</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4027,10 +4048,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374600</v>
+        <v>124375010</v>
       </c>
       <c r="B33" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4039,25 +4060,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4070,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467226</v>
+        <v>467143</v>
       </c>
       <c r="R33" t="n">
-        <v>6720796</v>
+        <v>6720866</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4133,7 +4154,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124376775</v>
+        <v>124374951</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4166,11 +4187,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4180,10 +4197,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467056</v>
+        <v>467182</v>
       </c>
       <c r="R34" t="n">
-        <v>6720996</v>
+        <v>6720879</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4243,7 +4260,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124375106</v>
+        <v>124374922</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4286,10 +4303,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467167</v>
+        <v>467194</v>
       </c>
       <c r="R35" t="n">
-        <v>6720870</v>
+        <v>6720885</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4349,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124376126</v>
+        <v>124374804</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>91032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4361,35 +4378,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4397,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466911</v>
+        <v>467239</v>
       </c>
       <c r="R36" t="n">
-        <v>6720956</v>
+        <v>6720849</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4441,6 +4457,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4459,10 +4476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124376342</v>
+        <v>124374600</v>
       </c>
       <c r="B37" t="n">
-        <v>96227</v>
+        <v>92293</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4475,27 +4492,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4503,10 +4519,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467083</v>
+        <v>467226</v>
       </c>
       <c r="R37" t="n">
-        <v>6720839</v>
+        <v>6720796</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4566,10 +4582,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124374694</v>
+        <v>124376233</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4578,25 +4594,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4609,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467218</v>
+        <v>467068</v>
       </c>
       <c r="R38" t="n">
-        <v>6720814</v>
+        <v>6720851</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4672,10 +4688,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124374845</v>
+        <v>124374436</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4684,39 +4700,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4724,10 +4731,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467251</v>
+        <v>467202</v>
       </c>
       <c r="R39" t="n">
-        <v>6720866</v>
+        <v>6720759</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4787,10 +4794,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124375436</v>
+        <v>124376342</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4799,37 +4806,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4839,10 +4838,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467164</v>
+        <v>467083</v>
       </c>
       <c r="R40" t="n">
-        <v>6720898</v>
+        <v>6720839</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4902,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124376031</v>
+        <v>124375140</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4914,39 +4913,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4954,10 +4944,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466944</v>
+        <v>467191</v>
       </c>
       <c r="R41" t="n">
-        <v>6720920</v>
+        <v>6720859</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5017,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124376194</v>
+        <v>124375650</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5029,39 +5019,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5069,10 +5050,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466996</v>
+        <v>467134</v>
       </c>
       <c r="R42" t="n">
-        <v>6720894</v>
+        <v>6720941</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5132,7 +5113,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375596</v>
+        <v>124376046</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5167,7 +5148,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5184,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467127</v>
+        <v>466941</v>
       </c>
       <c r="R43" t="n">
-        <v>6720921</v>
+        <v>6720908</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5247,10 +5228,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124375713</v>
+        <v>124376808</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5263,24 +5244,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5290,10 +5275,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467042</v>
+        <v>467087</v>
       </c>
       <c r="R44" t="n">
-        <v>6721029</v>
+        <v>6720934</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5353,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375292</v>
+        <v>124374476</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5369,21 +5354,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5396,10 +5381,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467160</v>
+        <v>467209</v>
       </c>
       <c r="R45" t="n">
-        <v>6720888</v>
+        <v>6720770</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5459,7 +5444,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375118</v>
+        <v>124375039</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5502,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467177</v>
+        <v>467157</v>
       </c>
       <c r="R46" t="n">
-        <v>6720859</v>
+        <v>6720881</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5565,7 +5550,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375400</v>
+        <v>124375783</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5600,7 +5585,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5617,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467157</v>
+        <v>467016</v>
       </c>
       <c r="R47" t="n">
-        <v>6720898</v>
+        <v>6720909</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5680,10 +5665,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124375783</v>
+        <v>124374553</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5692,39 +5677,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5732,10 +5708,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467016</v>
+        <v>467224</v>
       </c>
       <c r="R48" t="n">
-        <v>6720909</v>
+        <v>6720768</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5795,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376270</v>
+        <v>124374584</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>78547</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5807,36 +5783,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5844,10 +5814,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467075</v>
+        <v>467197</v>
       </c>
       <c r="R49" t="n">
-        <v>6720892</v>
+        <v>6720764</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5907,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375768</v>
+        <v>124376295</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>90977</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5919,25 +5889,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5950,10 +5920,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467034</v>
+        <v>467095</v>
       </c>
       <c r="R50" t="n">
-        <v>6720933</v>
+        <v>6720881</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6013,10 +5983,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375938</v>
+        <v>124376750</v>
       </c>
       <c r="B51" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6025,35 +5995,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6061,10 +6030,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466966</v>
+        <v>467146</v>
       </c>
       <c r="R51" t="n">
-        <v>6720916</v>
+        <v>6721019</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6105,6 +6074,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6123,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124374508</v>
+        <v>124375713</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6139,21 +6109,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6166,10 +6136,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467196</v>
+        <v>467042</v>
       </c>
       <c r="R52" t="n">
-        <v>6720772</v>
+        <v>6721029</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6229,10 +6199,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124376923</v>
+        <v>124375292</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6245,28 +6215,24 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6276,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467176</v>
+        <v>467160</v>
       </c>
       <c r="R53" t="n">
-        <v>6720792</v>
+        <v>6720888</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6339,10 +6305,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124375057</v>
+        <v>124375482</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6351,30 +6317,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6382,10 +6357,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467156</v>
+        <v>467160</v>
       </c>
       <c r="R54" t="n">
-        <v>6720850</v>
+        <v>6720905</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6445,10 +6420,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124375270</v>
+        <v>124376194</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6457,30 +6432,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6488,10 +6472,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467180</v>
+        <v>466996</v>
       </c>
       <c r="R55" t="n">
-        <v>6720912</v>
+        <v>6720894</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6551,7 +6535,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376827</v>
+        <v>124376889</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6601,7 +6585,7 @@
         <v>467053</v>
       </c>
       <c r="R56" t="n">
-        <v>6720938</v>
+        <v>6720874</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6661,7 +6645,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124375039</v>
+        <v>124374900</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6704,10 +6688,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467157</v>
+        <v>467191</v>
       </c>
       <c r="R57" t="n">
-        <v>6720881</v>
+        <v>6720901</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6767,7 +6751,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375010</v>
+        <v>124376775</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6800,7 +6784,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -6810,10 +6798,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467143</v>
+        <v>467056</v>
       </c>
       <c r="R58" t="n">
-        <v>6720866</v>
+        <v>6720996</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6873,10 +6861,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375650</v>
+        <v>124375621</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>91032</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6889,24 +6877,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -6916,10 +6908,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467134</v>
+        <v>467135</v>
       </c>
       <c r="R59" t="n">
-        <v>6720941</v>
+        <v>6720927</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6979,10 +6971,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124375482</v>
+        <v>124376126</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6991,39 +6983,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7031,10 +7019,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467160</v>
+        <v>466911</v>
       </c>
       <c r="R60" t="n">
-        <v>6720905</v>
+        <v>6720956</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7075,7 +7063,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7094,7 +7081,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124374964</v>
+        <v>124376762</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -7127,7 +7114,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7137,10 +7128,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467169</v>
+        <v>467043</v>
       </c>
       <c r="R61" t="n">
-        <v>6720904</v>
+        <v>6721047</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7200,10 +7191,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376233</v>
+        <v>124376827</v>
       </c>
       <c r="B62" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7212,28 +7203,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7243,10 +7238,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467068</v>
+        <v>467053</v>
       </c>
       <c r="R62" t="n">
-        <v>6720851</v>
+        <v>6720938</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7306,10 +7301,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124375210</v>
+        <v>124374620</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7322,24 +7317,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7349,10 +7348,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467193</v>
+        <v>467213</v>
       </c>
       <c r="R63" t="n">
-        <v>6720911</v>
+        <v>6720795</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7412,10 +7411,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376750</v>
+        <v>124376089</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7424,25 +7423,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7450,8 +7449,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7459,10 +7463,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467146</v>
+        <v>466904</v>
       </c>
       <c r="R64" t="n">
-        <v>6721019</v>
+        <v>6720952</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7522,10 +7526,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124375621</v>
+        <v>124376923</v>
       </c>
       <c r="B65" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7538,26 +7542,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -7569,10 +7573,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467135</v>
+        <v>467176</v>
       </c>
       <c r="R65" t="n">
-        <v>6720927</v>
+        <v>6720792</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7632,7 +7636,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124376889</v>
+        <v>124376843</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7679,10 +7683,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467053</v>
+        <v>467041</v>
       </c>
       <c r="R66" t="n">
-        <v>6720874</v>
+        <v>6720899</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7742,10 +7746,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124376808</v>
+        <v>124374845</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7754,34 +7758,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7789,10 +7798,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467087</v>
+        <v>467251</v>
       </c>
       <c r="R67" t="n">
-        <v>6720934</v>
+        <v>6720866</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7852,7 +7861,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376089</v>
+        <v>124376031</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7887,7 +7896,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7904,10 +7913,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466904</v>
+        <v>466944</v>
       </c>
       <c r="R68" t="n">
-        <v>6720952</v>
+        <v>6720920</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7967,10 +7976,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124376385</v>
+        <v>124375118</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7979,39 +7988,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467094</v>
+        <v>467177</v>
       </c>
       <c r="R69" t="n">
-        <v>6720828</v>
+        <v>6720859</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124375938</v>
+        <v>124374757</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466966</v>
+        <v>467204</v>
       </c>
       <c r="R2" t="n">
-        <v>6720916</v>
+        <v>6720836</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -767,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124374757</v>
+        <v>124375270</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467204</v>
+        <v>467180</v>
       </c>
       <c r="R3" t="n">
-        <v>6720836</v>
+        <v>6720912</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375270</v>
+        <v>124375938</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,30 +899,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467180</v>
+        <v>466966</v>
       </c>
       <c r="R4" t="n">
-        <v>6720912</v>
+        <v>6720916</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376794</v>
+        <v>124374309</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,30 +1013,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467106</v>
+        <v>467236</v>
       </c>
       <c r="R5" t="n">
-        <v>6720967</v>
+        <v>6720773</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1088,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124375106</v>
+        <v>124375768</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467167</v>
+        <v>467034</v>
       </c>
       <c r="R6" t="n">
-        <v>6720870</v>
+        <v>6720933</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1213,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124374309</v>
+        <v>124376794</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,35 +1233,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467236</v>
+        <v>467106</v>
       </c>
       <c r="R7" t="n">
-        <v>6720773</v>
+        <v>6720967</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1309,6 +1308,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124375768</v>
+        <v>124375106</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467034</v>
+        <v>467167</v>
       </c>
       <c r="R8" t="n">
-        <v>6720933</v>
+        <v>6720870</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124375436</v>
+        <v>124376270</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,39 +1445,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467164</v>
+        <v>467075</v>
       </c>
       <c r="R9" t="n">
-        <v>6720898</v>
+        <v>6720892</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1760,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376270</v>
+        <v>124375436</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,36 +1769,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467075</v>
+        <v>467164</v>
       </c>
       <c r="R12" t="n">
-        <v>6720892</v>
+        <v>6720898</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124374476</v>
+        <v>124375783</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5350,30 +5350,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5381,10 +5390,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467209</v>
+        <v>467016</v>
       </c>
       <c r="R45" t="n">
-        <v>6720770</v>
+        <v>6720909</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5444,7 +5453,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124375039</v>
+        <v>124374476</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5487,10 +5496,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467157</v>
+        <v>467209</v>
       </c>
       <c r="R46" t="n">
-        <v>6720881</v>
+        <v>6720770</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5550,10 +5559,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124375783</v>
+        <v>124374553</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5562,39 +5571,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467016</v>
+        <v>467224</v>
       </c>
       <c r="R47" t="n">
-        <v>6720909</v>
+        <v>6720768</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124374553</v>
+        <v>124375039</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5708,10 +5708,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467224</v>
+        <v>467157</v>
       </c>
       <c r="R48" t="n">
-        <v>6720768</v>
+        <v>6720881</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124374584</v>
+        <v>124376295</v>
       </c>
       <c r="B49" t="n">
-        <v>78547</v>
+        <v>90977</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5783,25 +5783,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467197</v>
+        <v>467095</v>
       </c>
       <c r="R49" t="n">
-        <v>6720764</v>
+        <v>6720881</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376295</v>
+        <v>124376750</v>
       </c>
       <c r="B50" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5889,28 +5889,32 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5920,10 +5924,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467095</v>
+        <v>467146</v>
       </c>
       <c r="R50" t="n">
-        <v>6720881</v>
+        <v>6721019</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5983,10 +5987,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124376750</v>
+        <v>124374584</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5999,28 +6003,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467146</v>
+        <v>467197</v>
       </c>
       <c r="R51" t="n">
-        <v>6721019</v>
+        <v>6720764</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124374757</v>
+        <v>124376270</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467204</v>
+        <v>467075</v>
       </c>
       <c r="R2" t="n">
-        <v>6720836</v>
+        <v>6720892</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375270</v>
+        <v>124375732</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +799,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467180</v>
+        <v>467043</v>
       </c>
       <c r="R3" t="n">
-        <v>6720912</v>
+        <v>6720984</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375938</v>
+        <v>124375783</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,35 +911,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466966</v>
+        <v>467016</v>
       </c>
       <c r="R4" t="n">
-        <v>6720916</v>
+        <v>6720909</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -979,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124374309</v>
+        <v>124376889</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,35 +1030,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467236</v>
+        <v>467053</v>
       </c>
       <c r="R5" t="n">
-        <v>6720773</v>
+        <v>6720874</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1093,6 +1105,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124375768</v>
+        <v>124374694</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467034</v>
+        <v>467218</v>
       </c>
       <c r="R6" t="n">
-        <v>6720933</v>
+        <v>6720814</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1217,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124376794</v>
+        <v>124376923</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1252,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1264,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467106</v>
+        <v>467176</v>
       </c>
       <c r="R7" t="n">
-        <v>6720967</v>
+        <v>6720792</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1327,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124375106</v>
+        <v>124375140</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1370,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467167</v>
+        <v>467191</v>
       </c>
       <c r="R8" t="n">
-        <v>6720870</v>
+        <v>6720859</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1433,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376270</v>
+        <v>124376233</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,32 +1462,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467075</v>
+        <v>467068</v>
       </c>
       <c r="R9" t="n">
-        <v>6720892</v>
+        <v>6720851</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1545,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124375210</v>
+        <v>124376808</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1578,7 +1585,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1588,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467193</v>
+        <v>467087</v>
       </c>
       <c r="R10" t="n">
-        <v>6720911</v>
+        <v>6720934</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124375684</v>
+        <v>124374964</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,21 +1678,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467166</v>
+        <v>467169</v>
       </c>
       <c r="R11" t="n">
-        <v>6720986</v>
+        <v>6720904</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1757,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124375436</v>
+        <v>124376750</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,39 +1780,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467164</v>
+        <v>467146</v>
       </c>
       <c r="R12" t="n">
-        <v>6720898</v>
+        <v>6721019</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1872,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124376865</v>
+        <v>124374620</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,26 +1894,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1919,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>466954</v>
+        <v>467213</v>
       </c>
       <c r="R13" t="n">
-        <v>6720913</v>
+        <v>6720795</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1982,7 +1988,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124374678</v>
+        <v>124375132</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2025,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467230</v>
+        <v>467184</v>
       </c>
       <c r="R14" t="n">
-        <v>6720817</v>
+        <v>6720843</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2088,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375732</v>
+        <v>124375118</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,36 +2106,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467043</v>
+        <v>467177</v>
       </c>
       <c r="R15" t="n">
-        <v>6720984</v>
+        <v>6720859</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124375461</v>
+        <v>124374995</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,39 +2212,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2252,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467162</v>
       </c>
       <c r="R16" t="n">
-        <v>6720908</v>
+        <v>6720859</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2315,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124375752</v>
+        <v>124374936</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2327,36 +2318,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2364,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467047</v>
+        <v>467173</v>
       </c>
       <c r="R17" t="n">
-        <v>6720974</v>
+        <v>6720889</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2427,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124376385</v>
+        <v>124374709</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2439,39 +2424,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2479,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467094</v>
+        <v>467216</v>
       </c>
       <c r="R18" t="n">
-        <v>6720828</v>
+        <v>6720827</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2542,10 +2518,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124375596</v>
+        <v>124374309</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,39 +2530,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2594,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467127</v>
+        <v>467236</v>
       </c>
       <c r="R19" t="n">
-        <v>6720921</v>
+        <v>6720773</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2638,7 +2614,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2657,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124374964</v>
+        <v>124375650</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2673,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2700,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467169</v>
+        <v>467134</v>
       </c>
       <c r="R20" t="n">
-        <v>6720904</v>
+        <v>6720941</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2763,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124375057</v>
+        <v>124376320</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2779,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2806,10 +2781,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467156</v>
+        <v>467117</v>
       </c>
       <c r="R21" t="n">
-        <v>6720850</v>
+        <v>6720888</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2869,10 +2844,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376320</v>
+        <v>124376762</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2885,24 +2860,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2912,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467117</v>
+        <v>467043</v>
       </c>
       <c r="R22" t="n">
-        <v>6720888</v>
+        <v>6721047</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2975,10 +2954,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374736</v>
+        <v>124374600</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2987,25 +2966,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3018,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467232</v>
+        <v>467226</v>
       </c>
       <c r="R23" t="n">
-        <v>6720833</v>
+        <v>6720796</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3081,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124376910</v>
+        <v>124375768</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3097,28 +3076,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3128,10 +3103,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467140</v>
+        <v>467034</v>
       </c>
       <c r="R24" t="n">
-        <v>6720805</v>
+        <v>6720933</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3191,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124374694</v>
+        <v>124375713</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3207,21 +3182,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3234,10 +3209,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467218</v>
+        <v>467042</v>
       </c>
       <c r="R25" t="n">
-        <v>6720814</v>
+        <v>6721029</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3297,7 +3272,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374508</v>
+        <v>124374678</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3340,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467196</v>
+        <v>467230</v>
       </c>
       <c r="R26" t="n">
-        <v>6720772</v>
+        <v>6720817</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3403,7 +3378,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124374936</v>
+        <v>124375010</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3446,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467173</v>
+        <v>467143</v>
       </c>
       <c r="R27" t="n">
-        <v>6720889</v>
+        <v>6720866</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3509,7 +3484,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374709</v>
+        <v>124374951</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3552,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467216</v>
+        <v>467182</v>
       </c>
       <c r="R28" t="n">
-        <v>6720827</v>
+        <v>6720879</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3615,7 +3590,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374570</v>
+        <v>124374553</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3658,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467219</v>
+        <v>467224</v>
       </c>
       <c r="R29" t="n">
-        <v>6720761</v>
+        <v>6720768</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3721,7 +3696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124375132</v>
+        <v>124376910</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3754,7 +3729,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -3764,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467184</v>
+        <v>467140</v>
       </c>
       <c r="R30" t="n">
-        <v>6720843</v>
+        <v>6720805</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3827,10 +3806,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124374995</v>
+        <v>124376126</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3839,30 +3818,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3870,10 +3854,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467162</v>
+        <v>466911</v>
       </c>
       <c r="R31" t="n">
-        <v>6720859</v>
+        <v>6720956</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3914,7 +3898,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3933,10 +3916,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375400</v>
+        <v>124375938</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3945,39 +3928,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3985,10 +3964,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467157</v>
+        <v>466966</v>
       </c>
       <c r="R32" t="n">
-        <v>6720898</v>
+        <v>6720916</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4029,7 +4008,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4048,7 +4026,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124375010</v>
+        <v>124374900</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4091,10 +4069,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467143</v>
+        <v>467191</v>
       </c>
       <c r="R33" t="n">
-        <v>6720866</v>
+        <v>6720901</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4154,10 +4132,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374951</v>
+        <v>124374804</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4170,24 +4148,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4197,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467182</v>
+        <v>467239</v>
       </c>
       <c r="R34" t="n">
-        <v>6720879</v>
+        <v>6720849</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4260,7 +4242,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124374922</v>
+        <v>124376794</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4293,7 +4275,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4303,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467194</v>
+        <v>467106</v>
       </c>
       <c r="R35" t="n">
-        <v>6720885</v>
+        <v>6720967</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4366,7 +4352,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124374804</v>
+        <v>124375621</v>
       </c>
       <c r="B36" t="n">
         <v>91032</v>
@@ -4413,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467239</v>
+        <v>467135</v>
       </c>
       <c r="R36" t="n">
-        <v>6720849</v>
+        <v>6720927</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4476,10 +4462,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124374600</v>
+        <v>124376089</v>
       </c>
       <c r="B37" t="n">
-        <v>92293</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4488,30 +4474,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4519,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>467226</v>
+        <v>466904</v>
       </c>
       <c r="R37" t="n">
-        <v>6720796</v>
+        <v>6720952</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4582,7 +4577,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124376233</v>
+        <v>124376295</v>
       </c>
       <c r="B38" t="n">
         <v>90977</v>
@@ -4625,10 +4620,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467068</v>
+        <v>467095</v>
       </c>
       <c r="R38" t="n">
-        <v>6720851</v>
+        <v>6720881</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4688,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124374436</v>
+        <v>124375596</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,30 +4695,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4731,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467202</v>
+        <v>467127</v>
       </c>
       <c r="R39" t="n">
-        <v>6720759</v>
+        <v>6720921</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4794,10 +4798,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124376342</v>
+        <v>124374584</v>
       </c>
       <c r="B40" t="n">
-        <v>96227</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4806,31 +4810,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4838,10 +4841,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467083</v>
+        <v>467197</v>
       </c>
       <c r="R40" t="n">
-        <v>6720839</v>
+        <v>6720764</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4901,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375140</v>
+        <v>124375684</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4917,21 +4920,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4944,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467191</v>
+        <v>467166</v>
       </c>
       <c r="R41" t="n">
-        <v>6720859</v>
+        <v>6720986</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5007,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124375650</v>
+        <v>124376865</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5023,24 +5026,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5050,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467134</v>
+        <v>466954</v>
       </c>
       <c r="R42" t="n">
-        <v>6720941</v>
+        <v>6720913</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5113,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124376046</v>
+        <v>124375270</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5125,39 +5132,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5165,10 +5163,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466941</v>
+        <v>467180</v>
       </c>
       <c r="R43" t="n">
-        <v>6720908</v>
+        <v>6720912</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5228,7 +5226,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124376808</v>
+        <v>124376775</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5275,10 +5273,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467087</v>
+        <v>467056</v>
       </c>
       <c r="R44" t="n">
-        <v>6720934</v>
+        <v>6720996</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5338,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375783</v>
+        <v>124375210</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5350,39 +5348,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5390,10 +5379,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467016</v>
+        <v>467193</v>
       </c>
       <c r="R45" t="n">
-        <v>6720909</v>
+        <v>6720911</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5453,10 +5442,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124374476</v>
+        <v>124376342</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5465,30 +5454,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5496,10 +5486,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467209</v>
+        <v>467083</v>
       </c>
       <c r="R46" t="n">
-        <v>6720770</v>
+        <v>6720839</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5559,7 +5549,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374553</v>
+        <v>124374476</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5602,10 +5592,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467224</v>
+        <v>467209</v>
       </c>
       <c r="R47" t="n">
-        <v>6720768</v>
+        <v>6720770</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5665,7 +5655,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124375039</v>
+        <v>124374508</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5708,10 +5698,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467157</v>
+        <v>467196</v>
       </c>
       <c r="R48" t="n">
-        <v>6720881</v>
+        <v>6720772</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5771,10 +5761,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124376295</v>
+        <v>124374436</v>
       </c>
       <c r="B49" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5783,25 +5773,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5814,10 +5804,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467095</v>
+        <v>467202</v>
       </c>
       <c r="R49" t="n">
-        <v>6720881</v>
+        <v>6720759</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5877,7 +5867,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124376750</v>
+        <v>124375039</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5910,11 +5900,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5924,10 +5910,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467146</v>
+        <v>467157</v>
       </c>
       <c r="R50" t="n">
-        <v>6721019</v>
+        <v>6720881</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5987,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124374584</v>
+        <v>124375482</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5999,30 +5985,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6030,10 +6025,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467197</v>
+        <v>467160</v>
       </c>
       <c r="R51" t="n">
-        <v>6720764</v>
+        <v>6720905</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6093,10 +6088,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124375713</v>
+        <v>124376031</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6105,30 +6100,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6136,10 +6140,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467042</v>
+        <v>466944</v>
       </c>
       <c r="R52" t="n">
-        <v>6721029</v>
+        <v>6720920</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6199,10 +6203,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124375292</v>
+        <v>124375436</v>
       </c>
       <c r="B53" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6211,30 +6215,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6242,10 +6255,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467160</v>
+        <v>467164</v>
       </c>
       <c r="R53" t="n">
-        <v>6720888</v>
+        <v>6720898</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6305,10 +6318,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124375482</v>
+        <v>124374736</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6317,39 +6330,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6357,10 +6361,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467160</v>
+        <v>467232</v>
       </c>
       <c r="R54" t="n">
-        <v>6720905</v>
+        <v>6720833</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6420,10 +6424,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124376194</v>
+        <v>124376843</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6432,39 +6436,34 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6472,10 +6471,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466996</v>
+        <v>467041</v>
       </c>
       <c r="R55" t="n">
-        <v>6720894</v>
+        <v>6720899</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6535,7 +6534,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124376889</v>
+        <v>124374757</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6568,11 +6567,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6582,10 +6577,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467053</v>
+        <v>467204</v>
       </c>
       <c r="R56" t="n">
-        <v>6720874</v>
+        <v>6720836</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6645,10 +6640,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124374900</v>
+        <v>124375752</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6657,30 +6652,36 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6688,10 +6689,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467191</v>
+        <v>467047</v>
       </c>
       <c r="R57" t="n">
-        <v>6720901</v>
+        <v>6720974</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6751,10 +6752,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124376775</v>
+        <v>124375400</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6763,34 +6764,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6798,10 +6804,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467056</v>
+        <v>467157</v>
       </c>
       <c r="R58" t="n">
-        <v>6720996</v>
+        <v>6720898</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6861,10 +6867,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375621</v>
+        <v>124375461</v>
       </c>
       <c r="B59" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6873,34 +6879,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6908,10 +6919,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467135</v>
+        <v>467156</v>
       </c>
       <c r="R59" t="n">
-        <v>6720927</v>
+        <v>6720908</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6971,10 +6982,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124376126</v>
+        <v>124374570</v>
       </c>
       <c r="B60" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6983,35 +6994,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7019,10 +7025,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466911</v>
+        <v>467219</v>
       </c>
       <c r="R60" t="n">
-        <v>6720956</v>
+        <v>6720761</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7063,6 +7069,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7081,10 +7088,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376762</v>
+        <v>124376046</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7093,34 +7100,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7128,10 +7140,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467043</v>
+        <v>466941</v>
       </c>
       <c r="R61" t="n">
-        <v>6721047</v>
+        <v>6720908</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7301,10 +7313,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124374620</v>
+        <v>124376194</v>
       </c>
       <c r="B63" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7313,34 +7325,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7348,10 +7365,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467213</v>
+        <v>466996</v>
       </c>
       <c r="R63" t="n">
-        <v>6720795</v>
+        <v>6720894</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7411,10 +7428,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124376089</v>
+        <v>124375292</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7423,39 +7440,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7463,10 +7471,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466904</v>
+        <v>467160</v>
       </c>
       <c r="R64" t="n">
-        <v>6720952</v>
+        <v>6720888</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7526,7 +7534,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124376923</v>
+        <v>124374922</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7559,11 +7567,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -7573,10 +7577,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467176</v>
+        <v>467194</v>
       </c>
       <c r="R65" t="n">
-        <v>6720792</v>
+        <v>6720885</v>
       </c>
       <c r="S65" t="n">
         <v>50</v>
@@ -7636,10 +7640,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124376843</v>
+        <v>124376385</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7648,34 +7652,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7683,10 +7692,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467041</v>
+        <v>467094</v>
       </c>
       <c r="R66" t="n">
-        <v>6720899</v>
+        <v>6720828</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7746,10 +7755,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124374845</v>
+        <v>124375057</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7758,39 +7767,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467251</v>
+        <v>467156</v>
       </c>
       <c r="R67" t="n">
-        <v>6720866</v>
+        <v>6720850</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7861,10 +7861,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124376031</v>
+        <v>124375106</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7873,39 +7873,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7913,10 +7904,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466944</v>
+        <v>467167</v>
       </c>
       <c r="R68" t="n">
-        <v>6720920</v>
+        <v>6720870</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7976,10 +7967,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124375118</v>
+        <v>124374845</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7988,30 +7979,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467177</v>
+        <v>467251</v>
       </c>
       <c r="R69" t="n">
-        <v>6720859</v>
+        <v>6720866</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>

--- a/artfynd/A 13342-2025 artfynd.xlsx
+++ b/artfynd/A 13342-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124376270</v>
+        <v>124376923</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467075</v>
+        <v>467176</v>
       </c>
       <c r="R2" t="n">
-        <v>6720892</v>
+        <v>6720792</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -787,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124375732</v>
+        <v>124374678</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,36 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467043</v>
+        <v>467230</v>
       </c>
       <c r="R3" t="n">
-        <v>6720984</v>
+        <v>6720817</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124375783</v>
+        <v>124376910</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,39 +903,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467016</v>
+        <v>467140</v>
       </c>
       <c r="R4" t="n">
-        <v>6720909</v>
+        <v>6720805</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1014,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124376889</v>
+        <v>124374600</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,32 +1013,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1061,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467053</v>
+        <v>467226</v>
       </c>
       <c r="R5" t="n">
-        <v>6720874</v>
+        <v>6720796</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1124,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124374694</v>
+        <v>124376750</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1157,7 +1140,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1167,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467218</v>
+        <v>467146</v>
       </c>
       <c r="R6" t="n">
-        <v>6720814</v>
+        <v>6721019</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1230,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124376923</v>
+        <v>124374584</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,28 +1233,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1277,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467176</v>
+        <v>467197</v>
       </c>
       <c r="R7" t="n">
-        <v>6720792</v>
+        <v>6720764</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1340,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124375140</v>
+        <v>124374476</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1383,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467191</v>
+        <v>467209</v>
       </c>
       <c r="R8" t="n">
-        <v>6720859</v>
+        <v>6720770</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1446,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124376233</v>
+        <v>124375596</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,30 +1441,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467068</v>
+        <v>467127</v>
       </c>
       <c r="R9" t="n">
-        <v>6720851</v>
+        <v>6720921</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1552,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124376808</v>
+        <v>124375938</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,34 +1556,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1599,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467087</v>
+        <v>466966</v>
       </c>
       <c r="R10" t="n">
-        <v>6720934</v>
+        <v>6720916</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1643,7 +1636,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1662,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124374964</v>
+        <v>124376126</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,30 +1666,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1705,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467169</v>
+        <v>466911</v>
       </c>
       <c r="R11" t="n">
-        <v>6720904</v>
+        <v>6720956</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1749,7 +1746,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124376750</v>
+        <v>124375783</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,34 +1776,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1815,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467146</v>
+        <v>467016</v>
       </c>
       <c r="R12" t="n">
-        <v>6721019</v>
+        <v>6720909</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1878,10 +1879,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124374620</v>
+        <v>124375482</v>
       </c>
       <c r="B13" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,34 +1891,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1925,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467213</v>
+        <v>467160</v>
       </c>
       <c r="R13" t="n">
-        <v>6720795</v>
+        <v>6720905</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1988,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124375132</v>
+        <v>124376808</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2021,7 +2027,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2031,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467184</v>
+        <v>467087</v>
       </c>
       <c r="R14" t="n">
-        <v>6720843</v>
+        <v>6720934</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2094,7 +2104,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124375118</v>
+        <v>124375106</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2137,10 +2147,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467177</v>
+        <v>467167</v>
       </c>
       <c r="R15" t="n">
-        <v>6720859</v>
+        <v>6720870</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2200,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124374995</v>
+        <v>124375621</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2216,24 +2226,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2243,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467162</v>
+        <v>467135</v>
       </c>
       <c r="R16" t="n">
-        <v>6720859</v>
+        <v>6720927</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2306,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124374936</v>
+        <v>124375713</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,21 +2336,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2363,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467173</v>
+        <v>467042</v>
       </c>
       <c r="R17" t="n">
-        <v>6720889</v>
+        <v>6721029</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2412,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124374709</v>
+        <v>124376342</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2424,30 +2438,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2455,10 +2470,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467216</v>
+        <v>467083</v>
       </c>
       <c r="R18" t="n">
-        <v>6720827</v>
+        <v>6720839</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2518,10 +2533,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124374309</v>
+        <v>124376865</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,35 +2549,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2570,10 +2580,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467236</v>
+        <v>466954</v>
       </c>
       <c r="R19" t="n">
-        <v>6720773</v>
+        <v>6720913</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2614,6 +2624,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2643,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124375650</v>
+        <v>124375270</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2659,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2686,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467134</v>
+        <v>467180</v>
       </c>
       <c r="R20" t="n">
-        <v>6720941</v>
+        <v>6720912</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2738,10 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124376320</v>
+        <v>124375400</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,30 +2761,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2781,10 +2801,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467117</v>
+        <v>467157</v>
       </c>
       <c r="R21" t="n">
-        <v>6720888</v>
+        <v>6720898</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2844,7 +2864,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124376762</v>
+        <v>124375039</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2877,11 +2897,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2891,10 +2907,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467043</v>
+        <v>467157</v>
       </c>
       <c r="R22" t="n">
-        <v>6721047</v>
+        <v>6720881</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2954,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124374600</v>
+        <v>124374309</v>
       </c>
       <c r="B23" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2966,30 +2982,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2997,10 +3022,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467226</v>
+        <v>467236</v>
       </c>
       <c r="R23" t="n">
-        <v>6720796</v>
+        <v>6720773</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3041,7 +3066,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3060,10 +3084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124375768</v>
+        <v>124374736</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,21 +3100,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3103,10 +3127,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467034</v>
+        <v>467232</v>
       </c>
       <c r="R24" t="n">
-        <v>6720933</v>
+        <v>6720833</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3166,10 +3190,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124375713</v>
+        <v>124374757</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,21 +3206,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3209,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467042</v>
+        <v>467204</v>
       </c>
       <c r="R25" t="n">
-        <v>6721029</v>
+        <v>6720836</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3272,7 +3296,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124374678</v>
+        <v>124374995</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3315,10 +3339,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467230</v>
+        <v>467162</v>
       </c>
       <c r="R26" t="n">
-        <v>6720817</v>
+        <v>6720859</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3378,10 +3402,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124375010</v>
+        <v>124376031</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,30 +3414,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3421,10 +3454,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467143</v>
+        <v>466944</v>
       </c>
       <c r="R27" t="n">
-        <v>6720866</v>
+        <v>6720920</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3484,7 +3517,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124374951</v>
+        <v>124375118</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3527,10 +3560,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467182</v>
+        <v>467177</v>
       </c>
       <c r="R28" t="n">
-        <v>6720879</v>
+        <v>6720859</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3590,10 +3623,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124374553</v>
+        <v>124376295</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3602,25 +3635,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3633,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467224</v>
+        <v>467095</v>
       </c>
       <c r="R29" t="n">
-        <v>6720768</v>
+        <v>6720881</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3696,10 +3729,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124376910</v>
+        <v>124376046</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3708,34 +3741,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3743,10 +3781,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467140</v>
+        <v>466941</v>
       </c>
       <c r="R30" t="n">
-        <v>6720805</v>
+        <v>6720908</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3806,10 +3844,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124376126</v>
+        <v>124376270</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3822,29 +3860,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3854,10 +3893,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466911</v>
+        <v>467075</v>
       </c>
       <c r="R31" t="n">
-        <v>6720956</v>
+        <v>6720892</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -3898,6 +3937,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3916,10 +3956,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124375938</v>
+        <v>124375010</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3928,35 +3968,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3964,10 +3999,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466966</v>
+        <v>467143</v>
       </c>
       <c r="R32" t="n">
-        <v>6720916</v>
+        <v>6720866</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4008,6 +4043,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4026,7 +4062,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124374900</v>
+        <v>124374709</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4069,10 +4105,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467191</v>
+        <v>467216</v>
       </c>
       <c r="R33" t="n">
-        <v>6720901</v>
+        <v>6720827</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4132,10 +4168,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124374804</v>
+        <v>124375752</v>
       </c>
       <c r="B34" t="n">
-        <v>91032</v>
+        <v>8447</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4144,34 +4180,36 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4179,10 +4217,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467239</v>
+        <v>467047</v>
       </c>
       <c r="R34" t="n">
-        <v>6720849</v>
+        <v>6720974</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4242,10 +4280,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124376794</v>
+        <v>124374845</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4254,34 +4292,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4289,10 +4332,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467106</v>
+        <v>467251</v>
       </c>
       <c r="R35" t="n">
-        <v>6720967</v>
+        <v>6720866</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4352,10 +4395,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124375621</v>
+        <v>124375684</v>
       </c>
       <c r="B36" t="n">
-        <v>91032</v>
+        <v>78547</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,28 +4411,24 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4399,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467135</v>
+        <v>467166</v>
       </c>
       <c r="R36" t="n">
-        <v>6720927</v>
+        <v>6720986</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4462,10 +4501,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124376089</v>
+        <v>124376794</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4474,39 +4513,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4514,10 +4548,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466904</v>
+        <v>467106</v>
       </c>
       <c r="R37" t="n">
-        <v>6720952</v>
+        <v>6720967</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4577,10 +4611,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124376295</v>
+        <v>124376827</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4589,28 +4623,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4620,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467095</v>
+        <v>467053</v>
       </c>
       <c r="R38" t="n">
-        <v>6720881</v>
+        <v>6720938</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4683,10 +4721,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124375596</v>
+        <v>124376233</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4695,39 +4733,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4735,10 +4764,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467127</v>
+        <v>467068</v>
       </c>
       <c r="R39" t="n">
-        <v>6720921</v>
+        <v>6720851</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4798,10 +4827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124374584</v>
+        <v>124376843</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4814,24 +4843,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4841,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467197</v>
+        <v>467041</v>
       </c>
       <c r="R40" t="n">
-        <v>6720764</v>
+        <v>6720899</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -4904,10 +4937,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124375684</v>
+        <v>124375210</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4920,21 +4953,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4947,10 +4980,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467166</v>
+        <v>467193</v>
       </c>
       <c r="R41" t="n">
-        <v>6720986</v>
+        <v>6720911</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5010,7 +5043,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124376865</v>
+        <v>124374900</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5043,11 +5076,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5057,10 +5086,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466954</v>
+        <v>467191</v>
       </c>
       <c r="R42" t="n">
-        <v>6720913</v>
+        <v>6720901</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5120,10 +5149,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124375270</v>
+        <v>124374804</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5136,24 +5165,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5163,10 +5196,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467180</v>
+        <v>467239</v>
       </c>
       <c r="R43" t="n">
-        <v>6720912</v>
+        <v>6720849</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5226,7 +5259,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124376775</v>
+        <v>124374553</v>
       </c>
       <c r="B44" t="n">
         <v>78810</v>
@@ -5259,11 +5292,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5273,10 +5302,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>467056</v>
+        <v>467224</v>
       </c>
       <c r="R44" t="n">
-        <v>6720996</v>
+        <v>6720768</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5336,7 +5365,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124375210</v>
+        <v>124375140</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5379,10 +5408,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>467193</v>
+        <v>467191</v>
       </c>
       <c r="R45" t="n">
-        <v>6720911</v>
+        <v>6720859</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5442,10 +5471,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124376342</v>
+        <v>124375768</v>
       </c>
       <c r="B46" t="n">
-        <v>96227</v>
+        <v>78547</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5454,31 +5483,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5486,10 +5514,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467083</v>
+        <v>467034</v>
       </c>
       <c r="R46" t="n">
-        <v>6720839</v>
+        <v>6720933</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5549,10 +5577,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124374476</v>
+        <v>124375732</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5561,30 +5589,36 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5592,10 +5626,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467209</v>
+        <v>467043</v>
       </c>
       <c r="R47" t="n">
-        <v>6720770</v>
+        <v>6720984</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -5655,10 +5689,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124374508</v>
+        <v>124375650</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5671,21 +5705,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5698,10 +5732,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467196</v>
+        <v>467134</v>
       </c>
       <c r="R48" t="n">
-        <v>6720772</v>
+        <v>6720941</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5761,10 +5795,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124374436</v>
+        <v>124376320</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5777,21 +5811,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5804,10 +5838,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467202</v>
+        <v>467117</v>
       </c>
       <c r="R49" t="n">
-        <v>6720759</v>
+        <v>6720888</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -5867,7 +5901,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124375039</v>
+        <v>124376889</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5900,7 +5934,11 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -5910,10 +5948,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467157</v>
+        <v>467053</v>
       </c>
       <c r="R50" t="n">
-        <v>6720881</v>
+        <v>6720874</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -5973,10 +6011,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124375482</v>
+        <v>124374951</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5985,39 +6023,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6025,10 +6054,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467160</v>
+        <v>467182</v>
       </c>
       <c r="R51" t="n">
-        <v>6720905</v>
+        <v>6720879</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6088,10 +6117,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124376031</v>
+        <v>124376775</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6100,39 +6129,34 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6140,10 +6164,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466944</v>
+        <v>467056</v>
       </c>
       <c r="R52" t="n">
-        <v>6720920</v>
+        <v>6720996</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6203,7 +6227,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124375436</v>
+        <v>124375461</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -6255,10 +6279,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467164</v>
+        <v>467156</v>
       </c>
       <c r="R53" t="n">
-        <v>6720898</v>
+        <v>6720908</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -6318,10 +6342,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124374736</v>
+        <v>124376089</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6330,30 +6354,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6361,10 +6394,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467232</v>
+        <v>466904</v>
       </c>
       <c r="R54" t="n">
-        <v>6720833</v>
+        <v>6720952</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6424,10 +6457,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124376843</v>
+        <v>124376385</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6436,34 +6469,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6471,10 +6509,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467041</v>
+        <v>467094</v>
       </c>
       <c r="R55" t="n">
-        <v>6720899</v>
+        <v>6720828</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6534,10 +6572,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124374757</v>
+        <v>124376194</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6546,30 +6584,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6577,10 +6624,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467204</v>
+        <v>466996</v>
       </c>
       <c r="R56" t="n">
-        <v>6720836</v>
+        <v>6720894</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6640,10 +6687,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124375752</v>
+        <v>124375057</v>
       </c>
       <c r="B57" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6652,36 +6699,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6689,10 +6730,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467047</v>
+        <v>467156</v>
       </c>
       <c r="R57" t="n">
-        <v>6720974</v>
+        <v>6720850</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6752,10 +6793,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124375400</v>
+        <v>124376762</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6764,39 +6805,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6804,10 +6840,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467157</v>
+        <v>467043</v>
       </c>
       <c r="R58" t="n">
-        <v>6720898</v>
+        <v>6721047</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -6867,10 +6903,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124375461</v>
+        <v>124374620</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6879,39 +6915,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6919,10 +6950,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467156</v>
+        <v>467213</v>
       </c>
       <c r="R59" t="n">
-        <v>6720908</v>
+        <v>6720795</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -6982,7 +7013,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124374570</v>
+        <v>124374936</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7025,10 +7056,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467219</v>
+        <v>467173</v>
       </c>
       <c r="R60" t="n">
-        <v>6720761</v>
+        <v>6720889</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7088,10 +7119,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124376046</v>
+        <v>124374570</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7100,39 +7131,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7140,10 +7162,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466941</v>
+        <v>467219</v>
       </c>
       <c r="R61" t="n">
-        <v>6720908</v>
+        <v>6720761</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7203,7 +7225,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124376827</v>
+        <v>124375132</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7236,11 +7258,7 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7250,10 +7268,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467053</v>
+        <v>467184</v>
       </c>
       <c r="R62" t="n">
-        <v>6720938</v>
+        <v>6720843</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7313,10 +7331,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124376194</v>
+        <v>124375292</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7325,39 +7343,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7365,10 +7374,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466996</v>
+        <v>467160</v>
       </c>
       <c r="R63" t="n">
-        <v>6720894</v>
+        <v>6720888</v>
       </c>
       <c r="S63" t="n">
         <v>50</v>
@@ -7428,10 +7437,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124375292</v>
+        <v>124374964</v>
       </c>
       <c r="B64" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7444,21 +7453,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7471,10 +7480,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467160</v>
+        <v>467169</v>
       </c>
       <c r="R64" t="n">
-        <v>6720888</v>
+        <v>6720904</v>
       </c>
       <c r="S64" t="n">
         <v>50</v>
@@ -7640,10 +7649,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124376385</v>
+        <v>124374694</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7652,39 +7661,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467094</v>
+        <v>467218</v>
       </c>
       <c r="R66" t="n">
-        <v>6720828</v>
+        <v>6720814</v>
       </c>
       <c r="S66" t="n">
         <v>50</v>
@@ -7755,10 +7755,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124375057</v>
+        <v>124375436</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7767,30 +7767,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7798,10 +7807,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467156</v>
+        <v>467164</v>
       </c>
       <c r="R67" t="n">
-        <v>6720850</v>
+        <v>6720898</v>
       </c>
       <c r="S67" t="n">
         <v>50</v>
@@ -7861,7 +7870,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124375106</v>
+        <v>124374508</v>
       </c>
       <c r="B68" t="n">
         <v>78810</v>
@@ -7904,10 +7913,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>467167</v>
+        <v>467196</v>
       </c>
       <c r="R68" t="n">
-        <v>6720870</v>
+        <v>6720772</v>
       </c>
       <c r="S68" t="n">
         <v>50</v>
@@ -7967,10 +7976,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124374845</v>
+        <v>124374436</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7979,39 +7988,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467251</v>
+        <v>467202</v>
       </c>
       <c r="R69" t="n">
-        <v>6720866</v>
+        <v>6720759</v>
       </c>
       <c r="S69" t="n">
         <v>50</v>
